--- a/AutomaTivio/reports/2026-08/conferencia_2026-08.xlsx
+++ b/AutomaTivio/reports/2026-08/conferencia_2026-08.xlsx
@@ -424,16 +424,6030 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A1"/>
+  <dimension ref="A1:E223"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="21" customWidth="1" min="1" max="1"/>
+    <col width="45" customWidth="1" min="1" max="1"/>
+    <col width="19" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="58" customWidth="1" min="4" max="4"/>
+    <col width="58" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>(nada nesta edição)</t>
+          <t>arquivo</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>fundo</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>campo</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>antes</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>depois</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>tivio-email-fundos-credito.html</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>banks</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>rows</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>[['Fundo', '1,23%', '8,17%', '14,72%', '29,50%', '45,34%', '438,74%', True], ['CDI', '1,22%', '8,14%', '14,65%', '29,14%', '44,10%', '403,41%', False], ['Alfa', '0,02%', '0,02%', '0,07%', '0,35%', '1,24%', '35,33%', False], ['%', '101%', '100%', '100%', '101%', '103%', '109%', False]]</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>[['Fundo', '1,10%', '9,36%', '14,63%', '29,82%', '45,41%', '444,67%', True], ['CDI', '1,09%', '9,33%', '14,57%', '29,49%', '44,17%', '408,92%', False], ['Alfa', '0,01%', '0,03%', '0,06%', '0,33%', '1,24%', '35,75%', False], ['%', '101%', '100%', '100%', '101%', '103%', '109%', False]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>tivio-email-fundos-credito.html</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>banks</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>meta</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>[['Público Alvo', 'Investidores em geral'], ['Resgate', 'D+0'], ['Benchmark', 'CDI'], ['Taxa de Performance', 'Não há'], ['Taxa de Administração', '0,25% a.a.'], ['PL Médio (12M)', 'R$ 1,40 bi'], ['Aplicação Mínima', 'R$ 1.000,00']]</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>[['Público Alvo', 'Investidores em geral'], ['Resgate', 'D+0'], ['Benchmark', 'CDI'], ['Taxa de Performance', 'Não há'], ['Taxa global', '0,25% a.a.'], ['PL Médio (12M)', 'R$ 1,45 bi'], ['Aplicação Mínima', 'R$ 1.000,00']]</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>tivio-email-fundos-credito.html</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>banks</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>O Fundo TIVIO BANKS obteve retorno de 1,23% no mês (101% do CDI) e acumula 8,17% (100% do CDI) em 2026. A alocação em crédito era de 76%, integralmente concentrada em emissores do setor bancário. O carrego da carteira encontra-se em CDI+0,26%, com duration média de 1,12 ano.</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>O TIVIO BANKS apresentou rentabilidade de 1,10% no mês (101% do CDI), acumulando 9,36% no ano. A alocação em crédito era de 76%, integralmente concentrada em emissores do setor bancário. O carrego da carteira encontra-se em CDI+0,26%, com duration média de 1,12 ano.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>tivio-email-fundos-credito.html</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>institucional</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>rows</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>[['Fundo', '1,27%', '8,13%', '14,68%', '29,66%', '47,95%', '815,48%', True], ['CDI', '1,22%', '8,14%', '14,65%', '29,14%', '44,10%', '744,64%', False], ['Alfa', '0,05%', '−0,01%', '0,03%', '0,52%', '3,86%', '70,84%', False], ['%', '104%', '100%', '100%', '102%', '109%', '110%', False]]</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>[['Fundo', '1,09%', '9,31%', '14,58%', '29,93%', '47,60%', '825,45%', True], ['CDI', '1,09%', '9,33%', '14,57%', '29,49%', '44,17%', '753,88%', False], ['Alfa', '−0,01%', '−0,02%', '0,01%', '0,44%', '3,43%', '71,57%', False], ['%', '100%', '100%', '100%', '102%', '108%', '109%', False]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>tivio-email-fundos-credito.html</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>institucional</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>meta</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>[['Público Alvo', 'Investidores em geral'], ['Resgate', 'D+0'], ['Benchmark', 'CDI'], ['Taxa de Performance', 'Não há'], ['Taxa de Administração', '0,20% a.a.'], ['PL Médio (12M)', 'R$ 2,52 bi'], ['Aplicação Mínima', 'R$ 1.000,00']]</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>[['Público Alvo', 'Investidores em geral'], ['Resgate', 'D+0'], ['Benchmark', 'CDI'], ['Taxa de Performance', 'Não há'], ['Taxa global', '0,20% a.a.'], ['PL Médio (12M)', 'R$ 2,49 bi'], ['Aplicação Mínima', 'R$ 1.000,00']]</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>tivio-email-fundos-credito.html</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>institucional</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>O Fundo TIVIO INSTITUCIONAL apresentou rentabilidade de 1,27% no mês (104% do CDI), acumulando 8,13% no ano. Na parcela de corporativos, os maiores atribuidores de resultado foram Aegea e Tupy, enquanto Randon foi o maior detrator.</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>O TIVIO INSTITUCIONAL apresentou rentabilidade de 1,09% no mês (100% do CDI), acumulando 9,31% no ano. Na parcela de corporativos, os maiores atribuidores de resultado foram Aegea e Tupy, enquanto Randon foi o maior detrator.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>tivio-email-fundos-credito.html</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>inst15</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>rows</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>[['Fundo', '1,37%', '8,32%', '15,01%', '30,73%', '51,48%', '1.625,14%', True], ['CDI', '1,22%', '8,14%', '14,65%', '29,14%', '44,10%', '1.391,81%', False], ['Alfa', '0,16%', '0,17%', '0,36%', '1,58%', '7,38%', '233,33%', False], ['%', '113%', '102%', '102%', '105%', '117%', '117%', False]]</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>[['Fundo', '1,11%', '9,53%', '14,94%', '30,92%', '51,22%', '1.644,37%', True], ['CDI', '1,09%', '9,33%', '14,57%', '29,49%', '44,17%', '1.408,13%', False], ['Alfa', '0,02%', '0,20%', '0,36%', '1,43%', '7,05%', '236,24%', False], ['%', '102%', '102%', '103%', '105%', '116%', '117%', False]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>tivio-email-fundos-credito.html</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>inst15</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>meta</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>[['Público Alvo', 'Investidores em geral'], ['Resgate', 'D+0'], ['Benchmark', 'CDI'], ['Taxa de Performance', 'Não há'], ['Taxa de Administração', '0,45% a.a.'], ['PL Médio (12M)', 'R$ 141,0 mi'], ['Aplicação Mínima', 'R$ 1.000,00']]</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>[['Público Alvo', 'Investidores em geral'], ['Resgate', 'D+0'], ['Benchmark', 'CDI'], ['Taxa de Performance', '20% do que exceder 102,5% do CDI'], ['Taxa global', '0,50% a.a.'], ['PL Médio (12M)', 'R$ 146,8 mi'], ['Aplicação Mínima', 'R$ 1.000,00']]</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>tivio-email-fundos-credito.html</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>inst15</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>O TIVIO INSTITUCIONAL 15 apresentou rentabilidade de 1,37% no mês (113% do CDI), acumulando 8,32% no ano. A parcela de debêntures foi a principal fonte de resultado, com destaque para Tupy e Unidas, enquanto Hapvida foi o maior detrator.</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>O TIVIO INSTITUCIONAL 15 apresentou rentabilidade de 1,11% no mês (102% do CDI), acumulando 9,53% no ano. A parcela de debêntures foi a principal fonte de resultado, com destaque para Tupy e Unidas, enquanto Hapvida foi o maior detrator.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>tivio-email-fundos-credito.html</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>infra</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>rows</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>[['Fundo', '1,10%', '4,66%', '10,20%', '19,42%', '29,69%', '75,20%', True], ['IMA-B 5', '1,24%', '7,80%', '12,94%', '22,65%', '32,69%', '85,54%', False], ['Alfa', '−0,14%', '−3,14%', '−2,75%', '−3,24%', '−3,01%', '−10,35%', False], ['%', '89%', '60%', '79%', '86%', '91%', '88%', False]]</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>[['Fundo', '1,26%', '5,98%', '9,91%', '19,03%', '29,49%', '77,41%', True], ['IMA-B 5', '1,28%', '9,18%', '13,34%', '23,32%', '33,11%', '87,91%', False], ['Alfa', '−0,01%', '−3,20%', '−3,44%', '−4,28%', '−3,62%', '−10,50%', False], ['%', '99%', '65%', '74%', '82%', '89%', '88%', False]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>tivio-email-fundos-credito.html</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>infra</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>meta</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>[['Público Alvo', 'Investidores em geral'], ['Resgate', 'D+31'], ['Benchmark', 'IMA-B 5'], ['Taxa de Performance', 'Não há'], ['Taxa de Administração', '0,75% a.a.'], ['PL Médio (12M)', 'R$ 52,0 mi'], ['Aplicação Mínima', 'R$ 1.000,00']]</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>[['Público Alvo', 'Investidores em geral'], ['Resgate', 'D+31'], ['Benchmark', 'IMA-B 5'], ['Taxa de Performance', 'Não há'], ['Taxa global', '0,75% a.a.'], ['PL Médio (12M)', 'R$ 49,4 mi'], ['Aplicação Mínima', 'R$ 1.000,00']]</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>tivio-email-fundos-credito.html</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>infra</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>O TIVIO INFRA PLUS apresentou rentabilidade, isenta de imposto de renda, de 1,10% no mês, acumulando 4,66% no ano. A gestão manteve postura cautelosa, priorizando o encurtamento da duration. Destacam-se as debêntures de RUMO e NTS, enquanto Alloha Fibra foi a maior detratora.</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>O TIVIO INFRA PLUS apresentou rentabilidade, isenta de imposto de renda, de 1,26% no mês, acumulando 5,98% no ano. A gestão manteve postura cautelosa, priorizando o encurtamento da duration. Destacam-se as debêntures de RUMO e NTS, enquanto Alloha Fibra foi a maior detratora.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>tivio-email-fundos-credito.html</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>altlight</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>rows</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>[['Fundo', '1,23%', '8,73%', '−', '−', '−', '11,79%', True], ['CDI', '1,22%', '8,14%', '−', '−', '−', '10,19%', False], ['CDI+', '0,12%', '0,94%', '−', '−', '−', '2,05%', False], ['%', '101%', '107%', '−', '−', '−', '116%', False]]</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>[['Fundo', '0,72%', '9,51%', '−', '−', '−', '12,60%', True], ['CDI', '1,09%', '9,33%', '−', '−', '−', '11,40%', False], ['CDI+', '−4,38%', '0,25%', '−', '−', '−', '1,36%', False], ['%', '66%', '102%', '−', '−', '−', '111%', False]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>tivio-email-fundos-credito.html</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>altlight</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>meta</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>[['Público Alvo', 'Investidor qualificado'], ['Resgate', 'D+50'], ['Benchmark', 'CDI'], ['Taxa de Performance', '15% do que exceder CDI+0,65%'], ['Taxa de Administração', '1,15% a.a.'], ['PL (desde o início)', 'R$ 26,9 mi'], ['Aplicação Mínima', 'R$ 1.000,00']]</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>[['Público Alvo', 'Investidor qualificado'], ['Resgate', 'D+50'], ['Benchmark', 'CDI'], ['Taxa de Performance', 'Não há'], ['Taxa global', '0,65% a.a.'], ['PL (desde o início)', 'R$ 26,8 mi'], ['Aplicação Mínima', 'R$ 1.000,00']]</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>tivio-email-fundos-credito.html</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>altlight</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>O TIVIO ALT LIGHT apresentou rentabilidade de 1,23% no mês (101% do CDI), acumulando 8,73% no ano e 11,79% desde o início (116% do CDI). A parcela de debêntures foi a principal contribuidora, seguida pela parcela de crédito estruturado.</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>O TIVIO ALT LIGHT rendeu 0,72% no mês (66% do CDI), acumulando 9,51% no ano e 12,60% desde o início (CDI+1,36% ao ano). A parcela de debêntures foi a principal contribuidora, seguida pela parcela de crédito estruturado.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>tivio-email-fundos-credito.html</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>alt180</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>rows</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>[['Fundo', '1,45%', '9,76%', '18,56%', '−', '−', '31,44%', True], ['CDI', '1,22%', '8,14%', '14,65%', '−', '−', '24,08%', False], ['CDI+', '2,56%', '2,61%', '3,42%', '−', '−', '3,66%', False], ['%', '119%', '120%', '127%', '−', '−', '131%', False]]</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>[['Fundo', '1,30%', '11,19%', '18,11%', '−', '−', '33,14%', True], ['CDI', '1,09%', '9,33%', '14,57%', '−', '−', '25,43%', False], ['CDI+', '2,48%', '2,59%', '3,10%', '−', '−', '3,60%', False], ['%', '119%', '120%', '124%', '−', '−', '130%', False]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>tivio-email-fundos-credito.html</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>alt180</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>meta</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>[['Público Alvo', 'Investidores qualificados, Multi Family e Family Offices'], ['Resgate', 'D+180'], ['Benchmark', 'CDI'], ['Taxa de Performance', '20% do que exceder o CDI'], ['Taxa de Administração', '1,15% a.a.'], ['PL Médio (12M)', 'R$ 84,8 mi'], ['Aplicação Mínima', 'R$ 1.000,00']]</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>[['Público Alvo', 'Investidores qualificados, Multi Family e Family Offices'], ['Resgate', 'D+180'], ['Benchmark', 'CDI'], ['Taxa de Performance', '20% do que exceder o CDI'], ['Taxa global', '1,15% a.a.'], ['PL Médio (12M)', 'R$ 94,5 mi'], ['Aplicação Mínima', 'R$ 1.000,00']]</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>tivio-email-fundos-credito.html</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>alt180</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>O TIVIO ALT 180 rendeu 1,45% no mês (119% do CDI), acumulando 9,76% no ano e 31,44% desde o início (CDI+3,66% ao ano). Em julho aumentamos a exposição a FIDCs de Consignado Público, com elevada pulverização e baixa inadimplência.</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>O TIVIO ALT 180 rendeu 1,30% no mês (119% do CDI), acumulando 11,19% no ano e 33,14% desde o início (CDI+3,60% ao ano). Em julho aumentamos a exposição a FIDCs de Consignado Público, com elevada pulverização e baixa inadimplência.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>tivio-email-fundos-credito.html</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>alt90</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>rows</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>[['Fundo', '1,36%', '9,06%', '16,72%', '−', '−', '19,79%', True], ['CDI', '1,22%', '8,14%', '14,65%', '−', '−', '17,13%', False], ['CDI+', '1,59%', '1,48%', '1,81%', '−', '−', '1,97%', False], ['%', '112%', '111%', '114%', '−', '−', '115%', False]]</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>[['Fundo', '1,22%', '10,40%', '16,49%', '−', '−', '21,25%', True], ['CDI', '1,09%', '9,33%', '14,57%', '−', '−', '18,41%', False], ['CDI+', '1,55%', '1,49%', '1,68%', '−', '−', '1,94%', False], ['%', '112%', '111%', '113%', '−', '−', '115%', False]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>tivio-email-fundos-credito.html</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>alt90</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>meta</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>[['Público Alvo', 'Investidor qualificado'], ['Resgate', 'D+90'], ['Benchmark', 'CDI'], ['Taxa de Performance', '10% do que exceder o CDI'], ['Taxa de Administração', '1,25% a.a.'], ['PL Médio (12M)', 'R$ 14,3 mi'], ['Aplicação Mínima', 'R$ 1.000,00']]</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>[['Público Alvo', 'Investidor qualificado'], ['Resgate', 'D+90'], ['Benchmark', 'CDI'], ['Taxa de Performance', '10% do que exceder o CDI'], ['Taxa global', '2,43% a.a.'], ['PL Médio (12M)', 'R$ 15,7 mi'], ['Aplicação Mínima', 'R$ 1.000,00']]</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>tivio-email-fundos-credito.html</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>alt90</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>O TIVIO ALT 90 rendeu 1,36% no mês (112% do CDI), acumulando 9,06% no ano e 19,79% desde o início (CDI+1,97% ao ano). A estratégia segue concentrada em FIDCs de cotas sênior, buscando retorno superior ao CDI com baixa volatilidade.</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>O TIVIO ALT 90 rendeu 1,22% no mês (112% do CDI), acumulando 10,40% no ano e 21,25% desde o início (CDI+1,94% ao ano). A estratégia segue concentrada em FIDCs de cotas sênior, buscando retorno superior ao CDI com baixa volatilidade.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>tivio-email-fundos-credito.html</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>banks</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>HIST</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>até 2026-07</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>até 2026-08 (209 meses)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>tivio-email-fundos-credito.html</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>institucional</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>HIST</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>até 2026-07</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>até 2026-08 (256 meses)</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>tivio-email-fundos-credito.html</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>inst15</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>HIST</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>até 2026-07</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>até 2026-08 (295 meses)</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>tivio-email-fundos-credito.html</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>infra</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>HIST</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>até 2026-07</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>até 2026-08 (64 meses)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>tivio-email-fundos-credito.html</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>altlight</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>HIST</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>até 2026-07</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>até 2026-08 (10 meses)</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>tivio-email-fundos-credito.html</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>alt180</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>HIST</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>até 2026-07</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>até 2026-08 (21 meses)</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>tivio-email-fundos-credito.html</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>alt90</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>HIST</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>até 2026-07</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>até 2026-08 (15 meses)</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>tivio-email-fundos-credito.html</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>data</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>31/07/2026</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>31/08/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>tivio-email-fundos-credito.html</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>data</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Julho de 2026</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Agosto de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>tivio-email-fundos-credito.html</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>data</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>julho de 2026</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>agosto de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>tivio-email-fundos-credito.html</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>libs de exportação</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>CDN</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>4 referências → vendor/ local (CDN como reserva)</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>tivio-post-credito-estruturado.html</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>alt180</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>b1val</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>R$ 148.155.859,36</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>R$ 151.939.343,55</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>tivio-post-credito-estruturado.html</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>alt180</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>b2val</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>R$ 84.791.205,56</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>R$ 94.506.904,26</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>tivio-post-credito-estruturado.html</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>alt180</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>v1</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>127%</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>124%</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>tivio-post-credito-estruturado.html</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>alt180</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>alloc</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>[{'n': 'FIDCs Cotas Sênior', 'p': 49.6}, {'n': 'FIDCs Cotas Mezanino', 'p': 27.5}, {'n': 'Liquidez', 'p': 9.3}, {'n': 'Crédito Estruturado', 'p': 5.5}, {'n': 'Crédito Privado', 'p': 3.5}, {'n': 'Precatório', 'p': 2.8}, {'n': 'Fiagro', 'p': 2.0}]</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>[{'n': 'FIDCs Cotas Sênior', 'p': 46.9}, {'n': 'FIDCs Cotas Mezanino', 'p': 27.0}, {'n': 'Bancário', 'p': 6.1}, {'n': 'Fiagro', 'p': 5.5}, {'n': 'Liquidez', 'p': 5.3}, {'n': 'Crédito Privado', 'p': 3.4}, {'n': 'Precatório', 'p': 2.7}, {'n': 'Crédito Estruturado', 'p': 2.6}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>tivio-post-credito-estruturado.html</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>alt180</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>taxas</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Taxa de administração e gestão: 1,15% a.a. Taxa de performance: 20% do que exceder do CDI. Resgate: D+180.</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Taxa global: 1,15% a.a. Taxa de performance: 20% do que exceder do CDI. Resgate: D+180.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>tivio-post-credito-estruturado.html</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>alt90</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>b1val</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>R$ 19.936.394,95</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>R$ 19.959.710,82</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>tivio-post-credito-estruturado.html</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>alt90</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>b2val</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>R$ 14.275.935,66</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>R$ 15.653.770,20</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>tivio-post-credito-estruturado.html</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>alt90</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>v1</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>114%</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>113%</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>tivio-post-credito-estruturado.html</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>alt90</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>alloc</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>[{'n': 'FIDCs Cotas Sênior', 'p': 81.3}, {'n': 'Liquidez', 'p': 11.9}, {'n': 'Crédito Privado', 'p': 3.6}, {'n': 'Crédito Estruturado', 'p': 2.8}, {'n': 'FIDC Mezanino', 'p': 0.6}]</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>[{'n': 'FIDCs Cotas Sênior', 'p': 82.9}, {'n': 'Bancário', 'p': 8.3}, {'n': 'Crédito Privado', 'p': 3.6}, {'n': 'Fiagro', 'p': 2.9}, {'n': 'Liquidez', 'p': 1.9}, {'n': 'FIDCs Cotas Mezanino', 'p': 0.6}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>tivio-post-credito-estruturado.html</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>alt90</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>taxas</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Taxa de administração e gestão: 1,25% a.a. Taxa de performance: 10% do que exceder do CDI. Resgate: D+90.</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>Taxa global: 2,43% a.a. Taxa de performance: 10% do que exceder do CDI. Resgate: D+90.</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>tivio-post-credito-estruturado.html</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>altlight</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>b1val</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>R$ 26.861.672,93</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>R$ 26.829.258,71</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>tivio-post-credito-estruturado.html</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>altlight</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>b2val</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>R$ 17.309.791,01</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>R$ 18.304.046,83</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>tivio-post-credito-estruturado.html</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>altlight</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>v1</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>116%</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>111%</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>tivio-post-credito-estruturado.html</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>altlight</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>v2</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>107%</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>102%</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>tivio-post-credito-estruturado.html</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>altlight</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>v3</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>101%</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>66%</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>tivio-post-credito-estruturado.html</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>altlight</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>alloc</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>[{'n': 'Bancário', 'p': 40.8}, {'n': 'Crédito Privado', 'p': 25.6}, {'n': 'FIDCs Cotas Sênior', 'p': 24.0}, {'n': 'Liquidez', 'p': 7.8}, {'n': 'FIP', 'p': 1.9}]</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>[{'n': 'Bancário', 'p': 40.7}, {'n': 'Crédito Privado', 'p': 25.8}, {'n': 'FIDCs Cotas Sênior', 'p': 23.5}, {'n': 'Liquidez', 'p': 7.8}, {'n': 'Ações', 'p': 1.9}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>tivio-post-credito-estruturado.html</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>altlight</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>taxas</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>Taxa de administração e gestão: 1,15% a.a. Taxa de performance: 15% do retorno que exceder CDI+0,65%.</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>Taxa global: 0,65% a.a. Taxa de performance: não há.</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>tivio-post-credito-estruturado.html</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>data</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>31/07/2026</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>31/08/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>tivio-post-credito-estruturado.html</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>data</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>Julho de 2026</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>Agosto de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>tivio-post-credito-estruturado.html</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>data</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>julho de 2026</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>agosto de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>tivio-post-credito-estruturado.html</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>data</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>JULHO DE 2026</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>AGOSTO DE 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>tivio-post-credito-estruturado.html</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>data</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>Julho 2026</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>Agosto 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>tivio-post-credito-estruturado.html</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>data</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>-jul26</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>-ago26</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>tivio-post-credito-estruturado.html</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>data</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>const ATUAL=6;</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>const ATUAL=7;</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>tivio-post-credito-estruturado.html</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>libs de exportação</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>CDN</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>4 referências → vendor/ local (CDN como reserva)</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>tivio-post-credito-privado.html</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>banks</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>pl</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>R$ 1.698.520.740,05</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>R$ 1.793.381.077,96</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>tivio-post-credito-privado.html</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>banks</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>plm</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>R$ 1.397.203.402,03</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>R$ 1.449.683.179,97</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>tivio-post-credito-privado.html</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>banks</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>alloc</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>{'total': '76', 'top': [{'p': '76,5%', 'n': 'financeiro'}, {'p': '23,7%', 'n': 'caixa'}]}</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>{'total': '76', 'top': [{'p': '76%', 'n': 'financeiro'}]}</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>tivio-post-credito-privado.html</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>banks</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>val</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>0,26</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>0,25</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>tivio-post-credito-privado.html</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>banks</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>val</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>1,12</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>1,05</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>tivio-post-credito-privado.html</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>banks</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>taxas</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>Taxa de administração: 0,25% a.a. Taxa de performance: não há. Aplicação: D+0 · Resgate: D+0.</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>Taxa global: 0,25% a.a. Taxa de performance: não há. Aplicação: D+0 · Resgate: D+0.</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>tivio-post-credito-privado.html</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>institucional</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>v3</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>104%</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>tivio-post-credito-privado.html</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>institucional</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>pl</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>R$ 1.983.487.947,49</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>R$ 1.815.644.128,24</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>tivio-post-credito-privado.html</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>institucional</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>plm</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>R$ 2.522.009.705,73</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>R$ 2.491.331.200,61</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>tivio-post-credito-privado.html</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>institucional</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>alloc</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>{'total': '69', 'top': [{'p': '52%', 'n': 'financeiro'}, {'p': '4%', 'n': 'energia elétrica'}, {'p': '2%', 'n': 'transporte e logística'}]}</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>{'total': '61', 'top': [{'p': '45%', 'n': 'financeiro'}, {'p': '5%', 'n': 'energia elétrica'}, {'p': '2%', 'n': 'FIDC'}]}</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>tivio-post-credito-privado.html</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>institucional</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>val</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>0,44</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>0,39</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>tivio-post-credito-privado.html</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>institucional</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>val</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>1,20</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>1,28</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>tivio-post-credito-privado.html</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>institucional</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>taxas</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>Taxa de administração: 0,20% a.a. Taxa de performance: não há. Aplicação: D+0 · Resgate: D+0.</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>Taxa global: 0,20% a.a. Taxa de performance: não há. Aplicação: D+0 · Resgate: D+0.</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>tivio-post-credito-privado.html</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>inst15</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>v1</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>102%</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>103%</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>tivio-post-credito-privado.html</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>inst15</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>v3</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>113%</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>102%</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>tivio-post-credito-privado.html</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>inst15</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>pl</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>R$ 161.593.743,98</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>R$ 156.046.891,63</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>tivio-post-credito-privado.html</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>inst15</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>plm</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>R$ 140.997.685,81</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>R$ 146.843.921,67</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>tivio-post-credito-privado.html</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>inst15</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>alloc</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>{'total': '74', 'top': [{'p': '29%', 'n': 'financeiro'}, {'p': '13%', 'n': 'FIDC'}, {'p': '7%', 'n': 'energia elétrica'}]}</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>{'total': '73', 'top': [{'p': '28%', 'n': 'financeiro'}, {'p': '13%', 'n': 'FIDC'}, {'p': '7%', 'n': 'energia elétrica'}]}</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>tivio-post-credito-privado.html</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>inst15</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>val</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>1,00</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>0,95</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>tivio-post-credito-privado.html</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>inst15</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>val</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>1,97</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>1,80</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>tivio-post-credito-privado.html</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>inst15</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>anos</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>tivio-post-credito-privado.html</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>inst15</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>taxas</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>Taxa de administração: 0,45% a.a. Taxa de performance: não há. Aplicação: D+0 · Resgate: D+0.</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>Taxa global: 0,50% a.a. Taxa de performance: 20% do que exceder 102,5% do CDI. Aplicação: D+0 · Resgate: D+0.</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>tivio-post-credito-privado.html</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>inst30</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>v3</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>113%</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>102%</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>tivio-post-credito-privado.html</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>inst30</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>pl</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>R$ 143.232.764,20</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>R$ 126.168.780,56</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>tivio-post-credito-privado.html</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>inst30</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>plm</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>R$ 155.004.649,74</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>R$ 158.893.390,74</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>tivio-post-credito-privado.html</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>inst30</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>alloc</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>{'total': '84', 'top': [{'p': '33%', 'n': 'financeiro'}, {'p': '15%', 'n': 'FIDC'}, {'p': '8%', 'n': 'energia elétrica'}]}</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>{'total': '80', 'top': [{'p': '31%', 'n': 'financeiro'}, {'p': '14%', 'n': 'FIDC'}, {'p': '8%', 'n': 'energia elétrica'}]}</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>tivio-post-credito-privado.html</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>inst30</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>val</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>1,04</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>tivio-post-credito-privado.html</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>inst30</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>val</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>1,86</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>tivio-post-credito-privado.html</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>inst30</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>anos</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>tivio-post-credito-privado.html</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>inst30</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>taxas</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>Taxa de administração: 0,63% a.a. Taxa de performance: 20% do que exceder o CDI. Resgate: D+30.</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>Taxa global: 0,625% a.a. Taxa de performance: 20% do que exceder 100% do CDI. Resgate: D+30.</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>tivio-post-credito-privado.html</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>infraplus</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>v1</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>12,94%</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>9,91%</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>tivio-post-credito-privado.html</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>infraplus</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>a1</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>*Alfa: -2,75%</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>*Alfa: −3,44%</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>tivio-post-credito-privado.html</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>infraplus</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>v2</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>7,80%</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>5,98%</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>tivio-post-credito-privado.html</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>infraplus</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>a2</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>*Alfa: -3,14%</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>*Alfa: −3,20%</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>tivio-post-credito-privado.html</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>infraplus</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>v3</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>1,24%</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>1,26%</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>tivio-post-credito-privado.html</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>infraplus</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>a3</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>*Alfa: -0,14%</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>*Alfa: −0,01%</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>tivio-post-credito-privado.html</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>infraplus</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>pl</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>R$ 42.983.282,75</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>R$ 42.694.019,75</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>tivio-post-credito-privado.html</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>infraplus</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>plm</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>R$ 52.049.593,91</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>R$ 49.421.174,50</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>tivio-post-credito-privado.html</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>infraplus</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>alloc</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>{'total': '95', 'top': [{'p': '55%', 'n': 'energia elétrica'}, {'p': '15%', 'n': 'transporte e logística'}, {'p': '7%', 'n': 'saneamento'}]}</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>{'total': '97', 'top': [{'p': '56%', 'n': 'energia elétrica'}, {'p': '15%', 'n': 'transporte e logística'}, {'p': '7%', 'n': 'saneamento'}]}</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>tivio-post-credito-privado.html</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>infraplus</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>val</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>8,63</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>8,23</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>tivio-post-credito-privado.html</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>infraplus</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>val</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>4,00</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>3,98</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>tivio-post-credito-privado.html</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>infraplus</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>taxas</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>Taxa de administração: 0,75% a.a. Taxa de performance: não há. Resgate: D+31. Rentabilidade isenta de IR para pessoa física.</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>Taxa global: 0,75% a.a. Taxa de performance: não há. Resgate: D+31. Rentabilidade isenta de IR para pessoa física.</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>tivio-post-credito-privado.html</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>data</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>31/07/2026</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>31/08/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>tivio-post-credito-privado.html</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>data</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>Julho de 2026</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>Agosto de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>tivio-post-credito-privado.html</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>data</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>julho de 2026</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>agosto de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>tivio-post-credito-privado.html</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>data</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>JULHO DE 2026</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>AGOSTO DE 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>tivio-post-credito-privado.html</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>data</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>Julho 2026</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>Agosto 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>tivio-post-credito-privado.html</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>data</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>-jul26</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>-ago26</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>tivio-post-credito-privado.html</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>data</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>const ATUAL=6;</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>const ATUAL=7;</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>tivio-post-credito-privado.html</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>libs de exportação</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>CDN</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>4 referências → vendor/ local (CDN como reserva)</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>tivio-post-investment-solutions.html</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>topgestor</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>v1</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>103%</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>91%</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>tivio-post-investment-solutions.html</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>topgestor</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>v2</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>101%</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>tivio-post-investment-solutions.html</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>topgestor</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>v3</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>101%</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>tivio-post-investment-solutions.html</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>topgestor</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>plm</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>R$ 352,4 mi</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>R$ 350,1 mi</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>tivio-post-investment-solutions.html</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>topgestorhy</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>v1</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>104%</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>tivio-post-investment-solutions.html</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>topgestorhy</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>v2</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>106%</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>105%</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>tivio-post-investment-solutions.html</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>topgestorhy</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>v3</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>109%</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>107%</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>tivio-post-investment-solutions.html</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>topgestorhy</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>plm</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>R$ 33,2 mi</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>R$ 35,7 mi</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>tivio-post-investment-solutions.html</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>topgestorativo</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>adm</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>0,00% a.a. (vértice tx zero)</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>0,15% a.a.</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>tivio-post-investment-solutions.html</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>topgestorativo</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>v1</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>93%</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>99%</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>tivio-post-investment-solutions.html</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>topgestorativo</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>v2</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>86%</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>87%</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>tivio-post-investment-solutions.html</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>topgestorativo</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>plm</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>R$ 374,3 mi</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>R$ 353,7 mi</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>tivio-post-investment-solutions.html</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>topgestorlongonly</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>v1</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>43%</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>370%</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>tivio-post-investment-solutions.html</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>topgestorlongonly</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>v2</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>44%</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>33%</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>tivio-post-investment-solutions.html</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>topgestorlongonly</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>v3</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>70%</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>53%</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>tivio-post-investment-solutions.html</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>topgestorlongonly</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>plm</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>R$ 95,0 mi</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>R$ 91,4 mi</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>tivio-post-investment-solutions.html</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>topmanagerglobal</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>v1</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>2,13%</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>4,88%</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>tivio-post-investment-solutions.html</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>topmanagerglobal</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>a1</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>*Alfa: −3,03%</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>*Alfa: 0,21%</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>tivio-post-investment-solutions.html</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>topmanagerglobal</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>v2</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>−5,35%</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>7,12%</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>tivio-post-investment-solutions.html</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>topmanagerglobal</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>a2</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>*Alfa: −1,59%</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>*Alfa: 0,45%</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>tivio-post-investment-solutions.html</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>topmanagerglobal</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>v3</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>7,66%</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>14,01%</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>tivio-post-investment-solutions.html</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>topmanagerglobal</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>a3</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>*Alfa: −6,22%</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>*Alfa: −1,01%</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>tivio-post-investment-solutions.html</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>topmanagerglobal</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>plm</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>R$ 100,8 mi</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>R$ 77,4 mi</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>tivio-post-investment-solutions.html</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>ativorf</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>perf</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>20% do que exceder o CDI</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>20% do que exceder 100% do CDI</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>tivio-post-investment-solutions.html</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>ativorf</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>v1</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>73%</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>89%</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>tivio-post-investment-solutions.html</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>ativorf</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>v2</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>74%</t>
+        </is>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>76%</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>tivio-post-investment-solutions.html</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>ativorf</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>v3</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>81%</t>
+        </is>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>82%</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>tivio-post-investment-solutions.html</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>ativorf</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>plm</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>R$ 102,7 mi</t>
+        </is>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>R$ 100,4 mi</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>tivio-post-investment-solutions.html</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>prevlowvol</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>v1</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>92%</t>
+        </is>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>95%</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>tivio-post-investment-solutions.html</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>prevlowvol</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>plm</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>R$ 662,8 mi</t>
+        </is>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>R$ 650,1 mi</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>tivio-post-investment-solutions.html</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>data</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>31/07/2026</t>
+        </is>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>31/08/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>tivio-post-investment-solutions.html</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>data</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>Julho de 2026</t>
+        </is>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>Agosto de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>tivio-post-investment-solutions.html</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>data</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>julho de 2026</t>
+        </is>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>agosto de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>tivio-post-investment-solutions.html</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>data</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>JULHO DE 2026</t>
+        </is>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>AGOSTO DE 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>tivio-post-investment-solutions.html</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>data</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>Julho 2026</t>
+        </is>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>Agosto 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>tivio-post-investment-solutions.html</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>data</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>-jul26</t>
+        </is>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>-ago26</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>tivio-post-investment-solutions.html</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>data</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>const ATUAL=6;</t>
+        </is>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>const ATUAL=7;</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>tivio-post-investment-solutions.html</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>libs de exportação</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>CDN</t>
+        </is>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>4 referências → vendor/ local (CDN como reserva)</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>tivio-relatorio-gestao-credito-privado.html</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>mercado</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>MARKET</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>[['Total', '446.217', '100,0%', '1,14%', '1,17%', '-0,03%', '2,86', True], ['Energia elétrica', '102.982', '23,11%', '0,75%', '0,76%', '-0,02%', '2,78', False], ['Assistência médica', '45.853', '10,29%', '1,45%', '1,48%', '-0,04%', '3,40', False], ['Locação de veículos', '43.937', '9,86%', '1,72%', '1,71%', '0,02%', '2,51', False], ['Saneamento', '40.735', '9,14%', '1,43%', '1,44%', '-0,01%', '2,87', False], ['Petróleo e gás', '33.732', '7,57%', '0,91%', '0,95%', '-0,04%', '3,01', False], ['Transporte e logística', '27.250', '6,11%', '1,41%', '1,54%', '-0,12%', '2,78', False], ['Comércio atacadista e varejista', '24.639', '5,53%', '1,33%', '1,39%', '-0,06%', '2,65', False], ['Financeiro', '23.379', '5,25%', '0,52%', '0,54%', '-0,02%', '2,38', False], ['Indústria e comércio', '20.251', '4,54%', '1,15%', '1,20%', '-0,04%', '2,82', False], ['TI e telecomunicações', '17.577', '3,94%', '1,11%', '1,12%', '-0,01%', '2,46', False], ['Bioenergia', '11.334', '2,54%', '1,74%', '1,80%', '-0,06%', '3,08', False], ['Metalurgia e siderurgia', '9.560', '2,15%', '1,25%', '1,15%', '0,10%', '3,10', False], ['Educação', '7.933', '1,78%', '1,02%', '1,06%', '-0,04%', '2,39', False], ['Outros serviços', '7.003', '1,57%', '1,10%', '1,12%', '-0,02%', '2,89', False], ['Empreendimentos e participações', '6.693', '1,50%', '1,23%', '1,24%', '-0,01%', '3,44', False], ['Serviços imobiliários', '6.353', '1,43%', '0,64%', '0,65%', '-0,01%', '3,62', False], ['Papel e Celulose', '5.247', '1,18%', '0,58%', '0,60%', '-0,03%', '4,73', False], ['Materiais de construção e agregados', '4.144', '0,93%', '1,04%', '1,04%', '0,00%', '3,64', False], ['Química e petroquímica', '2.554', '0,57%', '1,11%', '1,14%', '-0,03%', '3,75', False], ['Alimentos e bebidas', '1.727', '0,39%', '1,25%', '1,28%', '-0,03%', '1,37', False], ['Têxtil e calçados', '1.528', '0,34%', '1,25%', '1,25%', '0,00%', '2,90', False], ['Mineração', '1.072', '0,24%', '0,83%', '0,86%', '-0,03%', '2,51', False], ['Construção civil', '166', '0,04%', '1,66%', '1,82%', '-0,16%', '0,68', False]]</t>
+        </is>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>[['Setor', 'Volume (R$ MM)', '%', 'Spread Atual', 'Spread mês anterior', 'Variação', 'Duration', False], ['Total', '(a linha Total vem primeiro)', '', '', '', '', '', True]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>tivio-relatorio-gestao-credito-privado.html</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>banks</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>pl</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>R$ 1.698.520.740,05</t>
+        </is>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>R$ 1.793.381.077,96</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>tivio-relatorio-gestao-credito-privado.html</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>banks</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>plm</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>R$ 1.397.203.402,03</t>
+        </is>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>R$ 1.449.683.179,97</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>tivio-relatorio-gestao-credito-privado.html</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>banks</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>perfrows</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>{'pct': ['101%', '100%', '100%']}</t>
+        </is>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>{'fundo': ['1,10%', '9,36%', '14,63%', '29,82%', '45,41%', '444,67%'], 'bench': ['1,09%', '9,33%', '14,57%', '29,49%', '44,17%', '408,92%'], 'pct': ['101%', '100%', '100%', '101%', '103%', '109%']}</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>tivio-relatorio-gestao-credito-privado.html</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>banks</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>emissores</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>[['ITAÚ UNIBANCO', '3,42%', 100], ['BRADESCO', '3,18%', 93], ['SANTANDER', '2,86%', 84], ['BANCO DO BRASIL', '2,54%', 74], ['BTG PACTUAL', '2,21%', 65]]</t>
+        </is>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>[['BV', '6,36%', 100], ['XP', '6,04%', 95], ['BTG', '5,97%', 94], ['ABC', '5,92%', 93], ['NUBANK', '5,57%', 88]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>tivio-relatorio-gestao-credito-privado.html</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>banks</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>setores</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>[['Financeiro', '76,5%'], ['Caixa', '23,5%']]</t>
+        </is>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>[['Financeiro', '75,7%'], ['Caixa', '24,2%']]</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>tivio-relatorio-gestao-credito-privado.html</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>banks</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>rating</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>[['AAA', '46,2%', 100], ['AA+', '24,8%', 54], ['AA', '14,1%', 31], ['AA-', '9,4%', 20], ['A+', '3,9%', 8], ['A', '1,6%', 3]]</t>
+        </is>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>[['AAA', '50,8%', 100], ['AA+', '16,3%', 32], ['AA', '2,0%', 4], ['A+', '1,9%', 4], ['A', '3,0%', 6]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>tivio-relatorio-gestao-credito-privado.html</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>banks</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>val</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>0,26%</t>
+        </is>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>0,25%</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>tivio-relatorio-gestao-credito-privado.html</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>banks</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>val</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>1,12</t>
+        </is>
+      </c>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>1,05</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>tivio-relatorio-gestao-credito-privado.html</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>banks</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>hist12</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>{'b': 'CDI', 'l': ['2025-08', '2025-09', '2025-10', '2025-11', '2025-12', '2026-01', '2026-02', '2026-03', '2026-04', '2026-05', '2026-06', '2026-07', '2026-08'], 'f': [0.0, 1.23, 2.53, 3.62, 4.88, 6.11, 7.18, 8.48, 9.64, 10.82, 12.07, 13.45, 14.7], 'c': [0.0, 1.22, 2.51, 3.59, 4.85, 6.07, 7.13, 8.43, 9.61, 10.79, 12.03, 13.39, 14.63]}</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>tivio-relatorio-gestao-credito-privado.html</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>banks</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>histEnd</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>[12.0, 12.0, 'CDI']</t>
+        </is>
+      </c>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>[14.7, 14.63, 'CDI']</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>tivio-relatorio-gestao-credito-privado.html</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>banks</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>comentario</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>['No mês, o mercado de crédito privado high grade manteve o movimento de fechamento gradual de spreads, com fluxo comprador consistente no secundário e oferta primária ainda concentrada em emissores de primeira linha.', 'A liquidez permaneceu saudável ao longo da curva, com boa demanda por papéis bancários e por debêntures de empresas de energia, saneamento e infraestrutura, setores de maior peso na carteira.', 'Do ponto de vista da gestão, seguimos priorizando emissores de baixo risco de crédito e o controle da duration, mantendo carrego atrativo sobre o CDI sem elevar de forma relevante a volatilidade da cota.', 'O BANKS apresentou rentabilidade de &lt;b&gt;1,01%&lt;/b&gt; no mês (&lt;b&gt;101% do CDI&lt;/b&gt;), acumulando &lt;b&gt;8,17%&lt;/b&gt; no ano. Os principais atribuidores de resultado foram as debêntures corporativas e a parcela bancária da carteira.']</t>
+        </is>
+      </c>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t>['O Fundo Tivio Banks obteve retorno de 1,10% (101% do CDI) no mês e acumula 9,36% (100% do CDI) em 2026. A alocação em crédito era de 75%, integralmente concentrada em emissores do setor bancário. O carrego da carteira encontra-se em CDI +0,25%, com duration média de 1,05 ano.', 'Em agosto, o mercado de crédito foi marcado por um ambiente de menor liquidez nas negociações do mercado secundário e por uma leve reabertura dos spreads de crédito. Após meses consecutivos de compressão dos prêmios de risco, observou-se um movimento mais cauteloso por parte dos investidores, com os spreads médios dos títulos corporativos indexados ao CDI avançando aproximadamente 0,03%, passando de CDI + 1,19% para CDI + 1,22% ao ano. Apesar desse ajuste, os níveis de prêmio permaneceram próximos das mínimas históricas observadas ao longo do ciclo recente.', 'No mercado secundário, a redução do volume negociado contribuiu para uma formação de preços mais seletiva, especialmente em ativos corporativos com menor liquidez. Ainda assim, o comportamento dos investidores permaneceu construtivo, sustentado por um ambiente técnico favorável e pela continuidade da elevada demanda por ativos de crédito.', 'Já no mercado primário, as emissões bancárias seguiram registrando forte demanda por parte dos investidores. As ofertas de Letras Financeiras Seniores distribuídas ao longo do mês apresentaram níveis elevados de subscrição, com demanda que, em diversos casos, superou três vezes o volume ofertado. Esse forte apetite permitiu que as operações fossem precificadas com taxas inferiores aos limites inicialmente indicados pelos emissores, evidenciando a elevada disponibilidade de recursos para alocação na indústria de crédito.', 'Em relação aos fluxos, os fundos com alocação mínima de 15% em crédito e ao menos 1% em debêntures apresentaram captação líquida próxima de R$ 8 bilhões em agosto, resultado significativamente superior ao observado no mês anterior. O volume reforça a percepção de que os investidores seguem direcionando recursos para estratégias de crédito, impulsionados pelo elevado nível de carrego proporcionado pelos ativos indexados ao CDI e pela busca por alternativas de investimento com perfil de risco-retorno atrativo.', 'Nesse contexto, a combinação entre fluxos positivos para a indústria, vencimentos e amortizações recorrentes das carteiras, além da limitada oferta de novos ativos corporativos, continuou sustentando a demanda por crédito privado. Ainda que agosto tenha apresentado uma leve reabertura dos spreads médios de mercado, a dinâmica técnica permanece favorável e os prêmios seguem negociando em patamares historicamente reduzidos.', 'Por fim, sob a ótica da gestão, seguimos acompanhando de forma criteriosa a evolução dos fundamentos dos emissores presentes nas carteiras, com atenção especial aos indicadores operacionais, à geração de caixa e à manutenção de estruturas de capital adequadas. Em um ambiente em que os spreads permanecem comprimidos em termos históricos, mantemos disciplina na alocação dos recursos, priorizando operações que apresentem adequada relação entre risco e retorno e preservando flexibilidade para captura de oportunidades que possam surgir em eventuais períodos de maior volatilidade do mercado.']</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>tivio-relatorio-gestao-credito-privado.html</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>institucional</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>pl</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>R$ 1.983.487.947,49</t>
+        </is>
+      </c>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t>R$ 1.815.644.128,24</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>tivio-relatorio-gestao-credito-privado.html</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>institucional</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>plm</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>R$ 2.522.009.705,73</t>
+        </is>
+      </c>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t>R$ 2.491.331.200,61</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>tivio-relatorio-gestao-credito-privado.html</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>institucional</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>perfrows</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>{'pct': ['104%', '100%', '100%']}</t>
+        </is>
+      </c>
+      <c r="E161" t="inlineStr">
+        <is>
+          <t>{'fundo': ['1,09%', '9,31%', '14,58%', '29,93%', '47,60%', '825,45%'], 'bench': ['1,09%', '9,33%', '14,57%', '29,49%', '44,17%', '753,88%'], 'pct': ['100%', '100%', '100%', '102%', '108%', '109%']}</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>tivio-relatorio-gestao-credito-privado.html</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>institucional</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>emissores</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>[['AEGEA', '2,64%', 100], ['TUPY', '2,31%', 88], ['VALE', '2,05%', 78], ['PETROBRAS', '1,86%', 70], ['RANDON', '1,52%', 58]]</t>
+        </is>
+      </c>
+      <c r="E162" t="inlineStr">
+        <is>
+          <t>[['BTG', '3,45%', 100], ['BB', '3,44%', 100], ['SANTANDER', '3,06%', 89], ['SAFRA', '3,02%', 88], ['BRADESCO', '2,89%', 84]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>tivio-relatorio-gestao-credito-privado.html</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>institucional</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>setores</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>[['Financeiro', '52%'], ['Energia Elétrica', '4%'], ['Transporte e Logística', '2%'], ['Saneamento', '2%'], ['Caixa', '31%']]</t>
+        </is>
+      </c>
+      <c r="E163" t="inlineStr">
+        <is>
+          <t>[['Financeiro', '44,6%'], ['Energia Elétrica', '4,5%'], ['FIDC', '2,1%'], ['Transporte e Logística', '2,1%'], ['Saneamento', '2,0%'], ['Caixa', '38,7%']]</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>tivio-relatorio-gestao-credito-privado.html</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>institucional</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>rating</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>[['AAA', '46,2%', 100], ['AA+', '24,8%', 54], ['AA', '14,1%', 31], ['AA-', '9,4%', 20], ['A+', '3,9%', 8], ['A', '1,6%', 3]]</t>
+        </is>
+      </c>
+      <c r="E164" t="inlineStr">
+        <is>
+          <t>[['AAA', '39,6%', 100], ['AA+', '10,5%', 27], ['AA', '2,4%', 6], ['AA-', '2,7%', 7], ['A+', '1,2%', 3], ['A', '3,3%', 8]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>tivio-relatorio-gestao-credito-privado.html</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>institucional</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>val</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>0,44%</t>
+        </is>
+      </c>
+      <c r="E165" t="inlineStr">
+        <is>
+          <t>0,39%</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>tivio-relatorio-gestao-credito-privado.html</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>institucional</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>val</t>
+        </is>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>1,20</t>
+        </is>
+      </c>
+      <c r="E166" t="inlineStr">
+        <is>
+          <t>1,28</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>tivio-relatorio-gestao-credito-privado.html</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>institucional</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>hist12</t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="E167" t="inlineStr">
+        <is>
+          <t>{'b': 'CDI', 'l': ['2025-08', '2025-09', '2025-10', '2025-11', '2025-12', '2026-01', '2026-02', '2026-03', '2026-04', '2026-05', '2026-06', '2026-07', '2026-08'], 'f': [0.0, 1.25, 2.52, 3.59, 4.88, 6.12, 7.13, 8.29, 9.43, 10.74, 11.99, 13.41, 14.64], 'c': [0.0, 1.22, 2.51, 3.59, 4.85, 6.07, 7.13, 8.43, 9.61, 10.79, 12.03, 13.39, 14.63]}</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>tivio-relatorio-gestao-credito-privado.html</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>institucional</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>histEnd</t>
+        </is>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>[12.48, 12.0, 'CDI']</t>
+        </is>
+      </c>
+      <c r="E168" t="inlineStr">
+        <is>
+          <t>[14.64, 14.63, 'CDI']</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>tivio-relatorio-gestao-credito-privado.html</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>institucional</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>comentario</t>
+        </is>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>['No mês, o mercado de crédito privado high grade manteve o movimento de fechamento gradual de spreads, com fluxo comprador consistente no secundário e oferta primária ainda concentrada em emissores de primeira linha.', 'A liquidez permaneceu saudável ao longo da curva, com boa demanda por papéis bancários e por debêntures de empresas de energia, saneamento e infraestrutura, setores de maior peso na carteira.', 'Do ponto de vista da gestão, seguimos priorizando emissores de baixo risco de crédito e o controle da duration, mantendo carrego atrativo sobre o CDI sem elevar de forma relevante a volatilidade da cota.', 'O INSTITUCIONAL apresentou rentabilidade de &lt;b&gt;1,27%&lt;/b&gt; no mês (&lt;b&gt;104% do CDI&lt;/b&gt;), acumulando &lt;b&gt;8,13%&lt;/b&gt; no ano. Os principais atribuidores de resultado foram as debêntures corporativas e a parcela bancária da carteira.']</t>
+        </is>
+      </c>
+      <c r="E169" t="inlineStr">
+        <is>
+          <t>['Em agosto, o mercado de crédito foi marcado por um ambiente de menor liquidez nas negociações do mercado secundário e por uma leve reabertura dos spreads de crédito. Após meses consecutivos de compressão dos prêmios de risco, observou-se um movimento mais cauteloso por parte dos investidores, com os spreads médios dos títulos corporativos indexados ao CDI avançando aproximadamente 0,03%, passando de CDI + 1,19% para CDI + 1,22% ao ano. Apesar desse ajuste, os níveis de prêmio permaneceram próximos das mínimas históricas observadas ao longo do ciclo recente.', 'No mercado secundário, a redução do volume negociado contribuiu para uma formação de preços mais seletiva, especialmente em ativos corporativos com menor liquidez. Ainda assim, o comportamento dos investidores permaneceu construtivo, sustentado por um ambiente técnico favorável e pela continuidade da elevada demanda por ativos de crédito.', 'Já no mercado primário, as emissões bancárias seguiram registrando forte demanda por parte dos investidores. As ofertas de Letras Financeiras Seniores distribuídas ao longo do mês apresentaram níveis elevados de subscrição, com demanda que, em diversos casos, superou três vezes o volume ofertado. Esse forte apetite permitiu que as operações fossem precificadas com taxas inferiores aos limites inicialmente indicados pelos emissores, evidenciando a elevada disponibilidade de recursos para alocação na indústria de crédito. Por outro lado, o pipeline de emissões corporativas permaneceu limitado, restringindo a oferta de novos ativos em um momento de demanda ainda aquecida.', 'Em relação aos fluxos, os fundos com alocação mínima de 15% em crédito e ao menos 1% em debêntures apresentaram captação líquida próxima de R$ 8 bilhões em agosto, resultado significativamente superior ao observado no mês anterior. O volume reforça a percepção de que os investidores seguem direcionando recursos para estratégias de crédito, impulsionados pelo elevado nível de carrego proporcionado pelos ativos indexados ao CDI e pela busca por alternativas de investimento com perfil de risco-retorno atrativo.', 'Nesse contexto, a combinação entre fluxos positivos para a indústria, vencimentos e amortizações recorrentes das carteiras, além da limitada oferta de novos ativos corporativos, continuou sustentando a demanda por crédito privado. Ainda que agosto tenha apresentado uma leve reabertura dos spreads médios de mercado, a dinâmica técnica permanece favorável e os prêmios seguem negociando em patamares historicamente reduzidos.', 'Por fim, sob a ótica da gestão, seguimos acompanhando de forma criteriosa a evolução dos fundamentos dos emissores presentes nas carteiras, com atenção especial aos indicadores operacionais, à geração de caixa e à manutenção de estruturas de capital adequadas. Em um ambiente em que os spreads permanecem comprimidos em termos históricos, mantemos disciplina na alocação dos recursos, priorizando operações que apresentem adequada relação entre risco e retorno e preservando flexibilidade para captura de oportunidades que possam surgir em eventuais períodos de maior volatilidade do mercado.', 'Nesse cenário, o Fundo Tivio Institucional apresentou rentabilidade de 1,09% no mês (100% do CDI), acumulando 9,31% (100% do CDI) no ano. Na parcela de corporativos, os maiores atribuidores de resultado foram para Argo e Aegea, enquanto Aegea foi o maior detrator.']</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>tivio-relatorio-gestao-credito-privado.html</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>inst15</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>adm</t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>0,45% a.a.</t>
+        </is>
+      </c>
+      <c r="E170" t="inlineStr">
+        <is>
+          <t>0,50% a.a.</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>tivio-relatorio-gestao-credito-privado.html</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>inst15</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>perf</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>Não há</t>
+        </is>
+      </c>
+      <c r="E171" t="inlineStr">
+        <is>
+          <t>20% do que exceder 102,5% do CDI</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>tivio-relatorio-gestao-credito-privado.html</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>inst15</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>pl</t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>R$ 161.593.743,98</t>
+        </is>
+      </c>
+      <c r="E172" t="inlineStr">
+        <is>
+          <t>R$ 156.046.891,63</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>tivio-relatorio-gestao-credito-privado.html</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>inst15</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>plm</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>R$ 140.997.685,81</t>
+        </is>
+      </c>
+      <c r="E173" t="inlineStr">
+        <is>
+          <t>R$ 146.843.921,67</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>tivio-relatorio-gestao-credito-privado.html</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>inst15</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>perfrows</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>{'pct': ['113%', '102%', '102%']}</t>
+        </is>
+      </c>
+      <c r="E174" t="inlineStr">
+        <is>
+          <t>{'fundo': ['1,11%', '9,53%', '14,94%', '30,92%', '51,22%', '1.644,37%'], 'bench': ['1,09%', '9,33%', '14,57%', '29,49%', '44,17%', '1.408,13%'], 'pct': ['102%', '102%', '103%', '105%', '116%', '117%']}</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>tivio-relatorio-gestao-credito-privado.html</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>inst15</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>emissores</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>[['TUPY', '3,04%', 100], ['UNIDAS', '2,71%', 89], ['AEGEA', '2,33%', 77], ['HAPVIDA', '2,01%', 66], ['EQUATORIAL', '1,74%', 57]]</t>
+        </is>
+      </c>
+      <c r="E175" t="inlineStr">
+        <is>
+          <t>[['C6', '5,45%', 100], ['ABC', '3,43%', 63], ['XP', '3,28%', 60], ['BTG', '3,28%', 60], ['BRADESCO', '1,76%', 32]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>tivio-relatorio-gestao-credito-privado.html</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>inst15</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>setores</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>[['Financeiro', '29%'], ['FIDC', '13%'], ['Energia Elétrica', '7%'], ['Saneamento', '5%'], ['Transporte e Logística', '4%'], ['Caixa', '26%']]</t>
+        </is>
+      </c>
+      <c r="E176" t="inlineStr">
+        <is>
+          <t>[['Financeiro', '28,0%'], ['FIDC', '13,0%'], ['Energia Elétrica', '7,1%'], ['Locação de veículos', '3,8%'], ['Saneamento', '3,5%'], ['Caixa', '27,2%']]</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>tivio-relatorio-gestao-credito-privado.html</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>inst15</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>rating</t>
+        </is>
+      </c>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>[['AAA', '46,2%', 100], ['AA+', '24,8%', 54], ['AA', '14,1%', 31], ['AA-', '9,4%', 20], ['A+', '3,9%', 8], ['A', '1,6%', 3]]</t>
+        </is>
+      </c>
+      <c r="E177" t="inlineStr">
+        <is>
+          <t>[['AAA', '32,7%', 100], ['AA+', '7,8%', 24], ['AA', '4,1%', 13], ['AA-', '5,7%', 17], ['A+', '4,2%', 13], ['A', '6,2%', 19]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>tivio-relatorio-gestao-credito-privado.html</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>inst15</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>val</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>1,00%</t>
+        </is>
+      </c>
+      <c r="E178" t="inlineStr">
+        <is>
+          <t>0,95%</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>tivio-relatorio-gestao-credito-privado.html</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>inst15</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>val</t>
+        </is>
+      </c>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>1,97</t>
+        </is>
+      </c>
+      <c r="E179" t="inlineStr">
+        <is>
+          <t>1,80</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>tivio-relatorio-gestao-credito-privado.html</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>inst15</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>anos</t>
+        </is>
+      </c>
+      <c r="E180" t="inlineStr">
+        <is>
+          <t>ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>tivio-relatorio-gestao-credito-privado.html</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>inst15</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>hist12</t>
+        </is>
+      </c>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="E181" t="inlineStr">
+        <is>
+          <t>{'b': 'CDI', 'l': ['2025-08', '2025-09', '2025-10', '2025-11', '2025-12', '2026-01', '2026-02', '2026-03', '2026-04', '2026-05', '2026-06', '2026-07', '2026-08'], 'f': [0.0, 1.29, 2.5, 3.53, 5.0, 6.31, 7.33, 8.3, 9.48, 10.88, 12.2, 13.74, 15.0], 'c': [0.0, 1.22, 2.51, 3.59, 4.85, 6.07, 7.13, 8.43, 9.61, 10.79, 12.03, 13.39, 14.63]}</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>tivio-relatorio-gestao-credito-privado.html</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>inst15</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>histEnd</t>
+        </is>
+      </c>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>[12.24, 12.0, 'CDI']</t>
+        </is>
+      </c>
+      <c r="E182" t="inlineStr">
+        <is>
+          <t>[15.0, 14.63, 'CDI']</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>tivio-relatorio-gestao-credito-privado.html</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>inst15</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>comentario</t>
+        </is>
+      </c>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>['No mês, o mercado de crédito privado high grade manteve o movimento de fechamento gradual de spreads, com fluxo comprador consistente no secundário e oferta primária ainda concentrada em emissores de primeira linha.', 'A liquidez permaneceu saudável ao longo da curva, com boa demanda por papéis bancários e por debêntures de empresas de energia, saneamento e infraestrutura, setores de maior peso na carteira.', 'Do ponto de vista da gestão, seguimos priorizando emissores de baixo risco de crédito e o controle da duration, mantendo carrego atrativo sobre o CDI sem elevar de forma relevante a volatilidade da cota.', 'O INSTITUCIONAL 15 apresentou rentabilidade de &lt;b&gt;1,37%&lt;/b&gt; no mês (&lt;b&gt;113% do CDI&lt;/b&gt;), acumulando &lt;b&gt;8,32%&lt;/b&gt; no ano. Os principais atribuidores de resultado foram as debêntures corporativas e a parcela bancária da carteira.']</t>
+        </is>
+      </c>
+      <c r="E183" t="inlineStr">
+        <is>
+          <t>['Em agosto, o mercado de crédito foi marcado por um ambiente de menor liquidez nas negociações do mercado secundário e por uma leve reabertura dos spreads de crédito. Após meses consecutivos de compressão dos prêmios de risco, observou-se um movimento mais cauteloso por parte dos investidores, com os spreads médios dos títulos corporativos indexados ao CDI avançando aproximadamente 0,03%, passando de CDI + 1,19% para CDI + 1,22% ao ano. Apesar desse ajuste, os níveis de prêmio permaneceram próximos das mínimas históricas observadas ao longo do ciclo recente.', 'No mercado secundário, a redução do volume negociado contribuiu para uma formação de preços mais seletiva, especialmente em ativos corporativos com menor liquidez. Ainda assim, o comportamento dos investidores permaneceu construtivo, sustentado por um ambiente técnico favorável e pela continuidade da elevada demanda por ativos de crédito.', 'Já no mercado primário, as emissões bancárias seguiram registrando forte demanda por parte dos investidores. As ofertas de Letras Financeiras Seniores distribuídas ao longo do mês apresentaram níveis elevados de subscrição, com demanda que, em diversos casos, superou três vezes o volume ofertado. Esse forte apetite permitiu que as operações fossem precificadas com taxas inferiores aos limites inicialmente indicados pelos emissores, evidenciando a elevada disponibilidade de recursos para alocação na indústria de crédito. Por outro lado, o pipeline de emissões corporativas permaneceu limitado, restringindo a oferta de novos ativos em um momento de demanda ainda aquecida.', 'Em relação aos fluxos, os fundos com alocação mínima de 15% em crédito e ao menos 1% em debêntures apresentaram captação líquida próxima de R$ 8 bilhões em agosto, resultado significativamente superior ao observado no mês anterior. O volume reforça a percepção de que os investidores seguem direcionando recursos para estratégias de crédito, impulsionados pelo elevado nível de carrego proporcionado pelos ativos indexados ao CDI e pela busca por alternativas de investimento com perfil de risco-retorno atrativo.', 'Nesse contexto, a combinação entre fluxos positivos para a indústria, vencimentos e amortizações recorrentes das carteiras, além da limitada oferta de novos ativos corporativos, continuou sustentando a demanda por crédito privado. Ainda que agosto tenha apresentado uma leve reabertura dos spreads médios de mercado, a dinâmica técnica permanece favorável e os prêmios seguem negociando em patamares historicamente reduzidos.', 'Por fim, sob a ótica da gestão, seguimos acompanhando de forma criteriosa a evolução dos fundamentos dos emissores presentes nas carteiras, com atenção especial aos indicadores operacionais, à geração de caixa e à manutenção de estruturas de capital adequadas. Em um ambiente em que os spreads permanecem comprimidos em termos históricos, mantemos disciplina na alocação dos recursos, priorizando operações que apresentem adequada relação entre risco e retorno e preservando flexibilidade para captura de oportunidades que possam surgir em eventuais períodos de maior volatilidade do mercado.', 'Nesse cenário, o Tivio Institucional 15 apresentou rentabilidade de 1,11% no mês (102% do CDI), acumulando 9,53% (102% do CDI) no ano. Na parcela de corporativos, os maiores atribuidores de resultado foram para Tupy e Randon, enquanto Hapvida foi o maior detrator.']</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>tivio-relatorio-gestao-credito-privado.html</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>inst30</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>adm</t>
+        </is>
+      </c>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t>0,63% a.a.</t>
+        </is>
+      </c>
+      <c r="E184" t="inlineStr">
+        <is>
+          <t>0,625% a.a.</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>tivio-relatorio-gestao-credito-privado.html</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>inst30</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>perf</t>
+        </is>
+      </c>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>20% do que exceder o CDI</t>
+        </is>
+      </c>
+      <c r="E185" t="inlineStr">
+        <is>
+          <t>20% do que exceder 100% do CDI</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>tivio-relatorio-gestao-credito-privado.html</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>inst30</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>pl</t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>R$ 143.232.764,20</t>
+        </is>
+      </c>
+      <c r="E186" t="inlineStr">
+        <is>
+          <t>R$ 126.168.780,56</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>tivio-relatorio-gestao-credito-privado.html</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>inst30</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>plm</t>
+        </is>
+      </c>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>R$ 155.004.649,74</t>
+        </is>
+      </c>
+      <c r="E187" t="inlineStr">
+        <is>
+          <t>R$ 158.893.390,74</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>tivio-relatorio-gestao-credito-privado.html</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>inst30</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>perfrows</t>
+        </is>
+      </c>
+      <c r="D188" t="inlineStr">
+        <is>
+          <t>{'pct': ['113%', '101%', '101%']}</t>
+        </is>
+      </c>
+      <c r="E188" t="inlineStr">
+        <is>
+          <t>{'fundo': ['1,12%', '9,45%', '14,68%', '−', '−', '25,93%'], 'bench': ['1,09%', '9,33%', '14,57%', '−', '−', '25,71%'], 'pct': ['102%', '101%', '101%', '−', '−', '101%']}</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>tivio-relatorio-gestao-credito-privado.html</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>inst30</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>emissores</t>
+        </is>
+      </c>
+      <c r="D189" t="inlineStr">
+        <is>
+          <t>[['AEGEA', '2,88%', 100], ['EQUATORIAL', '2,55%', 89], ['TUPY', '2,22%', 77], ['SABESP', '1,94%', 67], ['ENGIE', '1,67%', 58]]</t>
+        </is>
+      </c>
+      <c r="E189" t="inlineStr">
+        <is>
+          <t>[['C6', '6,00%', 100], ['ABC', '3,78%', 63], ['XP', '3,62%', 60], ['BTG', '3,62%', 60], ['BRADESCO', '1,94%', 32]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>tivio-relatorio-gestao-credito-privado.html</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>inst30</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>setores</t>
+        </is>
+      </c>
+      <c r="D190" t="inlineStr">
+        <is>
+          <t>[['Financeiro', '33%'], ['FIDC', '15%'], ['Energia Elétrica', '8%'], ['Saneamento', '6%'], ['Transporte e Logística', '5%'], ['Caixa', '16%']]</t>
+        </is>
+      </c>
+      <c r="E190" t="inlineStr">
+        <is>
+          <t>[['Financeiro', '30,8%'], ['FIDC', '14,4%'], ['Energia Elétrica', '7,8%'], ['Locação de veículos', '4,2%'], ['Saneamento', '3,8%'], ['Caixa', '19,7%']]</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>tivio-relatorio-gestao-credito-privado.html</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>inst30</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>rating</t>
+        </is>
+      </c>
+      <c r="D191" t="inlineStr">
+        <is>
+          <t>[['AAA', '46,2%', 100], ['AA+', '24,8%', 54], ['AA', '14,1%', 31], ['AA-', '9,4%', 20], ['A+', '3,9%', 8], ['A', '1,6%', 3]]</t>
+        </is>
+      </c>
+      <c r="E191" t="inlineStr">
+        <is>
+          <t>[['AAA', '36,0%', 100], ['AA+', '8,6%', 24], ['AA', '4,5%', 13], ['AA-', '6,2%', 17], ['A+', '4,7%', 13], ['A', '6,8%', 19]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>tivio-relatorio-gestao-credito-privado.html</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>inst30</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>val</t>
+        </is>
+      </c>
+      <c r="D192" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E192" t="inlineStr">
+        <is>
+          <t>1,04%</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>tivio-relatorio-gestao-credito-privado.html</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>inst30</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>val</t>
+        </is>
+      </c>
+      <c r="D193" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E193" t="inlineStr">
+        <is>
+          <t>1,86</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>tivio-relatorio-gestao-credito-privado.html</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>inst30</t>
+        </is>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="D194" t="inlineStr">
+        <is>
+          <t>anos</t>
+        </is>
+      </c>
+      <c r="E194" t="inlineStr">
+        <is>
+          <t>ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>tivio-relatorio-gestao-credito-privado.html</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>inst30</t>
+        </is>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>hist12</t>
+        </is>
+      </c>
+      <c r="D195" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="E195" t="inlineStr">
+        <is>
+          <t>{'b': 'CDI', 'l': ['2025-08', '2025-09', '2025-10', '2025-11', '2025-12', '2026-01', '2026-02', '2026-03', '2026-04', '2026-05', '2026-06', '2026-07', '2026-08'], 'f': [0.0, 1.3, 2.52, 3.56, 4.85, 6.13, 7.14, 8.01, 9.16, 10.62, 11.95, 13.48, 14.75], 'c': [0.0, 1.22, 2.51, 3.59, 4.85, 6.07, 7.13, 8.43, 9.61, 10.79, 12.03, 13.39, 14.63]}</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>tivio-relatorio-gestao-credito-privado.html</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>inst30</t>
+        </is>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>histEnd</t>
+        </is>
+      </c>
+      <c r="D196" t="inlineStr">
+        <is>
+          <t>[12.12, 12.0, 'CDI']</t>
+        </is>
+      </c>
+      <c r="E196" t="inlineStr">
+        <is>
+          <t>[14.75, 14.63, 'CDI']</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>tivio-relatorio-gestao-credito-privado.html</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>inst30</t>
+        </is>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>comentario</t>
+        </is>
+      </c>
+      <c r="D197" t="inlineStr">
+        <is>
+          <t>['No mês, o mercado de crédito privado high grade manteve o movimento de fechamento gradual de spreads, com fluxo comprador consistente no secundário e oferta primária ainda concentrada em emissores de primeira linha.', 'A liquidez permaneceu saudável ao longo da curva, com boa demanda por papéis bancários e por debêntures de empresas de energia, saneamento e infraestrutura, setores de maior peso na carteira.', 'Do ponto de vista da gestão, seguimos priorizando emissores de baixo risco de crédito e o controle da duration, mantendo carrego atrativo sobre o CDI sem elevar de forma relevante a volatilidade da cota.', 'O INSTITUCIONAL 30 apresentou rentabilidade de &lt;b&gt;1,36%&lt;/b&gt; no mês (&lt;b&gt;113% do CDI&lt;/b&gt;), acumulando &lt;b&gt;8,08%&lt;/b&gt; no ano. Os principais atribuidores de resultado foram as debêntures corporativas e a parcela bancária da carteira.']</t>
+        </is>
+      </c>
+      <c r="E197" t="inlineStr">
+        <is>
+          <t>['Em agosto, o mercado de crédito foi marcado por um ambiente de menor liquidez nas negociações do mercado secundário e por uma leve reabertura dos spreads de crédito. Após meses consecutivos de compressão dos prêmios de risco, observou-se um movimento mais cauteloso por parte dos investidores, com os spreads médios dos títulos corporativos indexados ao CDI avançando aproximadamente 0,03%, passando de CDI + 1,19% para CDI + 1,22% ao ano. Apesar desse ajuste, os níveis de prêmio permaneceram próximos das mínimas históricas observadas ao longo do ciclo recente.', 'No mercado secundário, a redução do volume negociado contribuiu para uma formação de preços mais seletiva, especialmente em ativos corporativos com menor liquidez. Ainda assim, o comportamento dos investidores permaneceu construtivo, sustentado por um ambiente técnico favorável e pela continuidade da elevada demanda por ativos de crédito.', 'Já no mercado primário, as emissões bancárias seguiram registrando forte demanda por parte dos investidores. As ofertas de Letras Financeiras Seniores distribuídas ao longo do mês apresentaram níveis elevados de subscrição, com demanda que, em diversos casos, superou três vezes o volume ofertado. Esse forte apetite permitiu que as operações fossem precificadas com taxas inferiores aos limites inicialmente indicados pelos emissores, evidenciando a elevada disponibilidade de recursos para alocação na indústria de crédito. Por outro lado, o pipeline de emissões corporativas permaneceu limitado, restringindo a oferta de novos ativos em um momento de demanda ainda aquecida.', 'Em relação aos fluxos, os fundos com alocação mínima de 15% em crédito e ao menos 1% em debêntures apresentaram captação líquida próxima de R$ 8 bilhões em agosto, resultado significativamente superior ao observado no mês anterior. O volume reforça a percepção de que os investidores seguem direcionando recursos para estratégias de crédito, impulsionados pelo elevado nível de carrego proporcionado pelos ativos indexados ao CDI e pela busca por alternativas de investimento com perfil de risco-retorno atrativo.', 'Nesse contexto, a combinação entre fluxos positivos para a indústria, vencimentos e amortizações recorrentes das carteiras, além da limitada oferta de novos ativos corporativos, continuou sustentando a demanda por crédito privado. Ainda que agosto tenha apresentado uma leve reabertura dos spreads médios de mercado, a dinâmica técnica permanece favorável e os prêmios seguem negociando em patamares historicamente reduzidos.', 'Por fim, sob a ótica da gestão, seguimos acompanhando de forma criteriosa a evolução dos fundamentos dos emissores presentes nas carteiras, com atenção especial aos indicadores operacionais, à geração de caixa e à manutenção de estruturas de capital adequadas. Em um ambiente em que os spreads permanecem comprimidos em termos históricos, mantemos disciplina na alocação dos recursos, priorizando operações que apresentem adequada relação entre risco e retorno e preservando flexibilidade para captura de oportunidades que possam surgir em eventuais períodos de maior volatilidade do mercado.', 'Nesse cenário, o Tivio Institucional 30 apresentou rentabilidade de 1,12% no mês (102% do CDI), acumulando 9,45% (101% do CDI) no ano. Na parcela de corporativos, os maiores atribuidores de resultado foram para Tupy e Randon, enquanto Hapvida foi o maior detrator.']</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>tivio-relatorio-gestao-credito-privado.html</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>infraplus</t>
+        </is>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>pl</t>
+        </is>
+      </c>
+      <c r="D198" t="inlineStr">
+        <is>
+          <t>R$ 42.983.282,75</t>
+        </is>
+      </c>
+      <c r="E198" t="inlineStr">
+        <is>
+          <t>R$ 42.694.019,75</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>tivio-relatorio-gestao-credito-privado.html</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>infraplus</t>
+        </is>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>plm</t>
+        </is>
+      </c>
+      <c r="D199" t="inlineStr">
+        <is>
+          <t>R$ 52.049.593,91</t>
+        </is>
+      </c>
+      <c r="E199" t="inlineStr">
+        <is>
+          <t>R$ 49.421.174,50</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>tivio-relatorio-gestao-credito-privado.html</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>infraplus</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>perfrows</t>
+        </is>
+      </c>
+      <c r="D200" t="inlineStr">
+        <is>
+          <t>{'abs': ['1,24%', '7,80%', '12,94%'], 'alfa': ['−0,14%', '−3,14%', '−2,75%']}</t>
+        </is>
+      </c>
+      <c r="E200" t="inlineStr">
+        <is>
+          <t>{'fundo': ['1,26%', '5,98%', '9,91%', '19,03%', '29,49%', '77,41%'], 'bench': ['1,28%', '9,18%', '13,34%', '23,32%', '33,11%', '87,91%'], 'abs': ['1,26%', '5,98%', '9,91%', '19,03%', '29,49%', '77,41%'], 'alfa': ['−0,01%', '−3,20%', '−3,44%', '−4,28%', '−3,62%', '−10,50%']}</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>tivio-relatorio-gestao-credito-privado.html</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>infraplus</t>
+        </is>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>emissores</t>
+        </is>
+      </c>
+      <c r="D201" t="inlineStr">
+        <is>
+          <t>[['EQUATORIAL', '3,87%', 100], ['CEMIG', '3,42%', 88], ['COPEL', '3,14%', 81], ['SABESP', '3,03%', 78], ['ELETROBRAS', '2,92%', 75]]</t>
+        </is>
+      </c>
+      <c r="E201" t="inlineStr">
+        <is>
+          <t>[['AUREN', '7,68%', 100], ['EQUATORIAL', '7,24%', 94], ['EDF', '5,54%', 72], ['SINOP', '3,99%', 52], ['ELETROBRAS', '3,65%', 48]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>tivio-relatorio-gestao-credito-privado.html</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>infraplus</t>
+        </is>
+      </c>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>setores</t>
+        </is>
+      </c>
+      <c r="D202" t="inlineStr">
+        <is>
+          <t>[['Energia Elétrica', '55%'], ['Transporte e Logística', '15%'], ['Saneamento', '7%'], ['Petróleo e Gás', '5%'], ['TI e Telecomunicações', '4%'], ['Caixa', '5%']]</t>
+        </is>
+      </c>
+      <c r="E202" t="inlineStr">
+        <is>
+          <t>[['Energia Elétrica', '55,9%'], ['Transporte e Logística', '15,3%'], ['Saneamento', '7,3%'], ['TI e Telecomunicações', '5,4%'], ['Petróleo e Gás', '4,8%'], ['Caixa', '4,8%']]</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>tivio-relatorio-gestao-credito-privado.html</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>infraplus</t>
+        </is>
+      </c>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>rating</t>
+        </is>
+      </c>
+      <c r="D203" t="inlineStr">
+        <is>
+          <t>[['AAA', '32,35%', 100], ['AA+', '17,91%', 55], ['AA', '11,27%', 35], ['AA-', '15,61%', 48], ['A+', '7,15%', 22], ['A', '1,85%', 6]]</t>
+        </is>
+      </c>
+      <c r="E203" t="inlineStr">
+        <is>
+          <t>[['AAA', '35,4%', 100], ['AA+', '26,0%', 74], ['AA', '11,1%', 31], ['AA-', '8,8%', 25], ['A+', '5,1%', 14], ['A', '2,4%', 7]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>tivio-relatorio-gestao-credito-privado.html</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>infraplus</t>
+        </is>
+      </c>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t>val</t>
+        </is>
+      </c>
+      <c r="D204" t="inlineStr">
+        <is>
+          <t>8,63%</t>
+        </is>
+      </c>
+      <c r="E204" t="inlineStr">
+        <is>
+          <t>8,23%</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>tivio-relatorio-gestao-credito-privado.html</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>infraplus</t>
+        </is>
+      </c>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t>val</t>
+        </is>
+      </c>
+      <c r="D205" t="inlineStr">
+        <is>
+          <t>4,00</t>
+        </is>
+      </c>
+      <c r="E205" t="inlineStr">
+        <is>
+          <t>3,98</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>tivio-relatorio-gestao-credito-privado.html</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>infraplus</t>
+        </is>
+      </c>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>hist12</t>
+        </is>
+      </c>
+      <c r="D206" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="E206" t="inlineStr">
+        <is>
+          <t>{'b': 'IMA-B 5', 'l': ['2025-08', '2025-09', '2025-10', '2025-11', '2025-12', '2026-01', '2026-02', '2026-03', '2026-04', '2026-05', '2026-06', '2026-07', '2026-08'], 'f': [0.0, 1.64, 1.66, 3.1, 3.59, 5.89, 6.95, 6.67, 6.97, 7.26, 7.24, 8.41, 9.78], 'c': [0.0, 0.66, 1.69, 2.78, 3.76, 5.01, 6.29, 7.77, 9.19, 10.24, 10.48, 11.85, 13.28]}</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>tivio-relatorio-gestao-credito-privado.html</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>infraplus</t>
+        </is>
+      </c>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t>histEnd</t>
+        </is>
+      </c>
+      <c r="D207" t="inlineStr">
+        <is>
+          <t>[12.94, 15.69, 'IMA-B 5']</t>
+        </is>
+      </c>
+      <c r="E207" t="inlineStr">
+        <is>
+          <t>[9.78, 13.28, 'IMA-B 5']</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>tivio-relatorio-gestao-credito-privado.html</t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>infraplus</t>
+        </is>
+      </c>
+      <c r="C208" t="inlineStr">
+        <is>
+          <t>comentario</t>
+        </is>
+      </c>
+      <c r="D208" t="inlineStr">
+        <is>
+          <t>['Em julho, os títulos de crédito indexados ao IPCA precificados pela ANBIMA apresentaram desempenho negativo, refletindo a elevação da curva real de juros ao longo do período. Embora os spreads de crédito tenham fechado cerca de 16 bps em relação ao mês anterior, o avanço da curva de juros reais prevaleceu sobre esse efeito.', 'No mercado primário, manteve-se o cenário de oferta restrita, com parcela relevante das emissões sendo absorvida pelos balanços dos bancos distribuidores. No secundário, houve retomada da demanda por papéis incentivados, inclusive nos vencimentos mais longos.', 'Do ponto de vista da gestão, mantivemos postura cautelosa, priorizando o encurtamento da duration da carteira como forma de mitigar volatilidade e reduzir a sensibilidade a movimentos adversos nos spreads.', 'O Infra Plus apresentou rentabilidade, isenta de imposto de renda, de &lt;b&gt;1,24%&lt;/b&gt; no mês, acumulando &lt;b&gt;7,80%&lt;/b&gt; no ano. Destacam-se as debêntures de RUMO e NTS, enquanto Alloha Fibra foi a maior detratora.']</t>
+        </is>
+      </c>
+      <c r="E208" t="inlineStr">
+        <is>
+          <t>['Em agosto, os títulos de crédito indexados ao IPCA precificados pela ANBIMA apresentaram desempenho positivo, refletindo principalmente o movimento de fechamento da curva real de juros observado ao longo do período. Embora os spreads de crédito tenham registrado abertura média de aproximadamente 5 bps em relação a julho, a redução das taxas reais ao longo da estrutura a termo mais do que compensou esse movimento. Como resultado, as taxas médias dos títulos incentivados precificados pela ANBIMA encerraram o mês com fechamento próximo de 16 bps, proporcionando valorização dos ativos no mercado secundário.', 'No mercado primário, manteve-se o cenário de oferta restrita de ativos, com parcela relevante das emissões sendo absorvida diretamente pelos balanços dos bancos distribuidores. Já no mercado secundário, observou-se um nível de liquidez inferior à média observada ao longo de 2025, contribuindo para um ambiente de maior equilíbrio entre oferta e demanda dos ativos negociados.', 'Sob a ótica da gestão, mantivemos uma postura cautelosa ao longo do período, priorizando o encurtamento da duration da carteira como forma de mitigar a volatilidade e reduzir a sensibilidade do portfólio a eventuais movimentos adversos nos spreads de crédito. Apesar da melhora observada no desempenho dos ativos incentivados no mês, seguimos avaliando que os níveis atuais de prêmio ainda oferecem pouca margem de segurança frente aos riscos inerentes à classe. Dessa forma, permanecemos atentos à evolução das condições de mercado e à dinâmica de precificação dos ativos, buscando identificar oportunidades mais atrativas para aumentar a exposição ao risco de crédito de forma gradual e criteriosa, quando a relação risco-retorno se mostrar mais favorável.', 'Nesse cenário, o Tivio Infra Plus apresentou rentabilidade, isenta de imposto de renda de 1,26% no mês, acumulando 5,98% no ano. Na atribuição de performance, pode-se destacar as debêntures de NTS e São Simão, enquanto as de Jalles Machado foram as maiores detratoras.']</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>tivio-relatorio-gestao-credito-privado.html</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C209" t="inlineStr">
+        <is>
+          <t>data</t>
+        </is>
+      </c>
+      <c r="D209" t="inlineStr">
+        <is>
+          <t>31/07/2026</t>
+        </is>
+      </c>
+      <c r="E209" t="inlineStr">
+        <is>
+          <t>31/08/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>tivio-relatorio-gestao-credito-privado.html</t>
+        </is>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C210" t="inlineStr">
+        <is>
+          <t>data</t>
+        </is>
+      </c>
+      <c r="D210" t="inlineStr">
+        <is>
+          <t>Julho de 2026</t>
+        </is>
+      </c>
+      <c r="E210" t="inlineStr">
+        <is>
+          <t>Agosto de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>tivio-relatorio-gestao-credito-privado.html</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C211" t="inlineStr">
+        <is>
+          <t>data</t>
+        </is>
+      </c>
+      <c r="D211" t="inlineStr">
+        <is>
+          <t>julho de 2026</t>
+        </is>
+      </c>
+      <c r="E211" t="inlineStr">
+        <is>
+          <t>agosto de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>tivio-relatorio-gestao-credito-privado.html</t>
+        </is>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C212" t="inlineStr">
+        <is>
+          <t>data</t>
+        </is>
+      </c>
+      <c r="D212" t="inlineStr">
+        <is>
+          <t>Julho 2026</t>
+        </is>
+      </c>
+      <c r="E212" t="inlineStr">
+        <is>
+          <t>Agosto 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>tivio-relatorio-gestao-credito-privado.html</t>
+        </is>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C213" t="inlineStr">
+        <is>
+          <t>data</t>
+        </is>
+      </c>
+      <c r="D213" t="inlineStr">
+        <is>
+          <t>-jul26</t>
+        </is>
+      </c>
+      <c r="E213" t="inlineStr">
+        <is>
+          <t>-ago26</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>tivio-relatorio-gestao-credito-privado.html</t>
+        </is>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C214" t="inlineStr">
+        <is>
+          <t>data</t>
+        </is>
+      </c>
+      <c r="D214" t="inlineStr">
+        <is>
+          <t>julho/2026</t>
+        </is>
+      </c>
+      <c r="E214" t="inlineStr">
+        <is>
+          <t>agosto/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>tivio-relatorio-gestao-credito-privado.html</t>
+        </is>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C215" t="inlineStr">
+        <is>
+          <t>data</t>
+        </is>
+      </c>
+      <c r="D215" t="inlineStr">
+        <is>
+          <t>const A=6;const track</t>
+        </is>
+      </c>
+      <c r="E215" t="inlineStr">
+        <is>
+          <t>const A=7;const track</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>tivio-relatorio-gestao-credito-privado.html</t>
+        </is>
+      </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C216" t="inlineStr">
+        <is>
+          <t>libs de exportação</t>
+        </is>
+      </c>
+      <c r="D216" t="inlineStr">
+        <is>
+          <t>CDN</t>
+        </is>
+      </c>
+      <c r="E216" t="inlineStr">
+        <is>
+          <t>4 referências → vendor/ local (CDN como reserva)</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>tivio-central.html</t>
+        </is>
+      </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>s1</t>
+        </is>
+      </c>
+      <c r="C217" t="inlineStr">
+        <is>
+          <t>date</t>
+        </is>
+      </c>
+      <c r="D217" t="inlineStr">
+        <is>
+          <t>Julho 2026</t>
+        </is>
+      </c>
+      <c r="E217" t="inlineStr">
+        <is>
+          <t>Agosto 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>tivio-central.html</t>
+        </is>
+      </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>s2</t>
+        </is>
+      </c>
+      <c r="C218" t="inlineStr">
+        <is>
+          <t>date</t>
+        </is>
+      </c>
+      <c r="D218" t="inlineStr">
+        <is>
+          <t>Julho 2026</t>
+        </is>
+      </c>
+      <c r="E218" t="inlineStr">
+        <is>
+          <t>Agosto 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>tivio-central.html</t>
+        </is>
+      </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>s8</t>
+        </is>
+      </c>
+      <c r="C219" t="inlineStr">
+        <is>
+          <t>date</t>
+        </is>
+      </c>
+      <c r="D219" t="inlineStr">
+        <is>
+          <t>Julho 2026</t>
+        </is>
+      </c>
+      <c r="E219" t="inlineStr">
+        <is>
+          <t>Agosto 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>tivio-central.html</t>
+        </is>
+      </c>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>r1</t>
+        </is>
+      </c>
+      <c r="C220" t="inlineStr">
+        <is>
+          <t>date</t>
+        </is>
+      </c>
+      <c r="D220" t="inlineStr">
+        <is>
+          <t>Julho 2026</t>
+        </is>
+      </c>
+      <c r="E220" t="inlineStr">
+        <is>
+          <t>Agosto 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>tivio-central.html</t>
+        </is>
+      </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>e1</t>
+        </is>
+      </c>
+      <c r="C221" t="inlineStr">
+        <is>
+          <t>date</t>
+        </is>
+      </c>
+      <c r="D221" t="inlineStr">
+        <is>
+          <t>Julho 2026</t>
+        </is>
+      </c>
+      <c r="E221" t="inlineStr">
+        <is>
+          <t>Agosto 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>tivio-central.html</t>
+        </is>
+      </c>
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C222" t="inlineStr">
+        <is>
+          <t>Central</t>
+        </is>
+      </c>
+      <c r="D222" t="inlineStr">
+        <is>
+          <t>cards de relatório</t>
+        </is>
+      </c>
+      <c r="E222" t="inlineStr">
+        <is>
+          <t>13 registrados para Agosto 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>tivio-central.html</t>
+        </is>
+      </c>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C223" t="inlineStr">
+        <is>
+          <t>data automática</t>
+        </is>
+      </c>
+      <c r="D223" t="inlineStr"/>
+      <c r="E223" t="inlineStr">
+        <is>
+          <t>DATA_BASE=2026-08-31</t>
         </is>
       </c>
     </row>
@@ -6918,11 +12932,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C4"/>
+  <dimension ref="A1:C23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="11" customWidth="1" min="1" max="1"/>
-    <col width="11" customWidth="1" min="2" max="2"/>
+    <col width="38" customWidth="1" min="1" max="1"/>
+    <col width="58" customWidth="1" min="2" max="2"/>
     <col width="58" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
@@ -6991,6 +13005,329 @@
       <c r="C4" t="inlineStr">
         <is>
           <t>carteira sem data na Base Carteira — os números saem, mas não há como confirmar que a posição é a do mês</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>selos sem arquivo local em assets/selos (qr) — saem pela URL do site, e podem não aparecer nas exportações. Ver assets/selos/LEIA-ME.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>relatorio/bvp</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>bvp</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>logo não encontrado em assets/logos (procurei "tivio_bvp")</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>relatorio/atuarial</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>atuarial</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>relatório não gerado: sem dados nesta edição</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>relatorio/banks</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Tivio Banks - Relatório de Gestão - Agosto 2026.pdf</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>fonte Versos não carregou (CDN inacessível?) — o PDF sai com a fonte de fallback e a métrica do texto muda</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>relatorio/institucional</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Tivio Institucional - Relatório de Gestão - Agosto 2026.pdf</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>fonte Versos não carregou (CDN inacessível?) — o PDF sai com a fonte de fallback e a métrica do texto muda</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>relatorio/inst15</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Tivio Institucional 15 - Relatório de Gestão - Agosto 2026.pdf</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>fonte Versos não carregou (CDN inacessível?) — o PDF sai com a fonte de fallback e a métrica do texto muda</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>relatorio/inst30</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Tivio Institucional 30 - Relatório de Gestão - Agosto 2026.pdf</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>fonte Versos não carregou (CDN inacessível?) — o PDF sai com a fonte de fallback e a métrica do texto muda</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>relatorio/infraplus</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Tivio Infra Plus - Relatório de Gestão - Agosto 2026.pdf</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>fonte Versos não carregou (CDN inacessível?) — o PDF sai com a fonte de fallback e a métrica do texto muda</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>relatorio/bvp</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Tivio BVP - Relatório de Gestão - Agosto 2026.pdf</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>fonte Versos não carregou (CDN inacessível?) — o PDF sai com a fonte de fallback e a métrica do texto muda</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>relatorio/rfcp</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Tivio RF CP - Relatório de Gestão - Agosto 2026.pdf</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>fonte Versos não carregou (CDN inacessível?) — o PDF sai com a fonte de fallback e a métrica do texto muda</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>relatorio/alt180</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Tivio ALT 180 - Relatório de Gestão - Agosto 2026.pdf</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>fonte Versos não carregou (CDN inacessível?) — o PDF sai com a fonte de fallback e a métrica do texto muda</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>relatorio/alt90</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Tivio ALT 90 - Relatório de Gestão - Agosto 2026.pdf</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>fonte Versos não carregou (CDN inacessível?) — o PDF sai com a fonte de fallback e a métrica do texto muda</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>relatorio/altlight</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Tivio ALT Light - Relatório de Gestão - Agosto 2026.pdf</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>fonte Versos não carregou (CDN inacessível?) — o PDF sai com a fonte de fallback e a métrica do texto muda</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>relatorio/infrapluscdi</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Tivio Infra Plus CDI - Relatório de Gestão - Agosto 2026.pdf</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>fonte Versos não carregou (CDN inacessível?) — o PDF sai com a fonte de fallback e a métrica do texto muda</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>relatorio/esplanada</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Tivio Esplanada - Relatório de Gestão - Agosto 2026.pdf</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>fonte Versos não carregou (CDN inacessível?) — o PDF sai com a fonte de fallback e a métrica do texto muda</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>relatorio/legacy</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Tivio Legacy Prev - Relatório de Gestão - Agosto 2026.pdf</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>fonte Versos não carregou (CDN inacessível?) — o PDF sai com a fonte de fallback e a métrica do texto muda</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>tivio-email-fundos-credito.html</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>alt180</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>o texto se refere a "julho" como o mês corrente — a data base é agosto</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>tivio-post-investment-solutions.html</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>topgestormacro</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>sem dados — rentabilidade e PL mantidos</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>tivio-central.html</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>tivio-central.html</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>card "Relatório de Gestão · Incentivado CDI 30" removido: aponta para "Tivio Incentivado CDI 30 - Relatório de Gestão Mensal.html", que não existe nesta edição</t>
         </is>
       </c>
     </row>
@@ -7005,17 +13342,734 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A1"/>
+  <dimension ref="A1:C48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="21" customWidth="1" min="1" max="1"/>
+    <col width="58" customWidth="1" min="1" max="1"/>
+    <col width="11" customWidth="1" min="2" max="2"/>
+    <col width="11" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>(nada nesta edição)</t>
-        </is>
+          <t>arquivo</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>formato</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>bytes</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Tivio Banks - Relatório de Gestão - Agosto 2026.html</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>html</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>337714</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Tivio Institucional - Relatório de Gestão - Agosto 2026.html</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>html</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>345960</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Tivio Institucional 15 - Relatório de Gestão - Agosto 2026.html</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>html</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>348537</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Tivio Institucional 30 - Relatório de Gestão - Agosto 2026.html</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>html</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>350499</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Tivio Infra Plus - Relatório de Gestão - Agosto 2026.html</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>html</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>341721</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Tivio BVP - Relatório de Gestão - Agosto 2026.html</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>html</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>325134</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Tivio RF CP - Relatório de Gestão - Agosto 2026.html</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>html</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>338290</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Tivio ALT 180 - Relatório de Gestão - Agosto 2026.html</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>html</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>328509</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Tivio ALT 90 - Relatório de Gestão - Agosto 2026.html</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>html</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>327610</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Tivio ALT Light - Relatório de Gestão - Agosto 2026.html</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>html</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>327741</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Tivio Infra Plus CDI - Relatório de Gestão - Agosto 2026.html</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>html</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>348878</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Tivio Esplanada - Relatório de Gestão - Agosto 2026.html</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>html</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>331377</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Tivio Legacy Prev - Relatório de Gestão - Agosto 2026.html</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>html</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>333666</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Tivio Banks - Relatório de Gestão - Agosto 2026.pdf</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>pdf</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>349660</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Tivio Banks - Relatório de Gestão - Agosto 2026.pptx</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>pptx</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>47618</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Tivio Institucional - Relatório de Gestão - Agosto 2026.pdf</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>pdf</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>356572</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Tivio Institucional - Relatório de Gestão - Agosto 2026.pptx</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>pptx</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>47822</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Tivio Institucional 15 - Relatório de Gestão - Agosto 2026.pdf</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>pdf</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>359553</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Tivio Institucional 15 - Relatório de Gestão - Agosto 2026.pptx</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>pptx</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>47845</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Tivio Institucional 30 - Relatório de Gestão - Agosto 2026.pdf</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>pdf</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>357406</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Tivio Institucional 30 - Relatório de Gestão - Agosto 2026.pptx</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>pptx</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>47695</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Tivio Infra Plus - Relatório de Gestão - Agosto 2026.pdf</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>pdf</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>349868</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Tivio Infra Plus - Relatório de Gestão - Agosto 2026.pptx</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>pptx</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>46723</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Tivio BVP - Relatório de Gestão - Agosto 2026.pdf</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>pdf</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>346073</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Tivio BVP - Relatório de Gestão - Agosto 2026.pptx</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>pptx</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>47654</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Tivio RF CP - Relatório de Gestão - Agosto 2026.pdf</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>pdf</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>346414</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Tivio RF CP - Relatório de Gestão - Agosto 2026.pptx</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>pptx</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>47691</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Tivio ALT 180 - Relatório de Gestão - Agosto 2026.pdf</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>pdf</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>323363</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Tivio ALT 180 - Relatório de Gestão - Agosto 2026.pptx</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>pptx</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>43224</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Tivio ALT 90 - Relatório de Gestão - Agosto 2026.pdf</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>pdf</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>323905</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Tivio ALT 90 - Relatório de Gestão - Agosto 2026.pptx</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>pptx</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>43195</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Tivio ALT Light - Relatório de Gestão - Agosto 2026.pdf</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>pdf</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>340010</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Tivio ALT Light - Relatório de Gestão - Agosto 2026.pptx</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>pptx</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>42078</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Tivio Infra Plus CDI - Relatório de Gestão - Agosto 2026.pdf</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>pdf</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
+        <v>351728</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Tivio Infra Plus CDI - Relatório de Gestão - Agosto 2026.pptx</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>pptx</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
+        <v>47122</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Tivio Esplanada - Relatório de Gestão - Agosto 2026.pdf</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>pdf</t>
+        </is>
+      </c>
+      <c r="C37" t="n">
+        <v>348578</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Tivio Esplanada - Relatório de Gestão - Agosto 2026.pptx</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>pptx</t>
+        </is>
+      </c>
+      <c r="C38" t="n">
+        <v>46718</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Tivio Legacy Prev - Relatório de Gestão - Agosto 2026.pdf</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>pdf</t>
+        </is>
+      </c>
+      <c r="C39" t="n">
+        <v>347005</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Tivio Legacy Prev - Relatório de Gestão - Agosto 2026.pptx</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>pptx</t>
+        </is>
+      </c>
+      <c r="C40" t="n">
+        <v>47671</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>tivio-construtor-one-pager.html</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>html</t>
+        </is>
+      </c>
+      <c r="C41" t="n">
+        <v>87214</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>tivio-email-fundos-credito.html</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>html</t>
+        </is>
+      </c>
+      <c r="C42" t="n">
+        <v>130847</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>tivio-email-nordea-studio.html</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>html</t>
+        </is>
+      </c>
+      <c r="C43" t="n">
+        <v>49750</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>tivio-post-credito-estruturado.html</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>html</t>
+        </is>
+      </c>
+      <c r="C44" t="n">
+        <v>113275</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>tivio-post-credito-privado.html</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>html</t>
+        </is>
+      </c>
+      <c r="C45" t="n">
+        <v>126107</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>tivio-post-investment-solutions.html</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>html</t>
+        </is>
+      </c>
+      <c r="C46" t="n">
+        <v>103643</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>tivio-relatorio-gestao-credito-privado.html</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>html</t>
+        </is>
+      </c>
+      <c r="C47" t="n">
+        <v>121698</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>tivio-central.html</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>html</t>
+        </is>
+      </c>
+      <c r="C48" t="n">
+        <v>71673</v>
       </c>
     </row>
   </sheetData>

--- a/AutomaTivio/reports/2026-08/conferencia_2026-08.xlsx
+++ b/AutomaTivio/reports/2026-08/conferencia_2026-08.xlsx
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E223"/>
+  <dimension ref="A1:E231"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -808,7 +808,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>[['Fundo', '0,72%', '9,51%', '−', '−', '−', '12,60%', True], ['CDI', '1,09%', '9,33%', '−', '−', '−', '11,40%', False], ['CDI+', '−4,38%', '0,25%', '−', '−', '−', '1,36%', False], ['%', '66%', '102%', '−', '−', '−', '111%', False]]</t>
+          <t>[['Fundo', '0,72%', '9,51%', '−', '−', '−', '12,60%', True], ['CDI', '1,09%', '9,33%', '−', '−', '−', '11,40%', False], ['CDI+', '−4,38%', '0,25%', '−', '−', '−', '1,36%', False], ['%', '65,59%', '101,93%', '−', '−', '−', '110,53%', False]]</t>
         </is>
       </c>
     </row>
@@ -862,7 +862,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>O TIVIO ALT LIGHT rendeu 0,72% no mês (66% do CDI), acumulando 9,51% no ano e 12,60% desde o início (CDI+1,36% ao ano). A parcela de debêntures foi a principal contribuidora, seguida pela parcela de crédito estruturado.</t>
+          <t>O TIVIO ALT LIGHT rendeu 0,72% no mês (65,59% do CDI), acumulando 9,51% no ano e 12,60% desde o início (CDI+1,36% ao ano). A parcela de debêntures foi a principal contribuidora, seguida pela parcela de crédito estruturado.</t>
         </is>
       </c>
     </row>
@@ -889,7 +889,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>[['Fundo', '1,30%', '11,19%', '18,11%', '−', '−', '33,14%', True], ['CDI', '1,09%', '9,33%', '14,57%', '−', '−', '25,43%', False], ['CDI+', '2,48%', '2,59%', '3,10%', '−', '−', '3,60%', False], ['%', '119%', '120%', '124%', '−', '−', '130%', False]]</t>
+          <t>[['Fundo', '1,30%', '11,19%', '18,11%', '−', '−', '33,14%', True], ['CDI', '1,09%', '9,33%', '14,57%', '−', '−', '25,43%', False], ['CDI+', '2,48%', '2,59%', '3,10%', '−', '−', '3,60%', False], ['%', '118,88%', '119,92%', '124,27%', '−', '−', '130,33%', False]]</t>
         </is>
       </c>
     </row>
@@ -943,7 +943,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>O TIVIO ALT 180 rendeu 1,30% no mês (119% do CDI), acumulando 11,19% no ano e 33,14% desde o início (CDI+3,60% ao ano). Em julho aumentamos a exposição a FIDCs de Consignado Público, com elevada pulverização e baixa inadimplência.</t>
+          <t>O TIVIO ALT 180 rendeu 1,30% no mês (118,88% do CDI), acumulando 11,19% no ano e 33,14% desde o início (CDI+3,60% ao ano). Em julho aumentamos a exposição a FIDCs de Consignado Público, com elevada pulverização e baixa inadimplência.</t>
         </is>
       </c>
     </row>
@@ -970,7 +970,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>[['Fundo', '1,22%', '10,40%', '16,49%', '−', '−', '21,25%', True], ['CDI', '1,09%', '9,33%', '14,57%', '−', '−', '18,41%', False], ['CDI+', '1,55%', '1,49%', '1,68%', '−', '−', '1,94%', False], ['%', '112%', '111%', '113%', '−', '−', '115%', False]]</t>
+          <t>[['Fundo', '1,22%', '10,40%', '16,49%', '−', '−', '21,25%', True], ['CDI', '1,09%', '9,33%', '14,57%', '−', '−', '18,41%', False], ['CDI+', '1,55%', '1,49%', '1,68%', '−', '−', '1,94%', False], ['%', '111,86%', '111,49%', '113,19%', '−', '−', '115,41%', False]]</t>
         </is>
       </c>
     </row>
@@ -1024,7 +1024,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>O TIVIO ALT 90 rendeu 1,22% no mês (112% do CDI), acumulando 10,40% no ano e 21,25% desde o início (CDI+1,94% ao ano). A estratégia segue concentrada em FIDCs de cotas sênior, buscando retorno superior ao CDI com baixa volatilidade.</t>
+          <t>O TIVIO ALT 90 rendeu 1,22% no mês (111,86% do CDI), acumulando 10,40% no ano e 21,25% desde o início (CDI+1,94% ao ano). A estratégia segue concentrada em FIDCs de cotas sênior, buscando retorno superior ao CDI com baixa volatilidade.</t>
         </is>
       </c>
     </row>
@@ -1402,7 +1402,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>124%</t>
+          <t>124,27%</t>
         </is>
       </c>
     </row>
@@ -1419,17 +1419,17 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>alloc</t>
+          <t>v2</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>[{'n': 'FIDCs Cotas Sênior', 'p': 49.6}, {'n': 'FIDCs Cotas Mezanino', 'p': 27.5}, {'n': 'Liquidez', 'p': 9.3}, {'n': 'Crédito Estruturado', 'p': 5.5}, {'n': 'Crédito Privado', 'p': 3.5}, {'n': 'Precatório', 'p': 2.8}, {'n': 'Fiagro', 'p': 2.0}]</t>
+          <t>120%</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>[{'n': 'FIDCs Cotas Sênior', 'p': 46.9}, {'n': 'FIDCs Cotas Mezanino', 'p': 27.0}, {'n': 'Bancário', 'p': 6.1}, {'n': 'Fiagro', 'p': 5.5}, {'n': 'Liquidez', 'p': 5.3}, {'n': 'Crédito Privado', 'p': 3.4}, {'n': 'Precatório', 'p': 2.7}, {'n': 'Crédito Estruturado', 'p': 2.6}]</t>
+          <t>119,92%</t>
         </is>
       </c>
     </row>
@@ -1446,17 +1446,17 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>taxas</t>
+          <t>v3</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Taxa de administração e gestão: 1,15% a.a. Taxa de performance: 20% do que exceder do CDI. Resgate: D+180.</t>
+          <t>119%</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Taxa global: 1,15% a.a. Taxa de performance: 20% do que exceder do CDI. Resgate: D+180.</t>
+          <t>118,88%</t>
         </is>
       </c>
     </row>
@@ -1468,22 +1468,22 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>alt90</t>
+          <t>alt180</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>b1val</t>
+          <t>alloc</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>R$ 19.936.394,95</t>
+          <t>[{'n': 'FIDCs Cotas Sênior', 'p': 49.6}, {'n': 'FIDCs Cotas Mezanino', 'p': 27.5}, {'n': 'Liquidez', 'p': 9.3}, {'n': 'Crédito Estruturado', 'p': 5.5}, {'n': 'Crédito Privado', 'p': 3.5}, {'n': 'Precatório', 'p': 2.8}, {'n': 'Fiagro', 'p': 2.0}]</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>R$ 19.959.710,82</t>
+          <t>[{'n': 'FIDCs Cotas Sênior', 'p': 46.9}, {'n': 'FIDCs Cotas Mezanino', 'p': 27.0}, {'n': 'Bancário', 'p': 6.1}, {'n': 'Fiagro', 'p': 5.5}, {'n': 'Liquidez', 'p': 5.3}, {'n': 'Crédito Privado', 'p': 3.4}, {'n': 'Precatório', 'p': 2.7}, {'n': 'Crédito Estruturado', 'p': 2.6}]</t>
         </is>
       </c>
     </row>
@@ -1495,22 +1495,22 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>alt90</t>
+          <t>alt180</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>b2val</t>
+          <t>taxas</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>R$ 14.275.935,66</t>
+          <t>Taxa de administração e gestão: 1,15% a.a. Taxa de performance: 20% do que exceder do CDI. Resgate: D+180.</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>R$ 15.653.770,20</t>
+          <t>Taxa global: 1,15% a.a. Taxa de performance: 20% do que exceder do CDI. Resgate: D+180.</t>
         </is>
       </c>
     </row>
@@ -1527,17 +1527,17 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>v1</t>
+          <t>b1val</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>114%</t>
+          <t>R$ 19.936.394,95</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>113%</t>
+          <t>R$ 19.959.710,82</t>
         </is>
       </c>
     </row>
@@ -1554,17 +1554,17 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>alloc</t>
+          <t>b2val</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>[{'n': 'FIDCs Cotas Sênior', 'p': 81.3}, {'n': 'Liquidez', 'p': 11.9}, {'n': 'Crédito Privado', 'p': 3.6}, {'n': 'Crédito Estruturado', 'p': 2.8}, {'n': 'FIDC Mezanino', 'p': 0.6}]</t>
+          <t>R$ 14.275.935,66</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>[{'n': 'FIDCs Cotas Sênior', 'p': 82.9}, {'n': 'Bancário', 'p': 8.3}, {'n': 'Crédito Privado', 'p': 3.6}, {'n': 'Fiagro', 'p': 2.9}, {'n': 'Liquidez', 'p': 1.9}, {'n': 'FIDCs Cotas Mezanino', 'p': 0.6}]</t>
+          <t>R$ 15.653.770,20</t>
         </is>
       </c>
     </row>
@@ -1581,17 +1581,17 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>taxas</t>
+          <t>v1</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Taxa de administração e gestão: 1,25% a.a. Taxa de performance: 10% do que exceder do CDI. Resgate: D+90.</t>
+          <t>114%</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Taxa global: 2,43% a.a. Taxa de performance: 10% do que exceder do CDI. Resgate: D+90.</t>
+          <t>113,19%</t>
         </is>
       </c>
     </row>
@@ -1603,22 +1603,22 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>altlight</t>
+          <t>alt90</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>b1val</t>
+          <t>v2</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>R$ 26.861.672,93</t>
+          <t>111%</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>R$ 26.829.258,71</t>
+          <t>111,49%</t>
         </is>
       </c>
     </row>
@@ -1630,22 +1630,22 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>altlight</t>
+          <t>alt90</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>b2val</t>
+          <t>v3</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>R$ 17.309.791,01</t>
+          <t>112%</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>R$ 18.304.046,83</t>
+          <t>111,86%</t>
         </is>
       </c>
     </row>
@@ -1657,22 +1657,22 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>altlight</t>
+          <t>alt90</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>v1</t>
+          <t>alloc</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>116%</t>
+          <t>[{'n': 'FIDCs Cotas Sênior', 'p': 81.3}, {'n': 'Liquidez', 'p': 11.9}, {'n': 'Crédito Privado', 'p': 3.6}, {'n': 'Crédito Estruturado', 'p': 2.8}, {'n': 'FIDC Mezanino', 'p': 0.6}]</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>111%</t>
+          <t>[{'n': 'FIDCs Cotas Sênior', 'p': 82.9}, {'n': 'Bancário', 'p': 8.3}, {'n': 'Crédito Privado', 'p': 3.6}, {'n': 'Fiagro', 'p': 2.9}, {'n': 'Liquidez', 'p': 1.9}, {'n': 'FIDCs Cotas Mezanino', 'p': 0.6}]</t>
         </is>
       </c>
     </row>
@@ -1684,22 +1684,22 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>altlight</t>
+          <t>alt90</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>v2</t>
+          <t>taxas</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>107%</t>
+          <t>Taxa de administração e gestão: 1,25% a.a. Taxa de performance: 10% do que exceder do CDI. Resgate: D+90.</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>102%</t>
+          <t>Taxa global: 2,43% a.a. Taxa de performance: 10% do que exceder do CDI. Resgate: D+90.</t>
         </is>
       </c>
     </row>
@@ -1716,17 +1716,17 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>v3</t>
+          <t>b1val</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>101%</t>
+          <t>R$ 26.861.672,93</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>66%</t>
+          <t>R$ 26.829.258,71</t>
         </is>
       </c>
     </row>
@@ -1743,17 +1743,17 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>alloc</t>
+          <t>b2val</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>[{'n': 'Bancário', 'p': 40.8}, {'n': 'Crédito Privado', 'p': 25.6}, {'n': 'FIDCs Cotas Sênior', 'p': 24.0}, {'n': 'Liquidez', 'p': 7.8}, {'n': 'FIP', 'p': 1.9}]</t>
+          <t>R$ 17.309.791,01</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>[{'n': 'Bancário', 'p': 40.7}, {'n': 'Crédito Privado', 'p': 25.8}, {'n': 'FIDCs Cotas Sênior', 'p': 23.5}, {'n': 'Liquidez', 'p': 7.8}, {'n': 'Ações', 'p': 1.9}]</t>
+          <t>R$ 18.304.046,83</t>
         </is>
       </c>
     </row>
@@ -1770,17 +1770,17 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>taxas</t>
+          <t>v1</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Taxa de administração e gestão: 1,15% a.a. Taxa de performance: 15% do retorno que exceder CDI+0,65%.</t>
+          <t>116%</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Taxa global: 0,65% a.a. Taxa de performance: não há.</t>
+          <t>110,53%</t>
         </is>
       </c>
     </row>
@@ -1792,22 +1792,22 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>altlight</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>v2</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>31/07/2026</t>
+          <t>107%</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>31/08/2026</t>
+          <t>101,93%</t>
         </is>
       </c>
     </row>
@@ -1819,22 +1819,22 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>altlight</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>v3</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Julho de 2026</t>
+          <t>101%</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Agosto de 2026</t>
+          <t>65,59%</t>
         </is>
       </c>
     </row>
@@ -1846,22 +1846,22 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>altlight</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>alloc</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>julho de 2026</t>
+          <t>[{'n': 'Bancário', 'p': 40.8}, {'n': 'Crédito Privado', 'p': 25.6}, {'n': 'FIDCs Cotas Sênior', 'p': 24.0}, {'n': 'Liquidez', 'p': 7.8}, {'n': 'FIP', 'p': 1.9}]</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>agosto de 2026</t>
+          <t>[{'n': 'Bancário', 'p': 40.7}, {'n': 'Crédito Privado', 'p': 25.8}, {'n': 'FIDCs Cotas Sênior', 'p': 23.5}, {'n': 'Liquidez', 'p': 7.8}, {'n': 'Ações', 'p': 1.9}]</t>
         </is>
       </c>
     </row>
@@ -1873,22 +1873,22 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>altlight</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>taxas</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>JULHO DE 2026</t>
+          <t>Taxa de administração e gestão: 1,15% a.a. Taxa de performance: 15% do retorno que exceder CDI+0,65%.</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AGOSTO DE 2026</t>
+          <t>Taxa global: 0,65% a.a. Taxa de performance: não há.</t>
         </is>
       </c>
     </row>
@@ -1910,12 +1910,12 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Julho 2026</t>
+          <t>31/07/2026</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Agosto 2026</t>
+          <t>31/08/2026</t>
         </is>
       </c>
     </row>
@@ -1937,12 +1937,12 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>-jul26</t>
+          <t>Julho de 2026</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>-ago26</t>
+          <t>Agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -1964,12 +1964,12 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>const ATUAL=6;</t>
+          <t>julho de 2026</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>const ATUAL=7;</t>
+          <t>agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -1986,125 +1986,125 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>libs de exportação</t>
+          <t>data</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>CDN</t>
+          <t>JULHO DE 2026</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>4 referências → vendor/ local (CDN como reserva)</t>
+          <t>AGOSTO DE 2026</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>tivio-post-credito-privado.html</t>
+          <t>tivio-post-credito-estruturado.html</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>banks</t>
+          <t>—</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>pl</t>
+          <t>data</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>R$ 1.698.520.740,05</t>
+          <t>Julho 2026</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>R$ 1.793.381.077,96</t>
+          <t>Agosto 2026</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>tivio-post-credito-privado.html</t>
+          <t>tivio-post-credito-estruturado.html</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>banks</t>
+          <t>—</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>plm</t>
+          <t>data</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>R$ 1.397.203.402,03</t>
+          <t>-jul26</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>R$ 1.449.683.179,97</t>
+          <t>-ago26</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>tivio-post-credito-privado.html</t>
+          <t>tivio-post-credito-estruturado.html</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>banks</t>
+          <t>—</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>alloc</t>
+          <t>data</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>{'total': '76', 'top': [{'p': '76,5%', 'n': 'financeiro'}, {'p': '23,7%', 'n': 'caixa'}]}</t>
+          <t>const ATUAL=6;</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>{'total': '76', 'top': [{'p': '76%', 'n': 'financeiro'}]}</t>
+          <t>const ATUAL=7;</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>tivio-post-credito-privado.html</t>
+          <t>tivio-post-credito-estruturado.html</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>banks</t>
+          <t>—</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>val</t>
+          <t>libs de exportação</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>0,26</t>
+          <t>CDN</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>0,25</t>
+          <t>4 referências → vendor/ local (CDN como reserva)</t>
         </is>
       </c>
     </row>
@@ -2121,17 +2121,17 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>val</t>
+          <t>pl</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>1,12</t>
+          <t>R$ 1.698.520.740,05</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>1,05</t>
+          <t>R$ 1.793.381.077,96</t>
         </is>
       </c>
     </row>
@@ -2148,17 +2148,17 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>taxas</t>
+          <t>plm</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Taxa de administração: 0,25% a.a. Taxa de performance: não há. Aplicação: D+0 · Resgate: D+0.</t>
+          <t>R$ 1.397.203.402,03</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Taxa global: 0,25% a.a. Taxa de performance: não há. Aplicação: D+0 · Resgate: D+0.</t>
+          <t>R$ 1.449.683.179,97</t>
         </is>
       </c>
     </row>
@@ -2170,22 +2170,22 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>institucional</t>
+          <t>banks</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>v3</t>
+          <t>alloc</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>104%</t>
+          <t>{'total': '76', 'top': [{'p': '76,5%', 'n': 'financeiro'}, {'p': '23,7%', 'n': 'caixa'}]}</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>{'total': '76', 'top': [{'p': '76%', 'n': 'financeiro'}]}</t>
         </is>
       </c>
     </row>
@@ -2197,22 +2197,22 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>institucional</t>
+          <t>banks</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>pl</t>
+          <t>val</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>R$ 1.983.487.947,49</t>
+          <t>0,26</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>R$ 1.815.644.128,24</t>
+          <t>0,25</t>
         </is>
       </c>
     </row>
@@ -2224,22 +2224,22 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>institucional</t>
+          <t>banks</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>plm</t>
+          <t>val</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>R$ 2.522.009.705,73</t>
+          <t>1,12</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>R$ 2.491.331.200,61</t>
+          <t>1,05</t>
         </is>
       </c>
     </row>
@@ -2251,22 +2251,22 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>institucional</t>
+          <t>banks</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>alloc</t>
+          <t>taxas</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>{'total': '69', 'top': [{'p': '52%', 'n': 'financeiro'}, {'p': '4%', 'n': 'energia elétrica'}, {'p': '2%', 'n': 'transporte e logística'}]}</t>
+          <t>Taxa de administração: 0,25% a.a. Taxa de performance: não há. Aplicação: D+0 · Resgate: D+0.</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>{'total': '61', 'top': [{'p': '45%', 'n': 'financeiro'}, {'p': '5%', 'n': 'energia elétrica'}, {'p': '2%', 'n': 'FIDC'}]}</t>
+          <t>Taxa global: 0,25% a.a. Taxa de performance: não há. Aplicação: D+0 · Resgate: D+0.</t>
         </is>
       </c>
     </row>
@@ -2283,17 +2283,17 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>val</t>
+          <t>v3</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>0,44</t>
+          <t>104%</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>0,39</t>
+          <t>100%</t>
         </is>
       </c>
     </row>
@@ -2310,17 +2310,17 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>val</t>
+          <t>pl</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>1,20</t>
+          <t>R$ 1.983.487.947,49</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>1,28</t>
+          <t>R$ 1.815.644.128,24</t>
         </is>
       </c>
     </row>
@@ -2337,17 +2337,17 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>taxas</t>
+          <t>plm</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Taxa de administração: 0,20% a.a. Taxa de performance: não há. Aplicação: D+0 · Resgate: D+0.</t>
+          <t>R$ 2.522.009.705,73</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Taxa global: 0,20% a.a. Taxa de performance: não há. Aplicação: D+0 · Resgate: D+0.</t>
+          <t>R$ 2.491.331.200,61</t>
         </is>
       </c>
     </row>
@@ -2359,22 +2359,22 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>inst15</t>
+          <t>institucional</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>v1</t>
+          <t>alloc</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>102%</t>
+          <t>{'total': '69', 'top': [{'p': '52%', 'n': 'financeiro'}, {'p': '4%', 'n': 'energia elétrica'}, {'p': '2%', 'n': 'transporte e logística'}]}</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>103%</t>
+          <t>{'total': '61', 'top': [{'p': '45%', 'n': 'financeiro'}, {'p': '5%', 'n': 'energia elétrica'}, {'p': '2%', 'n': 'FIDC'}]}</t>
         </is>
       </c>
     </row>
@@ -2386,22 +2386,22 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>inst15</t>
+          <t>institucional</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>v3</t>
+          <t>val</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>113%</t>
+          <t>0,44</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>102%</t>
+          <t>0,39</t>
         </is>
       </c>
     </row>
@@ -2413,22 +2413,22 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>inst15</t>
+          <t>institucional</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>pl</t>
+          <t>val</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>R$ 161.593.743,98</t>
+          <t>1,20</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>R$ 156.046.891,63</t>
+          <t>1,28</t>
         </is>
       </c>
     </row>
@@ -2440,22 +2440,22 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>inst15</t>
+          <t>institucional</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>plm</t>
+          <t>taxas</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>R$ 140.997.685,81</t>
+          <t>Taxa de administração: 0,20% a.a. Taxa de performance: não há. Aplicação: D+0 · Resgate: D+0.</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>R$ 146.843.921,67</t>
+          <t>Taxa global: 0,20% a.a. Taxa de performance: não há. Aplicação: D+0 · Resgate: D+0.</t>
         </is>
       </c>
     </row>
@@ -2472,17 +2472,17 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>alloc</t>
+          <t>v1</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>{'total': '74', 'top': [{'p': '29%', 'n': 'financeiro'}, {'p': '13%', 'n': 'FIDC'}, {'p': '7%', 'n': 'energia elétrica'}]}</t>
+          <t>102%</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>{'total': '73', 'top': [{'p': '28%', 'n': 'financeiro'}, {'p': '13%', 'n': 'FIDC'}, {'p': '7%', 'n': 'energia elétrica'}]}</t>
+          <t>103%</t>
         </is>
       </c>
     </row>
@@ -2499,17 +2499,17 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>val</t>
+          <t>v3</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>1,00</t>
+          <t>113%</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>0,95</t>
+          <t>102%</t>
         </is>
       </c>
     </row>
@@ -2526,17 +2526,17 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>val</t>
+          <t>pl</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>1,97</t>
+          <t>R$ 161.593.743,98</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>1,80</t>
+          <t>R$ 156.046.891,63</t>
         </is>
       </c>
     </row>
@@ -2553,17 +2553,17 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>unit</t>
+          <t>plm</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>anos</t>
+          <t>R$ 140.997.685,81</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>ano</t>
+          <t>R$ 146.843.921,67</t>
         </is>
       </c>
     </row>
@@ -2580,17 +2580,17 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>taxas</t>
+          <t>alloc</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Taxa de administração: 0,45% a.a. Taxa de performance: não há. Aplicação: D+0 · Resgate: D+0.</t>
+          <t>{'total': '74', 'top': [{'p': '29%', 'n': 'financeiro'}, {'p': '13%', 'n': 'FIDC'}, {'p': '7%', 'n': 'energia elétrica'}]}</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Taxa global: 0,50% a.a. Taxa de performance: 20% do que exceder 102,5% do CDI. Aplicação: D+0 · Resgate: D+0.</t>
+          <t>{'total': '73', 'top': [{'p': '28%', 'n': 'financeiro'}, {'p': '13%', 'n': 'FIDC'}, {'p': '7%', 'n': 'energia elétrica'}]}</t>
         </is>
       </c>
     </row>
@@ -2602,22 +2602,22 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>inst30</t>
+          <t>inst15</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>v3</t>
+          <t>val</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>113%</t>
+          <t>1,00</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>102%</t>
+          <t>0,95</t>
         </is>
       </c>
     </row>
@@ -2629,22 +2629,22 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>inst30</t>
+          <t>inst15</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>pl</t>
+          <t>val</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>R$ 143.232.764,20</t>
+          <t>1,97</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>R$ 126.168.780,56</t>
+          <t>1,80</t>
         </is>
       </c>
     </row>
@@ -2656,22 +2656,22 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>inst30</t>
+          <t>inst15</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>plm</t>
+          <t>unit</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>R$ 155.004.649,74</t>
+          <t>anos</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>R$ 158.893.390,74</t>
+          <t>ano</t>
         </is>
       </c>
     </row>
@@ -2683,22 +2683,22 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>inst30</t>
+          <t>inst15</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>alloc</t>
+          <t>taxas</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>{'total': '84', 'top': [{'p': '33%', 'n': 'financeiro'}, {'p': '15%', 'n': 'FIDC'}, {'p': '8%', 'n': 'energia elétrica'}]}</t>
+          <t>Taxa de administração: 0,45% a.a. Taxa de performance: não há. Aplicação: D+0 · Resgate: D+0.</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>{'total': '80', 'top': [{'p': '31%', 'n': 'financeiro'}, {'p': '14%', 'n': 'FIDC'}, {'p': '8%', 'n': 'energia elétrica'}]}</t>
+          <t>Taxa global: 0,50% a.a. Taxa de performance: 20% do que exceder 102,5% do CDI. Aplicação: D+0 · Resgate: D+0.</t>
         </is>
       </c>
     </row>
@@ -2715,17 +2715,17 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>val</t>
+          <t>v3</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>113%</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>1,04</t>
+          <t>102%</t>
         </is>
       </c>
     </row>
@@ -2742,17 +2742,17 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>val</t>
+          <t>pl</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>R$ 143.232.764,20</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>1,86</t>
+          <t>R$ 126.168.780,56</t>
         </is>
       </c>
     </row>
@@ -2769,17 +2769,17 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>unit</t>
+          <t>plm</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>anos</t>
+          <t>R$ 155.004.649,74</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>ano</t>
+          <t>R$ 158.893.390,74</t>
         </is>
       </c>
     </row>
@@ -2796,17 +2796,17 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>taxas</t>
+          <t>alloc</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>Taxa de administração: 0,63% a.a. Taxa de performance: 20% do que exceder o CDI. Resgate: D+30.</t>
+          <t>{'total': '84', 'top': [{'p': '33%', 'n': 'financeiro'}, {'p': '15%', 'n': 'FIDC'}, {'p': '8%', 'n': 'energia elétrica'}]}</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Taxa global: 0,625% a.a. Taxa de performance: 20% do que exceder 100% do CDI. Resgate: D+30.</t>
+          <t>{'total': '80', 'top': [{'p': '31%', 'n': 'financeiro'}, {'p': '14%', 'n': 'FIDC'}, {'p': '8%', 'n': 'energia elétrica'}]}</t>
         </is>
       </c>
     </row>
@@ -2818,22 +2818,22 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>infraplus</t>
+          <t>inst30</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>v1</t>
+          <t>val</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>12,94%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>9,91%</t>
+          <t>1,04</t>
         </is>
       </c>
     </row>
@@ -2845,22 +2845,22 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>infraplus</t>
+          <t>inst30</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>a1</t>
+          <t>val</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>*Alfa: -2,75%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>*Alfa: −3,44%</t>
+          <t>1,86</t>
         </is>
       </c>
     </row>
@@ -2872,22 +2872,22 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>infraplus</t>
+          <t>inst30</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>v2</t>
+          <t>unit</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>7,80%</t>
+          <t>anos</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>5,98%</t>
+          <t>ano</t>
         </is>
       </c>
     </row>
@@ -2899,22 +2899,22 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>infraplus</t>
+          <t>inst30</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>a2</t>
+          <t>taxas</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>*Alfa: -3,14%</t>
+          <t>Taxa de administração: 0,63% a.a. Taxa de performance: 20% do que exceder o CDI. Resgate: D+30.</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>*Alfa: −3,20%</t>
+          <t>Taxa global: 0,625% a.a. Taxa de performance: 20% do que exceder 100% do CDI. Resgate: D+30.</t>
         </is>
       </c>
     </row>
@@ -2931,17 +2931,17 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>v3</t>
+          <t>v1</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>12,94%</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>9,91%</t>
         </is>
       </c>
     </row>
@@ -2958,17 +2958,17 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>a3</t>
+          <t>a1</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>*Alfa: -0,14%</t>
+          <t>*Alfa: -2,75%</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>*Alfa: −0,01%</t>
+          <t>*Alfa: −3,44%</t>
         </is>
       </c>
     </row>
@@ -2985,17 +2985,17 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>pl</t>
+          <t>v2</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>R$ 42.983.282,75</t>
+          <t>7,80%</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>R$ 42.694.019,75</t>
+          <t>5,98%</t>
         </is>
       </c>
     </row>
@@ -3012,17 +3012,17 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>plm</t>
+          <t>a2</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>R$ 52.049.593,91</t>
+          <t>*Alfa: -3,14%</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>R$ 49.421.174,50</t>
+          <t>*Alfa: −3,20%</t>
         </is>
       </c>
     </row>
@@ -3039,17 +3039,17 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>alloc</t>
+          <t>v3</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>{'total': '95', 'top': [{'p': '55%', 'n': 'energia elétrica'}, {'p': '15%', 'n': 'transporte e logística'}, {'p': '7%', 'n': 'saneamento'}]}</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>{'total': '97', 'top': [{'p': '56%', 'n': 'energia elétrica'}, {'p': '15%', 'n': 'transporte e logística'}, {'p': '7%', 'n': 'saneamento'}]}</t>
+          <t>1,26%</t>
         </is>
       </c>
     </row>
@@ -3066,17 +3066,17 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>val</t>
+          <t>a3</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>8,63</t>
+          <t>*Alfa: -0,14%</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>8,23</t>
+          <t>*Alfa: −0,01%</t>
         </is>
       </c>
     </row>
@@ -3093,17 +3093,17 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>val</t>
+          <t>pl</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>4,00</t>
+          <t>R$ 42.983.282,75</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>3,98</t>
+          <t>R$ 42.694.019,75</t>
         </is>
       </c>
     </row>
@@ -3120,17 +3120,17 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>taxas</t>
+          <t>plm</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>Taxa de administração: 0,75% a.a. Taxa de performance: não há. Resgate: D+31. Rentabilidade isenta de IR para pessoa física.</t>
+          <t>R$ 52.049.593,91</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Taxa global: 0,75% a.a. Taxa de performance: não há. Resgate: D+31. Rentabilidade isenta de IR para pessoa física.</t>
+          <t>R$ 49.421.174,50</t>
         </is>
       </c>
     </row>
@@ -3142,22 +3142,22 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>infraplus</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>alloc</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>31/07/2026</t>
+          <t>{'total': '95', 'top': [{'p': '55%', 'n': 'energia elétrica'}, {'p': '15%', 'n': 'transporte e logística'}, {'p': '7%', 'n': 'saneamento'}]}</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>31/08/2026</t>
+          <t>{'total': '97', 'top': [{'p': '56%', 'n': 'energia elétrica'}, {'p': '15%', 'n': 'transporte e logística'}, {'p': '7%', 'n': 'saneamento'}]}</t>
         </is>
       </c>
     </row>
@@ -3169,22 +3169,22 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>infraplus</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>val</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>Julho de 2026</t>
+          <t>8,63</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Agosto de 2026</t>
+          <t>8,23</t>
         </is>
       </c>
     </row>
@@ -3196,22 +3196,22 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>infraplus</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>val</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>julho de 2026</t>
+          <t>4,00</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>agosto de 2026</t>
+          <t>3,98</t>
         </is>
       </c>
     </row>
@@ -3223,22 +3223,22 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>infraplus</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>taxas</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>JULHO DE 2026</t>
+          <t>Taxa de administração: 0,75% a.a. Taxa de performance: não há. Resgate: D+31. Rentabilidade isenta de IR para pessoa física.</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>AGOSTO DE 2026</t>
+          <t>Taxa global: 0,75% a.a. Taxa de performance: não há. Resgate: D+31. Rentabilidade isenta de IR para pessoa física.</t>
         </is>
       </c>
     </row>
@@ -3260,12 +3260,12 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>Julho 2026</t>
+          <t>31/07/2026</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Agosto 2026</t>
+          <t>31/08/2026</t>
         </is>
       </c>
     </row>
@@ -3287,12 +3287,12 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>-jul26</t>
+          <t>Julho de 2026</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>-ago26</t>
+          <t>Agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -3314,12 +3314,12 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>const ATUAL=6;</t>
+          <t>julho de 2026</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>const ATUAL=7;</t>
+          <t>agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -3336,125 +3336,125 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>libs de exportação</t>
+          <t>data</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>CDN</t>
+          <t>JULHO DE 2026</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>4 referências → vendor/ local (CDN como reserva)</t>
+          <t>AGOSTO DE 2026</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>tivio-post-investment-solutions.html</t>
+          <t>tivio-post-credito-privado.html</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>topgestor</t>
+          <t>—</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>v1</t>
+          <t>data</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>103%</t>
+          <t>Julho 2026</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>91%</t>
+          <t>Agosto 2026</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>tivio-post-investment-solutions.html</t>
+          <t>tivio-post-credito-privado.html</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>topgestor</t>
+          <t>—</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>v2</t>
+          <t>data</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>101%</t>
+          <t>-jul26</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>-ago26</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>tivio-post-investment-solutions.html</t>
+          <t>tivio-post-credito-privado.html</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>topgestor</t>
+          <t>—</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>v3</t>
+          <t>data</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>101%</t>
+          <t>const ATUAL=6;</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>const ATUAL=7;</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>tivio-post-investment-solutions.html</t>
+          <t>tivio-post-credito-privado.html</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>topgestor</t>
+          <t>—</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>plm</t>
+          <t>libs de exportação</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>R$ 352,4 mi</t>
+          <t>CDN</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>R$ 350,1 mi</t>
+          <t>4 referências → vendor/ local (CDN como reserva)</t>
         </is>
       </c>
     </row>
@@ -3466,7 +3466,7 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>topgestorhy</t>
+          <t>topgestor</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
@@ -3476,12 +3476,12 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>104%</t>
+          <t>103%</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>91%</t>
         </is>
       </c>
     </row>
@@ -3493,7 +3493,7 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>topgestorhy</t>
+          <t>topgestor</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
@@ -3503,12 +3503,12 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>106%</t>
+          <t>101%</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>105%</t>
+          <t>100%</t>
         </is>
       </c>
     </row>
@@ -3520,7 +3520,7 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>topgestorhy</t>
+          <t>topgestor</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
@@ -3530,12 +3530,12 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>109%</t>
+          <t>101%</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>107%</t>
+          <t>100%</t>
         </is>
       </c>
     </row>
@@ -3547,7 +3547,7 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>topgestorhy</t>
+          <t>topgestor</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
@@ -3557,12 +3557,12 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>R$ 33,2 mi</t>
+          <t>R$ 352,4 mi</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>R$ 35,7 mi</t>
+          <t>R$ 350,1 mi</t>
         </is>
       </c>
     </row>
@@ -3574,22 +3574,22 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>topgestorativo</t>
+          <t>topgestorhy</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>adm</t>
+          <t>v1</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>0,00% a.a. (vértice tx zero)</t>
+          <t>104%</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>0,15% a.a.</t>
+          <t>100%</t>
         </is>
       </c>
     </row>
@@ -3601,22 +3601,22 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>topgestorativo</t>
+          <t>topgestorhy</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>v1</t>
+          <t>v2</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>93%</t>
+          <t>106%</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>99%</t>
+          <t>105%</t>
         </is>
       </c>
     </row>
@@ -3628,22 +3628,22 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>topgestorativo</t>
+          <t>topgestorhy</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>v2</t>
+          <t>v3</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>86%</t>
+          <t>109%</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>87%</t>
+          <t>107%</t>
         </is>
       </c>
     </row>
@@ -3655,7 +3655,7 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>topgestorativo</t>
+          <t>topgestorhy</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
@@ -3665,12 +3665,12 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>R$ 374,3 mi</t>
+          <t>R$ 33,2 mi</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>R$ 353,7 mi</t>
+          <t>R$ 35,7 mi</t>
         </is>
       </c>
     </row>
@@ -3682,22 +3682,22 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>topgestorlongonly</t>
+          <t>topgestorativo</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>v1</t>
+          <t>adm</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>43%</t>
+          <t>0,00% a.a. (vértice tx zero)</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>370%</t>
+          <t>0,15% a.a.</t>
         </is>
       </c>
     </row>
@@ -3709,22 +3709,22 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>topgestorlongonly</t>
+          <t>topgestorativo</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>v2</t>
+          <t>v1</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>44%</t>
+          <t>93%</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>33%</t>
+          <t>99%</t>
         </is>
       </c>
     </row>
@@ -3736,22 +3736,22 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>topgestorlongonly</t>
+          <t>topgestorativo</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>v3</t>
+          <t>v2</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>70%</t>
+          <t>86%</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>53%</t>
+          <t>87%</t>
         </is>
       </c>
     </row>
@@ -3763,7 +3763,7 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>topgestorlongonly</t>
+          <t>topgestorativo</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
@@ -3773,12 +3773,12 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>R$ 95,0 mi</t>
+          <t>R$ 374,3 mi</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>R$ 91,4 mi</t>
+          <t>R$ 353,7 mi</t>
         </is>
       </c>
     </row>
@@ -3790,7 +3790,7 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>topmanagerglobal</t>
+          <t>topgestorlongonly</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
@@ -3800,12 +3800,12 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>2,13%</t>
+          <t>43%</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>4,88%</t>
+          <t>370%</t>
         </is>
       </c>
     </row>
@@ -3817,22 +3817,22 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>topmanagerglobal</t>
+          <t>topgestorlongonly</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>a1</t>
+          <t>v2</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>*Alfa: −3,03%</t>
+          <t>44%</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>*Alfa: 0,21%</t>
+          <t>33%</t>
         </is>
       </c>
     </row>
@@ -3844,22 +3844,22 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>topmanagerglobal</t>
+          <t>topgestorlongonly</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>v2</t>
+          <t>v3</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>−5,35%</t>
+          <t>70%</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>7,12%</t>
+          <t>53%</t>
         </is>
       </c>
     </row>
@@ -3871,22 +3871,22 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>topmanagerglobal</t>
+          <t>topgestorlongonly</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>a2</t>
+          <t>plm</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>*Alfa: −1,59%</t>
+          <t>R$ 95,0 mi</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>*Alfa: 0,45%</t>
+          <t>R$ 91,4 mi</t>
         </is>
       </c>
     </row>
@@ -3903,17 +3903,17 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>v3</t>
+          <t>v1</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>7,66%</t>
+          <t>2,13%</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>14,01%</t>
+          <t>4,88%</t>
         </is>
       </c>
     </row>
@@ -3930,17 +3930,17 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>a3</t>
+          <t>a1</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>*Alfa: −6,22%</t>
+          <t>*Alfa: −3,03%</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>*Alfa: −1,01%</t>
+          <t>*Alfa: 0,21%</t>
         </is>
       </c>
     </row>
@@ -3957,17 +3957,17 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>plm</t>
+          <t>v2</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>R$ 100,8 mi</t>
+          <t>−5,35%</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>R$ 77,4 mi</t>
+          <t>7,12%</t>
         </is>
       </c>
     </row>
@@ -3979,22 +3979,22 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>ativorf</t>
+          <t>topmanagerglobal</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>perf</t>
+          <t>a2</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>20% do que exceder o CDI</t>
+          <t>*Alfa: −1,59%</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>20% do que exceder 100% do CDI</t>
+          <t>*Alfa: 0,45%</t>
         </is>
       </c>
     </row>
@@ -4006,22 +4006,22 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>ativorf</t>
+          <t>topmanagerglobal</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>v1</t>
+          <t>v3</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>73%</t>
+          <t>7,66%</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>89%</t>
+          <t>14,01%</t>
         </is>
       </c>
     </row>
@@ -4033,22 +4033,22 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>ativorf</t>
+          <t>topmanagerglobal</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>v2</t>
+          <t>a3</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>74%</t>
+          <t>*Alfa: −6,22%</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>76%</t>
+          <t>*Alfa: −1,01%</t>
         </is>
       </c>
     </row>
@@ -4060,22 +4060,22 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>ativorf</t>
+          <t>topmanagerglobal</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>v3</t>
+          <t>plm</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>81%</t>
+          <t>R$ 100,8 mi</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>82%</t>
+          <t>R$ 77,4 mi</t>
         </is>
       </c>
     </row>
@@ -4092,17 +4092,17 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>plm</t>
+          <t>perf</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>R$ 102,7 mi</t>
+          <t>20% do que exceder o CDI</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>R$ 100,4 mi</t>
+          <t>20% do que exceder 100% do CDI</t>
         </is>
       </c>
     </row>
@@ -4114,7 +4114,7 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>prevlowvol</t>
+          <t>ativorf</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
@@ -4124,12 +4124,12 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>92%</t>
+          <t>73%</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>95%</t>
+          <t>89%</t>
         </is>
       </c>
     </row>
@@ -4141,22 +4141,22 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>prevlowvol</t>
+          <t>ativorf</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>plm</t>
+          <t>v2</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>R$ 662,8 mi</t>
+          <t>74%</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>R$ 650,1 mi</t>
+          <t>76%</t>
         </is>
       </c>
     </row>
@@ -4168,22 +4168,22 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>ativorf</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>v3</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>31/07/2026</t>
+          <t>81%</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>31/08/2026</t>
+          <t>82%</t>
         </is>
       </c>
     </row>
@@ -4195,22 +4195,22 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>ativorf</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>plm</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>Julho de 2026</t>
+          <t>R$ 102,7 mi</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Agosto de 2026</t>
+          <t>R$ 100,4 mi</t>
         </is>
       </c>
     </row>
@@ -4222,22 +4222,22 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>prevlowvol</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>v1</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>julho de 2026</t>
+          <t>92%</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>agosto de 2026</t>
+          <t>95%</t>
         </is>
       </c>
     </row>
@@ -4249,22 +4249,22 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>prevlowvol</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>plm</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>JULHO DE 2026</t>
+          <t>R$ 662,8 mi</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>AGOSTO DE 2026</t>
+          <t>R$ 650,1 mi</t>
         </is>
       </c>
     </row>
@@ -4286,12 +4286,12 @@
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>Julho 2026</t>
+          <t>31/07/2026</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Agosto 2026</t>
+          <t>31/08/2026</t>
         </is>
       </c>
     </row>
@@ -4313,12 +4313,12 @@
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>-jul26</t>
+          <t>Julho de 2026</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>-ago26</t>
+          <t>Agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -4340,12 +4340,12 @@
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>const ATUAL=6;</t>
+          <t>julho de 2026</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>const ATUAL=7;</t>
+          <t>agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -4362,125 +4362,125 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>libs de exportação</t>
+          <t>data</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>CDN</t>
+          <t>JULHO DE 2026</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>4 referências → vendor/ local (CDN como reserva)</t>
+          <t>AGOSTO DE 2026</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>tivio-relatorio-gestao-credito-privado.html</t>
+          <t>tivio-post-investment-solutions.html</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>mercado</t>
+          <t>—</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>MARKET</t>
+          <t>data</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>[['Total', '446.217', '100,0%', '1,14%', '1,17%', '-0,03%', '2,86', True], ['Energia elétrica', '102.982', '23,11%', '0,75%', '0,76%', '-0,02%', '2,78', False], ['Assistência médica', '45.853', '10,29%', '1,45%', '1,48%', '-0,04%', '3,40', False], ['Locação de veículos', '43.937', '9,86%', '1,72%', '1,71%', '0,02%', '2,51', False], ['Saneamento', '40.735', '9,14%', '1,43%', '1,44%', '-0,01%', '2,87', False], ['Petróleo e gás', '33.732', '7,57%', '0,91%', '0,95%', '-0,04%', '3,01', False], ['Transporte e logística', '27.250', '6,11%', '1,41%', '1,54%', '-0,12%', '2,78', False], ['Comércio atacadista e varejista', '24.639', '5,53%', '1,33%', '1,39%', '-0,06%', '2,65', False], ['Financeiro', '23.379', '5,25%', '0,52%', '0,54%', '-0,02%', '2,38', False], ['Indústria e comércio', '20.251', '4,54%', '1,15%', '1,20%', '-0,04%', '2,82', False], ['TI e telecomunicações', '17.577', '3,94%', '1,11%', '1,12%', '-0,01%', '2,46', False], ['Bioenergia', '11.334', '2,54%', '1,74%', '1,80%', '-0,06%', '3,08', False], ['Metalurgia e siderurgia', '9.560', '2,15%', '1,25%', '1,15%', '0,10%', '3,10', False], ['Educação', '7.933', '1,78%', '1,02%', '1,06%', '-0,04%', '2,39', False], ['Outros serviços', '7.003', '1,57%', '1,10%', '1,12%', '-0,02%', '2,89', False], ['Empreendimentos e participações', '6.693', '1,50%', '1,23%', '1,24%', '-0,01%', '3,44', False], ['Serviços imobiliários', '6.353', '1,43%', '0,64%', '0,65%', '-0,01%', '3,62', False], ['Papel e Celulose', '5.247', '1,18%', '0,58%', '0,60%', '-0,03%', '4,73', False], ['Materiais de construção e agregados', '4.144', '0,93%', '1,04%', '1,04%', '0,00%', '3,64', False], ['Química e petroquímica', '2.554', '0,57%', '1,11%', '1,14%', '-0,03%', '3,75', False], ['Alimentos e bebidas', '1.727', '0,39%', '1,25%', '1,28%', '-0,03%', '1,37', False], ['Têxtil e calçados', '1.528', '0,34%', '1,25%', '1,25%', '0,00%', '2,90', False], ['Mineração', '1.072', '0,24%', '0,83%', '0,86%', '-0,03%', '2,51', False], ['Construção civil', '166', '0,04%', '1,66%', '1,82%', '-0,16%', '0,68', False]]</t>
+          <t>Julho 2026</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>[['Setor', 'Volume (R$ MM)', '%', 'Spread Atual', 'Spread mês anterior', 'Variação', 'Duration', False], ['Total', '(a linha Total vem primeiro)', '', '', '', '', '', True]]</t>
+          <t>Agosto 2026</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>tivio-relatorio-gestao-credito-privado.html</t>
+          <t>tivio-post-investment-solutions.html</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>banks</t>
+          <t>—</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>pl</t>
+          <t>data</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>R$ 1.698.520.740,05</t>
+          <t>-jul26</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>R$ 1.793.381.077,96</t>
+          <t>-ago26</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>tivio-relatorio-gestao-credito-privado.html</t>
+          <t>tivio-post-investment-solutions.html</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>banks</t>
+          <t>—</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>plm</t>
+          <t>data</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>R$ 1.397.203.402,03</t>
+          <t>const ATUAL=6;</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>R$ 1.449.683.179,97</t>
+          <t>const ATUAL=7;</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>tivio-relatorio-gestao-credito-privado.html</t>
+          <t>tivio-post-investment-solutions.html</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>banks</t>
+          <t>—</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>perfrows</t>
+          <t>libs de exportação</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>{'pct': ['101%', '100%', '100%']}</t>
+          <t>CDN</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>{'fundo': ['1,10%', '9,36%', '14,63%', '29,82%', '45,41%', '444,67%'], 'bench': ['1,09%', '9,33%', '14,57%', '29,49%', '44,17%', '408,92%'], 'pct': ['101%', '100%', '100%', '101%', '103%', '109%']}</t>
+          <t>4 referências → vendor/ local (CDN como reserva)</t>
         </is>
       </c>
     </row>
@@ -4492,22 +4492,22 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>banks</t>
+          <t>mercado</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>emissores</t>
+          <t>MARKET</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>[['ITAÚ UNIBANCO', '3,42%', 100], ['BRADESCO', '3,18%', 93], ['SANTANDER', '2,86%', 84], ['BANCO DO BRASIL', '2,54%', 74], ['BTG PACTUAL', '2,21%', 65]]</t>
+          <t>[['Total', '446.217', '100,0%', '1,14%', '1,17%', '-0,03%', '2,86', True], ['Energia elétrica', '102.982', '23,11%', '0,75%', '0,76%', '-0,02%', '2,78', False], ['Assistência médica', '45.853', '10,29%', '1,45%', '1,48%', '-0,04%', '3,40', False], ['Locação de veículos', '43.937', '9,86%', '1,72%', '1,71%', '0,02%', '2,51', False], ['Saneamento', '40.735', '9,14%', '1,43%', '1,44%', '-0,01%', '2,87', False], ['Petróleo e gás', '33.732', '7,57%', '0,91%', '0,95%', '-0,04%', '3,01', False], ['Transporte e logística', '27.250', '6,11%', '1,41%', '1,54%', '-0,12%', '2,78', False], ['Comércio atacadista e varejista', '24.639', '5,53%', '1,33%', '1,39%', '-0,06%', '2,65', False], ['Financeiro', '23.379', '5,25%', '0,52%', '0,54%', '-0,02%', '2,38', False], ['Indústria e comércio', '20.251', '4,54%', '1,15%', '1,20%', '-0,04%', '2,82', False], ['TI e telecomunicações', '17.577', '3,94%', '1,11%', '1,12%', '-0,01%', '2,46', False], ['Bioenergia', '11.334', '2,54%', '1,74%', '1,80%', '-0,06%', '3,08', False], ['Metalurgia e siderurgia', '9.560', '2,15%', '1,25%', '1,15%', '0,10%', '3,10', False], ['Educação', '7.933', '1,78%', '1,02%', '1,06%', '-0,04%', '2,39', False], ['Outros serviços', '7.003', '1,57%', '1,10%', '1,12%', '-0,02%', '2,89', False], ['Empreendimentos e participações', '6.693', '1,50%', '1,23%', '1,24%', '-0,01%', '3,44', False], ['Serviços imobiliários', '6.353', '1,43%', '0,64%', '0,65%', '-0,01%', '3,62', False], ['Papel e Celulose', '5.247', '1,18%', '0,58%', '0,60%', '-0,03%', '4,73', False], ['Materiais de construção e agregados', '4.144', '0,93%', '1,04%', '1,04%', '0,00%', '3,64', False], ['Química e petroquímica', '2.554', '0,57%', '1,11%', '1,14%', '-0,03%', '3,75', False], ['Alimentos e bebidas', '1.727', '0,39%', '1,25%', '1,28%', '-0,03%', '1,37', False], ['Têxtil e calçados', '1.528', '0,34%', '1,25%', '1,25%', '0,00%', '2,90', False], ['Mineração', '1.072', '0,24%', '0,83%', '0,86%', '-0,03%', '2,51', False], ['Construção civil', '166', '0,04%', '1,66%', '1,82%', '-0,16%', '0,68', False]]</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>[['BV', '6,36%', 100], ['XP', '6,04%', 95], ['BTG', '5,97%', 94], ['ABC', '5,92%', 93], ['NUBANK', '5,57%', 88]]</t>
+          <t>[['Setor', 'Volume (R$ MM)', '%', 'Spread Atual', 'Spread mês anterior', 'Variação', 'Duration', False], ['Total', '(a linha Total vem primeiro)', '', '', '', '', '', True]]</t>
         </is>
       </c>
     </row>
@@ -4524,17 +4524,17 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>setores</t>
+          <t>pl</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>[['Financeiro', '76,5%'], ['Caixa', '23,5%']]</t>
+          <t>R$ 1.698.520.740,05</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>[['Financeiro', '75,7%'], ['Caixa', '24,2%']]</t>
+          <t>R$ 1.793.381.077,96</t>
         </is>
       </c>
     </row>
@@ -4551,17 +4551,17 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>rating</t>
+          <t>plm</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>[['AAA', '46,2%', 100], ['AA+', '24,8%', 54], ['AA', '14,1%', 31], ['AA-', '9,4%', 20], ['A+', '3,9%', 8], ['A', '1,6%', 3]]</t>
+          <t>R$ 1.397.203.402,03</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>[['AAA', '50,8%', 100], ['AA+', '16,3%', 32], ['AA', '2,0%', 4], ['A+', '1,9%', 4], ['A', '3,0%', 6]]</t>
+          <t>R$ 1.449.683.179,97</t>
         </is>
       </c>
     </row>
@@ -4578,17 +4578,17 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>val</t>
+          <t>perfrows</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>{'pct': ['101%', '100%', '100%']}</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>0,25%</t>
+          <t>{'fundo': ['1,10%', '9,36%', '14,63%', '29,82%', '45,41%', '444,67%'], 'bench': ['1,09%', '9,33%', '14,57%', '29,49%', '44,17%', '408,92%'], 'pct': ['101%', '100%', '100%', '101%', '103%', '109%']}</t>
         </is>
       </c>
     </row>
@@ -4605,17 +4605,17 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>val</t>
+          <t>emissores</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>1,12</t>
+          <t>[['ITAÚ UNIBANCO', '3,42%', 100], ['BRADESCO', '3,18%', 93], ['SANTANDER', '2,86%', 84], ['BANCO DO BRASIL', '2,54%', 74], ['BTG PACTUAL', '2,21%', 65]]</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>1,05</t>
+          <t>[['BV', '6,36%', 100], ['XP', '6,04%', 95], ['BTG', '5,97%', 94], ['ABC', '5,92%', 93], ['NUBANK', '5,57%', 88]]</t>
         </is>
       </c>
     </row>
@@ -4632,17 +4632,17 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>hist12</t>
+          <t>setores</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>[['Financeiro', '76,5%'], ['Caixa', '23,5%']]</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>{'b': 'CDI', 'l': ['2025-08', '2025-09', '2025-10', '2025-11', '2025-12', '2026-01', '2026-02', '2026-03', '2026-04', '2026-05', '2026-06', '2026-07', '2026-08'], 'f': [0.0, 1.23, 2.53, 3.62, 4.88, 6.11, 7.18, 8.48, 9.64, 10.82, 12.07, 13.45, 14.7], 'c': [0.0, 1.22, 2.51, 3.59, 4.85, 6.07, 7.13, 8.43, 9.61, 10.79, 12.03, 13.39, 14.63]}</t>
+          <t>[['Financeiro', '75,7%'], ['Caixa', '24,2%']]</t>
         </is>
       </c>
     </row>
@@ -4659,17 +4659,17 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>histEnd</t>
+          <t>rating</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>[12.0, 12.0, 'CDI']</t>
+          <t>[['AAA', '46,2%', 100], ['AA+', '24,8%', 54], ['AA', '14,1%', 31], ['AA-', '9,4%', 20], ['A+', '3,9%', 8], ['A', '1,6%', 3]]</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>[14.7, 14.63, 'CDI']</t>
+          <t>[['AAA', '50,8%', 100], ['AA+', '16,3%', 32], ['AA', '2,0%', 4], ['A+', '1,9%', 4], ['A', '3,0%', 6]]</t>
         </is>
       </c>
     </row>
@@ -4686,17 +4686,17 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>comentario</t>
+          <t>val</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>['No mês, o mercado de crédito privado high grade manteve o movimento de fechamento gradual de spreads, com fluxo comprador consistente no secundário e oferta primária ainda concentrada em emissores de primeira linha.', 'A liquidez permaneceu saudável ao longo da curva, com boa demanda por papéis bancários e por debêntures de empresas de energia, saneamento e infraestrutura, setores de maior peso na carteira.', 'Do ponto de vista da gestão, seguimos priorizando emissores de baixo risco de crédito e o controle da duration, mantendo carrego atrativo sobre o CDI sem elevar de forma relevante a volatilidade da cota.', 'O BANKS apresentou rentabilidade de &lt;b&gt;1,01%&lt;/b&gt; no mês (&lt;b&gt;101% do CDI&lt;/b&gt;), acumulando &lt;b&gt;8,17%&lt;/b&gt; no ano. Os principais atribuidores de resultado foram as debêntures corporativas e a parcela bancária da carteira.']</t>
+          <t>0,26%</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>['O Fundo Tivio Banks obteve retorno de 1,10% (101% do CDI) no mês e acumula 9,36% (100% do CDI) em 2026. A alocação em crédito era de 75%, integralmente concentrada em emissores do setor bancário. O carrego da carteira encontra-se em CDI +0,25%, com duration média de 1,05 ano.', 'Em agosto, o mercado de crédito foi marcado por um ambiente de menor liquidez nas negociações do mercado secundário e por uma leve reabertura dos spreads de crédito. Após meses consecutivos de compressão dos prêmios de risco, observou-se um movimento mais cauteloso por parte dos investidores, com os spreads médios dos títulos corporativos indexados ao CDI avançando aproximadamente 0,03%, passando de CDI + 1,19% para CDI + 1,22% ao ano. Apesar desse ajuste, os níveis de prêmio permaneceram próximos das mínimas históricas observadas ao longo do ciclo recente.', 'No mercado secundário, a redução do volume negociado contribuiu para uma formação de preços mais seletiva, especialmente em ativos corporativos com menor liquidez. Ainda assim, o comportamento dos investidores permaneceu construtivo, sustentado por um ambiente técnico favorável e pela continuidade da elevada demanda por ativos de crédito.', 'Já no mercado primário, as emissões bancárias seguiram registrando forte demanda por parte dos investidores. As ofertas de Letras Financeiras Seniores distribuídas ao longo do mês apresentaram níveis elevados de subscrição, com demanda que, em diversos casos, superou três vezes o volume ofertado. Esse forte apetite permitiu que as operações fossem precificadas com taxas inferiores aos limites inicialmente indicados pelos emissores, evidenciando a elevada disponibilidade de recursos para alocação na indústria de crédito.', 'Em relação aos fluxos, os fundos com alocação mínima de 15% em crédito e ao menos 1% em debêntures apresentaram captação líquida próxima de R$ 8 bilhões em agosto, resultado significativamente superior ao observado no mês anterior. O volume reforça a percepção de que os investidores seguem direcionando recursos para estratégias de crédito, impulsionados pelo elevado nível de carrego proporcionado pelos ativos indexados ao CDI e pela busca por alternativas de investimento com perfil de risco-retorno atrativo.', 'Nesse contexto, a combinação entre fluxos positivos para a indústria, vencimentos e amortizações recorrentes das carteiras, além da limitada oferta de novos ativos corporativos, continuou sustentando a demanda por crédito privado. Ainda que agosto tenha apresentado uma leve reabertura dos spreads médios de mercado, a dinâmica técnica permanece favorável e os prêmios seguem negociando em patamares historicamente reduzidos.', 'Por fim, sob a ótica da gestão, seguimos acompanhando de forma criteriosa a evolução dos fundamentos dos emissores presentes nas carteiras, com atenção especial aos indicadores operacionais, à geração de caixa e à manutenção de estruturas de capital adequadas. Em um ambiente em que os spreads permanecem comprimidos em termos históricos, mantemos disciplina na alocação dos recursos, priorizando operações que apresentem adequada relação entre risco e retorno e preservando flexibilidade para captura de oportunidades que possam surgir em eventuais períodos de maior volatilidade do mercado.']</t>
+          <t>0,25%</t>
         </is>
       </c>
     </row>
@@ -4708,22 +4708,22 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>institucional</t>
+          <t>banks</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>pl</t>
+          <t>val</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>R$ 1.983.487.947,49</t>
+          <t>1,12</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>R$ 1.815.644.128,24</t>
+          <t>1,05</t>
         </is>
       </c>
     </row>
@@ -4735,22 +4735,22 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>institucional</t>
+          <t>banks</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>plm</t>
+          <t>hist12</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>R$ 2.522.009.705,73</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>R$ 2.491.331.200,61</t>
+          <t>{'b': 'CDI', 'l': ['2025-08', '2025-09', '2025-10', '2025-11', '2025-12', '2026-01', '2026-02', '2026-03', '2026-04', '2026-05', '2026-06', '2026-07', '2026-08'], 'f': [0.0, 1.23, 2.53, 3.62, 4.88, 6.11, 7.18, 8.48, 9.64, 10.82, 12.07, 13.45, 14.7], 'c': [0.0, 1.22, 2.51, 3.59, 4.85, 6.07, 7.13, 8.43, 9.61, 10.79, 12.03, 13.39, 14.63]}</t>
         </is>
       </c>
     </row>
@@ -4762,22 +4762,22 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>institucional</t>
+          <t>banks</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>perfrows</t>
+          <t>histEnd</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>{'pct': ['104%', '100%', '100%']}</t>
+          <t>[12.0, 12.0, 'CDI']</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>{'fundo': ['1,09%', '9,31%', '14,58%', '29,93%', '47,60%', '825,45%'], 'bench': ['1,09%', '9,33%', '14,57%', '29,49%', '44,17%', '753,88%'], 'pct': ['100%', '100%', '100%', '102%', '108%', '109%']}</t>
+          <t>[14.7, 14.63, 'CDI']</t>
         </is>
       </c>
     </row>
@@ -4789,22 +4789,22 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>institucional</t>
+          <t>banks</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>emissores</t>
+          <t>comentario</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>[['AEGEA', '2,64%', 100], ['TUPY', '2,31%', 88], ['VALE', '2,05%', 78], ['PETROBRAS', '1,86%', 70], ['RANDON', '1,52%', 58]]</t>
+          <t>['No mês, o mercado de crédito privado high grade manteve o movimento de fechamento gradual de spreads, com fluxo comprador consistente no secundário e oferta primária ainda concentrada em emissores de primeira linha.', 'A liquidez permaneceu saudável ao longo da curva, com boa demanda por papéis bancários e por debêntures de empresas de energia, saneamento e infraestrutura, setores de maior peso na carteira.', 'Do ponto de vista da gestão, seguimos priorizando emissores de baixo risco de crédito e o controle da duration, mantendo carrego atrativo sobre o CDI sem elevar de forma relevante a volatilidade da cota.', 'O BANKS apresentou rentabilidade de &lt;b&gt;1,01%&lt;/b&gt; no mês (&lt;b&gt;101% do CDI&lt;/b&gt;), acumulando &lt;b&gt;8,17%&lt;/b&gt; no ano. Os principais atribuidores de resultado foram as debêntures corporativas e a parcela bancária da carteira.']</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>[['BTG', '3,45%', 100], ['BB', '3,44%', 100], ['SANTANDER', '3,06%', 89], ['SAFRA', '3,02%', 88], ['BRADESCO', '2,89%', 84]]</t>
+          <t>['O Fundo Tivio Banks obteve retorno de 1,10% (101% do CDI) no mês e acumula 9,36% (100% do CDI) em 2026. A alocação em crédito era de 75%, integralmente concentrada em emissores do setor bancário. O carrego da carteira encontra-se em CDI +0,25%, com duration média de 1,05 ano.', 'Em agosto, o mercado de crédito foi marcado por um ambiente de menor liquidez nas negociações do mercado secundário e por uma leve reabertura dos spreads de crédito. Após meses consecutivos de compressão dos prêmios de risco, observou-se um movimento mais cauteloso por parte dos investidores, com os spreads médios dos títulos corporativos indexados ao CDI avançando aproximadamente 0,03%, passando de CDI + 1,19% para CDI + 1,22% ao ano. Apesar desse ajuste, os níveis de prêmio permaneceram próximos das mínimas históricas observadas ao longo do ciclo recente.', 'No mercado secundário, a redução do volume negociado contribuiu para uma formação de preços mais seletiva, especialmente em ativos corporativos com menor liquidez. Ainda assim, o comportamento dos investidores permaneceu construtivo, sustentado por um ambiente técnico favorável e pela continuidade da elevada demanda por ativos de crédito.', 'Já no mercado primário, as emissões bancárias seguiram registrando forte demanda por parte dos investidores. As ofertas de Letras Financeiras Seniores distribuídas ao longo do mês apresentaram níveis elevados de subscrição, com demanda que, em diversos casos, superou três vezes o volume ofertado. Esse forte apetite permitiu que as operações fossem precificadas com taxas inferiores aos limites inicialmente indicados pelos emissores, evidenciando a elevada disponibilidade de recursos para alocação na indústria de crédito.', 'Em relação aos fluxos, os fundos com alocação mínima de 15% em crédito e ao menos 1% em debêntures apresentaram captação líquida próxima de R$ 8 bilhões em agosto, resultado significativamente superior ao observado no mês anterior. O volume reforça a percepção de que os investidores seguem direcionando recursos para estratégias de crédito, impulsionados pelo elevado nível de carrego proporcionado pelos ativos indexados ao CDI e pela busca por alternativas de investimento com perfil de risco-retorno atrativo.', 'Nesse contexto, a combinação entre fluxos positivos para a indústria, vencimentos e amortizações recorrentes das carteiras, além da limitada oferta de novos ativos corporativos, continuou sustentando a demanda por crédito privado. Ainda que agosto tenha apresentado uma leve reabertura dos spreads médios de mercado, a dinâmica técnica permanece favorável e os prêmios seguem negociando em patamares historicamente reduzidos.', 'Por fim, sob a ótica da gestão, seguimos acompanhando de forma criteriosa a evolução dos fundamentos dos emissores presentes nas carteiras, com atenção especial aos indicadores operacionais, à geração de caixa e à manutenção de estruturas de capital adequadas. Em um ambiente em que os spreads permanecem comprimidos em termos históricos, mantemos disciplina na alocação dos recursos, priorizando operações que apresentem adequada relação entre risco e retorno e preservando flexibilidade para captura de oportunidades que possam surgir em eventuais períodos de maior volatilidade do mercado.']</t>
         </is>
       </c>
     </row>
@@ -4821,17 +4821,17 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>setores</t>
+          <t>pl</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>[['Financeiro', '52%'], ['Energia Elétrica', '4%'], ['Transporte e Logística', '2%'], ['Saneamento', '2%'], ['Caixa', '31%']]</t>
+          <t>R$ 1.983.487.947,49</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>[['Financeiro', '44,6%'], ['Energia Elétrica', '4,5%'], ['FIDC', '2,1%'], ['Transporte e Logística', '2,1%'], ['Saneamento', '2,0%'], ['Caixa', '38,7%']]</t>
+          <t>R$ 1.815.644.128,24</t>
         </is>
       </c>
     </row>
@@ -4848,17 +4848,17 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>rating</t>
+          <t>plm</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>[['AAA', '46,2%', 100], ['AA+', '24,8%', 54], ['AA', '14,1%', 31], ['AA-', '9,4%', 20], ['A+', '3,9%', 8], ['A', '1,6%', 3]]</t>
+          <t>R$ 2.522.009.705,73</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>[['AAA', '39,6%', 100], ['AA+', '10,5%', 27], ['AA', '2,4%', 6], ['AA-', '2,7%', 7], ['A+', '1,2%', 3], ['A', '3,3%', 8]]</t>
+          <t>R$ 2.491.331.200,61</t>
         </is>
       </c>
     </row>
@@ -4875,17 +4875,17 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>val</t>
+          <t>perfrows</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>{'pct': ['104%', '100%', '100%']}</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>{'fundo': ['1,09%', '9,31%', '14,58%', '29,93%', '47,60%', '825,45%'], 'bench': ['1,09%', '9,33%', '14,57%', '29,49%', '44,17%', '753,88%'], 'pct': ['100%', '100%', '100%', '102%', '108%', '109%']}</t>
         </is>
       </c>
     </row>
@@ -4902,17 +4902,17 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>val</t>
+          <t>emissores</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>1,20</t>
+          <t>[['AEGEA', '2,64%', 100], ['TUPY', '2,31%', 88], ['VALE', '2,05%', 78], ['PETROBRAS', '1,86%', 70], ['RANDON', '1,52%', 58]]</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>1,28</t>
+          <t>[['BTG', '3,45%', 100], ['BB', '3,44%', 100], ['SANTANDER', '3,06%', 89], ['SAFRA', '3,02%', 88], ['BRADESCO', '2,89%', 84]]</t>
         </is>
       </c>
     </row>
@@ -4929,17 +4929,17 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>hist12</t>
+          <t>setores</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>[['Financeiro', '52%'], ['Energia Elétrica', '4%'], ['Transporte e Logística', '2%'], ['Saneamento', '2%'], ['Caixa', '31%']]</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>{'b': 'CDI', 'l': ['2025-08', '2025-09', '2025-10', '2025-11', '2025-12', '2026-01', '2026-02', '2026-03', '2026-04', '2026-05', '2026-06', '2026-07', '2026-08'], 'f': [0.0, 1.25, 2.52, 3.59, 4.88, 6.12, 7.13, 8.29, 9.43, 10.74, 11.99, 13.41, 14.64], 'c': [0.0, 1.22, 2.51, 3.59, 4.85, 6.07, 7.13, 8.43, 9.61, 10.79, 12.03, 13.39, 14.63]}</t>
+          <t>[['Financeiro', '44,6%'], ['Energia Elétrica', '4,5%'], ['FIDC', '2,1%'], ['Transporte e Logística', '2,1%'], ['Saneamento', '2,0%'], ['Caixa', '38,7%']]</t>
         </is>
       </c>
     </row>
@@ -4956,17 +4956,17 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>histEnd</t>
+          <t>rating</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>[12.48, 12.0, 'CDI']</t>
+          <t>[['AAA', '46,2%', 100], ['AA+', '24,8%', 54], ['AA', '14,1%', 31], ['AA-', '9,4%', 20], ['A+', '3,9%', 8], ['A', '1,6%', 3]]</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>[14.64, 14.63, 'CDI']</t>
+          <t>[['AAA', '39,6%', 100], ['AA+', '10,5%', 27], ['AA', '2,4%', 6], ['AA-', '2,7%', 7], ['A+', '1,2%', 3], ['A', '3,3%', 8]]</t>
         </is>
       </c>
     </row>
@@ -4983,17 +4983,17 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>comentario</t>
+          <t>val</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>['No mês, o mercado de crédito privado high grade manteve o movimento de fechamento gradual de spreads, com fluxo comprador consistente no secundário e oferta primária ainda concentrada em emissores de primeira linha.', 'A liquidez permaneceu saudável ao longo da curva, com boa demanda por papéis bancários e por debêntures de empresas de energia, saneamento e infraestrutura, setores de maior peso na carteira.', 'Do ponto de vista da gestão, seguimos priorizando emissores de baixo risco de crédito e o controle da duration, mantendo carrego atrativo sobre o CDI sem elevar de forma relevante a volatilidade da cota.', 'O INSTITUCIONAL apresentou rentabilidade de &lt;b&gt;1,27%&lt;/b&gt; no mês (&lt;b&gt;104% do CDI&lt;/b&gt;), acumulando &lt;b&gt;8,13%&lt;/b&gt; no ano. Os principais atribuidores de resultado foram as debêntures corporativas e a parcela bancária da carteira.']</t>
+          <t>0,44%</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>['Em agosto, o mercado de crédito foi marcado por um ambiente de menor liquidez nas negociações do mercado secundário e por uma leve reabertura dos spreads de crédito. Após meses consecutivos de compressão dos prêmios de risco, observou-se um movimento mais cauteloso por parte dos investidores, com os spreads médios dos títulos corporativos indexados ao CDI avançando aproximadamente 0,03%, passando de CDI + 1,19% para CDI + 1,22% ao ano. Apesar desse ajuste, os níveis de prêmio permaneceram próximos das mínimas históricas observadas ao longo do ciclo recente.', 'No mercado secundário, a redução do volume negociado contribuiu para uma formação de preços mais seletiva, especialmente em ativos corporativos com menor liquidez. Ainda assim, o comportamento dos investidores permaneceu construtivo, sustentado por um ambiente técnico favorável e pela continuidade da elevada demanda por ativos de crédito.', 'Já no mercado primário, as emissões bancárias seguiram registrando forte demanda por parte dos investidores. As ofertas de Letras Financeiras Seniores distribuídas ao longo do mês apresentaram níveis elevados de subscrição, com demanda que, em diversos casos, superou três vezes o volume ofertado. Esse forte apetite permitiu que as operações fossem precificadas com taxas inferiores aos limites inicialmente indicados pelos emissores, evidenciando a elevada disponibilidade de recursos para alocação na indústria de crédito. Por outro lado, o pipeline de emissões corporativas permaneceu limitado, restringindo a oferta de novos ativos em um momento de demanda ainda aquecida.', 'Em relação aos fluxos, os fundos com alocação mínima de 15% em crédito e ao menos 1% em debêntures apresentaram captação líquida próxima de R$ 8 bilhões em agosto, resultado significativamente superior ao observado no mês anterior. O volume reforça a percepção de que os investidores seguem direcionando recursos para estratégias de crédito, impulsionados pelo elevado nível de carrego proporcionado pelos ativos indexados ao CDI e pela busca por alternativas de investimento com perfil de risco-retorno atrativo.', 'Nesse contexto, a combinação entre fluxos positivos para a indústria, vencimentos e amortizações recorrentes das carteiras, além da limitada oferta de novos ativos corporativos, continuou sustentando a demanda por crédito privado. Ainda que agosto tenha apresentado uma leve reabertura dos spreads médios de mercado, a dinâmica técnica permanece favorável e os prêmios seguem negociando em patamares historicamente reduzidos.', 'Por fim, sob a ótica da gestão, seguimos acompanhando de forma criteriosa a evolução dos fundamentos dos emissores presentes nas carteiras, com atenção especial aos indicadores operacionais, à geração de caixa e à manutenção de estruturas de capital adequadas. Em um ambiente em que os spreads permanecem comprimidos em termos históricos, mantemos disciplina na alocação dos recursos, priorizando operações que apresentem adequada relação entre risco e retorno e preservando flexibilidade para captura de oportunidades que possam surgir em eventuais períodos de maior volatilidade do mercado.', 'Nesse cenário, o Fundo Tivio Institucional apresentou rentabilidade de 1,09% no mês (100% do CDI), acumulando 9,31% (100% do CDI) no ano. Na parcela de corporativos, os maiores atribuidores de resultado foram para Argo e Aegea, enquanto Aegea foi o maior detrator.']</t>
+          <t>0,39%</t>
         </is>
       </c>
     </row>
@@ -5005,22 +5005,22 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>inst15</t>
+          <t>institucional</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>adm</t>
+          <t>val</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>0,45% a.a.</t>
+          <t>1,20</t>
         </is>
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>0,50% a.a.</t>
+          <t>1,28</t>
         </is>
       </c>
     </row>
@@ -5032,22 +5032,22 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>inst15</t>
+          <t>institucional</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>perf</t>
+          <t>hist12</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>Não há</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>20% do que exceder 102,5% do CDI</t>
+          <t>{'b': 'CDI', 'l': ['2025-08', '2025-09', '2025-10', '2025-11', '2025-12', '2026-01', '2026-02', '2026-03', '2026-04', '2026-05', '2026-06', '2026-07', '2026-08'], 'f': [0.0, 1.25, 2.52, 3.59, 4.88, 6.12, 7.13, 8.29, 9.43, 10.74, 11.99, 13.41, 14.64], 'c': [0.0, 1.22, 2.51, 3.59, 4.85, 6.07, 7.13, 8.43, 9.61, 10.79, 12.03, 13.39, 14.63]}</t>
         </is>
       </c>
     </row>
@@ -5059,22 +5059,22 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>inst15</t>
+          <t>institucional</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>pl</t>
+          <t>histEnd</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>R$ 161.593.743,98</t>
+          <t>[12.48, 12.0, 'CDI']</t>
         </is>
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>R$ 156.046.891,63</t>
+          <t>[14.64, 14.63, 'CDI']</t>
         </is>
       </c>
     </row>
@@ -5086,22 +5086,22 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>inst15</t>
+          <t>institucional</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>plm</t>
+          <t>comentario</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>R$ 140.997.685,81</t>
+          <t>['No mês, o mercado de crédito privado high grade manteve o movimento de fechamento gradual de spreads, com fluxo comprador consistente no secundário e oferta primária ainda concentrada em emissores de primeira linha.', 'A liquidez permaneceu saudável ao longo da curva, com boa demanda por papéis bancários e por debêntures de empresas de energia, saneamento e infraestrutura, setores de maior peso na carteira.', 'Do ponto de vista da gestão, seguimos priorizando emissores de baixo risco de crédito e o controle da duration, mantendo carrego atrativo sobre o CDI sem elevar de forma relevante a volatilidade da cota.', 'O INSTITUCIONAL apresentou rentabilidade de &lt;b&gt;1,27%&lt;/b&gt; no mês (&lt;b&gt;104% do CDI&lt;/b&gt;), acumulando &lt;b&gt;8,13%&lt;/b&gt; no ano. Os principais atribuidores de resultado foram as debêntures corporativas e a parcela bancária da carteira.']</t>
         </is>
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>R$ 146.843.921,67</t>
+          <t>['Em agosto, o mercado de crédito foi marcado por um ambiente de menor liquidez nas negociações do mercado secundário e por uma leve reabertura dos spreads de crédito. Após meses consecutivos de compressão dos prêmios de risco, observou-se um movimento mais cauteloso por parte dos investidores, com os spreads médios dos títulos corporativos indexados ao CDI avançando aproximadamente 0,03%, passando de CDI + 1,19% para CDI + 1,22% ao ano. Apesar desse ajuste, os níveis de prêmio permaneceram próximos das mínimas históricas observadas ao longo do ciclo recente.', 'No mercado secundário, a redução do volume negociado contribuiu para uma formação de preços mais seletiva, especialmente em ativos corporativos com menor liquidez. Ainda assim, o comportamento dos investidores permaneceu construtivo, sustentado por um ambiente técnico favorável e pela continuidade da elevada demanda por ativos de crédito.', 'Já no mercado primário, as emissões bancárias seguiram registrando forte demanda por parte dos investidores. As ofertas de Letras Financeiras Seniores distribuídas ao longo do mês apresentaram níveis elevados de subscrição, com demanda que, em diversos casos, superou três vezes o volume ofertado. Esse forte apetite permitiu que as operações fossem precificadas com taxas inferiores aos limites inicialmente indicados pelos emissores, evidenciando a elevada disponibilidade de recursos para alocação na indústria de crédito. Por outro lado, o pipeline de emissões corporativas permaneceu limitado, restringindo a oferta de novos ativos em um momento de demanda ainda aquecida.', 'Em relação aos fluxos, os fundos com alocação mínima de 15% em crédito e ao menos 1% em debêntures apresentaram captação líquida próxima de R$ 8 bilhões em agosto, resultado significativamente superior ao observado no mês anterior. O volume reforça a percepção de que os investidores seguem direcionando recursos para estratégias de crédito, impulsionados pelo elevado nível de carrego proporcionado pelos ativos indexados ao CDI e pela busca por alternativas de investimento com perfil de risco-retorno atrativo.', 'Nesse contexto, a combinação entre fluxos positivos para a indústria, vencimentos e amortizações recorrentes das carteiras, além da limitada oferta de novos ativos corporativos, continuou sustentando a demanda por crédito privado. Ainda que agosto tenha apresentado uma leve reabertura dos spreads médios de mercado, a dinâmica técnica permanece favorável e os prêmios seguem negociando em patamares historicamente reduzidos.', 'Por fim, sob a ótica da gestão, seguimos acompanhando de forma criteriosa a evolução dos fundamentos dos emissores presentes nas carteiras, com atenção especial aos indicadores operacionais, à geração de caixa e à manutenção de estruturas de capital adequadas. Em um ambiente em que os spreads permanecem comprimidos em termos históricos, mantemos disciplina na alocação dos recursos, priorizando operações que apresentem adequada relação entre risco e retorno e preservando flexibilidade para captura de oportunidades que possam surgir em eventuais períodos de maior volatilidade do mercado.', 'Nesse cenário, o Fundo Tivio Institucional apresentou rentabilidade de 1,09% no mês (100% do CDI), acumulando 9,31% (100% do CDI) no ano. Na parcela de corporativos, os maiores atribuidores de resultado foram para Argo e Aegea, enquanto Aegea foi o maior detrator.']</t>
         </is>
       </c>
     </row>
@@ -5118,17 +5118,17 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>perfrows</t>
+          <t>adm</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>{'pct': ['113%', '102%', '102%']}</t>
+          <t>0,45% a.a.</t>
         </is>
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>{'fundo': ['1,11%', '9,53%', '14,94%', '30,92%', '51,22%', '1.644,37%'], 'bench': ['1,09%', '9,33%', '14,57%', '29,49%', '44,17%', '1.408,13%'], 'pct': ['102%', '102%', '103%', '105%', '116%', '117%']}</t>
+          <t>0,50% a.a.</t>
         </is>
       </c>
     </row>
@@ -5145,17 +5145,17 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>emissores</t>
+          <t>perf</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>[['TUPY', '3,04%', 100], ['UNIDAS', '2,71%', 89], ['AEGEA', '2,33%', 77], ['HAPVIDA', '2,01%', 66], ['EQUATORIAL', '1,74%', 57]]</t>
+          <t>Não há</t>
         </is>
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>[['C6', '5,45%', 100], ['ABC', '3,43%', 63], ['XP', '3,28%', 60], ['BTG', '3,28%', 60], ['BRADESCO', '1,76%', 32]]</t>
+          <t>20% do que exceder 102,5% do CDI</t>
         </is>
       </c>
     </row>
@@ -5172,17 +5172,17 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>setores</t>
+          <t>pl</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>[['Financeiro', '29%'], ['FIDC', '13%'], ['Energia Elétrica', '7%'], ['Saneamento', '5%'], ['Transporte e Logística', '4%'], ['Caixa', '26%']]</t>
+          <t>R$ 161.593.743,98</t>
         </is>
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>[['Financeiro', '28,0%'], ['FIDC', '13,0%'], ['Energia Elétrica', '7,1%'], ['Locação de veículos', '3,8%'], ['Saneamento', '3,5%'], ['Caixa', '27,2%']]</t>
+          <t>R$ 156.046.891,63</t>
         </is>
       </c>
     </row>
@@ -5199,17 +5199,17 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>rating</t>
+          <t>plm</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>[['AAA', '46,2%', 100], ['AA+', '24,8%', 54], ['AA', '14,1%', 31], ['AA-', '9,4%', 20], ['A+', '3,9%', 8], ['A', '1,6%', 3]]</t>
+          <t>R$ 140.997.685,81</t>
         </is>
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>[['AAA', '32,7%', 100], ['AA+', '7,8%', 24], ['AA', '4,1%', 13], ['AA-', '5,7%', 17], ['A+', '4,2%', 13], ['A', '6,2%', 19]]</t>
+          <t>R$ 146.843.921,67</t>
         </is>
       </c>
     </row>
@@ -5226,17 +5226,17 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>val</t>
+          <t>perfrows</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>1,00%</t>
+          <t>{'pct': ['113%', '102%', '102%']}</t>
         </is>
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>{'fundo': ['1,11%', '9,53%', '14,94%', '30,92%', '51,22%', '1.644,37%'], 'bench': ['1,09%', '9,33%', '14,57%', '29,49%', '44,17%', '1.408,13%'], 'pct': ['102%', '102%', '103%', '105%', '116%', '117%']}</t>
         </is>
       </c>
     </row>
@@ -5253,17 +5253,17 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>val</t>
+          <t>emissores</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>1,97</t>
+          <t>[['TUPY', '3,04%', 100], ['UNIDAS', '2,71%', 89], ['AEGEA', '2,33%', 77], ['HAPVIDA', '2,01%', 66], ['EQUATORIAL', '1,74%', 57]]</t>
         </is>
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>1,80</t>
+          <t>[['C6', '5,45%', 100], ['ABC', '3,43%', 63], ['XP', '3,28%', 60], ['BTG', '3,28%', 60], ['BRADESCO', '1,76%', 32]]</t>
         </is>
       </c>
     </row>
@@ -5280,17 +5280,17 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>unit</t>
+          <t>setores</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>anos</t>
+          <t>[['Financeiro', '29%'], ['FIDC', '13%'], ['Energia Elétrica', '7%'], ['Saneamento', '5%'], ['Transporte e Logística', '4%'], ['Caixa', '26%']]</t>
         </is>
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>ano</t>
+          <t>[['Financeiro', '28,0%'], ['FIDC', '13,0%'], ['Energia Elétrica', '7,1%'], ['Locação de veículos', '3,8%'], ['Saneamento', '3,5%'], ['Caixa', '27,2%']]</t>
         </is>
       </c>
     </row>
@@ -5307,17 +5307,17 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>hist12</t>
+          <t>rating</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>[['AAA', '46,2%', 100], ['AA+', '24,8%', 54], ['AA', '14,1%', 31], ['AA-', '9,4%', 20], ['A+', '3,9%', 8], ['A', '1,6%', 3]]</t>
         </is>
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>{'b': 'CDI', 'l': ['2025-08', '2025-09', '2025-10', '2025-11', '2025-12', '2026-01', '2026-02', '2026-03', '2026-04', '2026-05', '2026-06', '2026-07', '2026-08'], 'f': [0.0, 1.29, 2.5, 3.53, 5.0, 6.31, 7.33, 8.3, 9.48, 10.88, 12.2, 13.74, 15.0], 'c': [0.0, 1.22, 2.51, 3.59, 4.85, 6.07, 7.13, 8.43, 9.61, 10.79, 12.03, 13.39, 14.63]}</t>
+          <t>[['AAA', '32,7%', 100], ['AA+', '7,8%', 24], ['AA', '4,1%', 13], ['AA-', '5,7%', 17], ['A+', '4,2%', 13], ['A', '6,2%', 19]]</t>
         </is>
       </c>
     </row>
@@ -5334,17 +5334,17 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>histEnd</t>
+          <t>val</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>[12.24, 12.0, 'CDI']</t>
+          <t>1,00%</t>
         </is>
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>[15.0, 14.63, 'CDI']</t>
+          <t>0,95%</t>
         </is>
       </c>
     </row>
@@ -5361,17 +5361,17 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>comentario</t>
+          <t>val</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>['No mês, o mercado de crédito privado high grade manteve o movimento de fechamento gradual de spreads, com fluxo comprador consistente no secundário e oferta primária ainda concentrada em emissores de primeira linha.', 'A liquidez permaneceu saudável ao longo da curva, com boa demanda por papéis bancários e por debêntures de empresas de energia, saneamento e infraestrutura, setores de maior peso na carteira.', 'Do ponto de vista da gestão, seguimos priorizando emissores de baixo risco de crédito e o controle da duration, mantendo carrego atrativo sobre o CDI sem elevar de forma relevante a volatilidade da cota.', 'O INSTITUCIONAL 15 apresentou rentabilidade de &lt;b&gt;1,37%&lt;/b&gt; no mês (&lt;b&gt;113% do CDI&lt;/b&gt;), acumulando &lt;b&gt;8,32%&lt;/b&gt; no ano. Os principais atribuidores de resultado foram as debêntures corporativas e a parcela bancária da carteira.']</t>
+          <t>1,97</t>
         </is>
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>['Em agosto, o mercado de crédito foi marcado por um ambiente de menor liquidez nas negociações do mercado secundário e por uma leve reabertura dos spreads de crédito. Após meses consecutivos de compressão dos prêmios de risco, observou-se um movimento mais cauteloso por parte dos investidores, com os spreads médios dos títulos corporativos indexados ao CDI avançando aproximadamente 0,03%, passando de CDI + 1,19% para CDI + 1,22% ao ano. Apesar desse ajuste, os níveis de prêmio permaneceram próximos das mínimas históricas observadas ao longo do ciclo recente.', 'No mercado secundário, a redução do volume negociado contribuiu para uma formação de preços mais seletiva, especialmente em ativos corporativos com menor liquidez. Ainda assim, o comportamento dos investidores permaneceu construtivo, sustentado por um ambiente técnico favorável e pela continuidade da elevada demanda por ativos de crédito.', 'Já no mercado primário, as emissões bancárias seguiram registrando forte demanda por parte dos investidores. As ofertas de Letras Financeiras Seniores distribuídas ao longo do mês apresentaram níveis elevados de subscrição, com demanda que, em diversos casos, superou três vezes o volume ofertado. Esse forte apetite permitiu que as operações fossem precificadas com taxas inferiores aos limites inicialmente indicados pelos emissores, evidenciando a elevada disponibilidade de recursos para alocação na indústria de crédito. Por outro lado, o pipeline de emissões corporativas permaneceu limitado, restringindo a oferta de novos ativos em um momento de demanda ainda aquecida.', 'Em relação aos fluxos, os fundos com alocação mínima de 15% em crédito e ao menos 1% em debêntures apresentaram captação líquida próxima de R$ 8 bilhões em agosto, resultado significativamente superior ao observado no mês anterior. O volume reforça a percepção de que os investidores seguem direcionando recursos para estratégias de crédito, impulsionados pelo elevado nível de carrego proporcionado pelos ativos indexados ao CDI e pela busca por alternativas de investimento com perfil de risco-retorno atrativo.', 'Nesse contexto, a combinação entre fluxos positivos para a indústria, vencimentos e amortizações recorrentes das carteiras, além da limitada oferta de novos ativos corporativos, continuou sustentando a demanda por crédito privado. Ainda que agosto tenha apresentado uma leve reabertura dos spreads médios de mercado, a dinâmica técnica permanece favorável e os prêmios seguem negociando em patamares historicamente reduzidos.', 'Por fim, sob a ótica da gestão, seguimos acompanhando de forma criteriosa a evolução dos fundamentos dos emissores presentes nas carteiras, com atenção especial aos indicadores operacionais, à geração de caixa e à manutenção de estruturas de capital adequadas. Em um ambiente em que os spreads permanecem comprimidos em termos históricos, mantemos disciplina na alocação dos recursos, priorizando operações que apresentem adequada relação entre risco e retorno e preservando flexibilidade para captura de oportunidades que possam surgir em eventuais períodos de maior volatilidade do mercado.', 'Nesse cenário, o Tivio Institucional 15 apresentou rentabilidade de 1,11% no mês (102% do CDI), acumulando 9,53% (102% do CDI) no ano. Na parcela de corporativos, os maiores atribuidores de resultado foram para Tupy e Randon, enquanto Hapvida foi o maior detrator.']</t>
+          <t>1,80</t>
         </is>
       </c>
     </row>
@@ -5383,22 +5383,22 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>inst30</t>
+          <t>inst15</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>adm</t>
+          <t>unit</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>0,63% a.a.</t>
+          <t>anos</t>
         </is>
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>0,625% a.a.</t>
+          <t>ano</t>
         </is>
       </c>
     </row>
@@ -5410,22 +5410,22 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>inst30</t>
+          <t>inst15</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>perf</t>
+          <t>hist12</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>20% do que exceder o CDI</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>20% do que exceder 100% do CDI</t>
+          <t>{'b': 'CDI', 'l': ['2025-08', '2025-09', '2025-10', '2025-11', '2025-12', '2026-01', '2026-02', '2026-03', '2026-04', '2026-05', '2026-06', '2026-07', '2026-08'], 'f': [0.0, 1.29, 2.5, 3.53, 5.0, 6.31, 7.33, 8.3, 9.48, 10.88, 12.2, 13.74, 15.0], 'c': [0.0, 1.22, 2.51, 3.59, 4.85, 6.07, 7.13, 8.43, 9.61, 10.79, 12.03, 13.39, 14.63]}</t>
         </is>
       </c>
     </row>
@@ -5437,22 +5437,22 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>inst30</t>
+          <t>inst15</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>pl</t>
+          <t>histEnd</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>R$ 143.232.764,20</t>
+          <t>[12.24, 12.0, 'CDI']</t>
         </is>
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>R$ 126.168.780,56</t>
+          <t>[15.0, 14.63, 'CDI']</t>
         </is>
       </c>
     </row>
@@ -5464,22 +5464,22 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>inst30</t>
+          <t>inst15</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>plm</t>
+          <t>comentario</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>R$ 155.004.649,74</t>
+          <t>['No mês, o mercado de crédito privado high grade manteve o movimento de fechamento gradual de spreads, com fluxo comprador consistente no secundário e oferta primária ainda concentrada em emissores de primeira linha.', 'A liquidez permaneceu saudável ao longo da curva, com boa demanda por papéis bancários e por debêntures de empresas de energia, saneamento e infraestrutura, setores de maior peso na carteira.', 'Do ponto de vista da gestão, seguimos priorizando emissores de baixo risco de crédito e o controle da duration, mantendo carrego atrativo sobre o CDI sem elevar de forma relevante a volatilidade da cota.', 'O INSTITUCIONAL 15 apresentou rentabilidade de &lt;b&gt;1,37%&lt;/b&gt; no mês (&lt;b&gt;113% do CDI&lt;/b&gt;), acumulando &lt;b&gt;8,32%&lt;/b&gt; no ano. Os principais atribuidores de resultado foram as debêntures corporativas e a parcela bancária da carteira.']</t>
         </is>
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>R$ 158.893.390,74</t>
+          <t>['Em agosto, o mercado de crédito foi marcado por um ambiente de menor liquidez nas negociações do mercado secundário e por uma leve reabertura dos spreads de crédito. Após meses consecutivos de compressão dos prêmios de risco, observou-se um movimento mais cauteloso por parte dos investidores, com os spreads médios dos títulos corporativos indexados ao CDI avançando aproximadamente 0,03%, passando de CDI + 1,19% para CDI + 1,22% ao ano. Apesar desse ajuste, os níveis de prêmio permaneceram próximos das mínimas históricas observadas ao longo do ciclo recente.', 'No mercado secundário, a redução do volume negociado contribuiu para uma formação de preços mais seletiva, especialmente em ativos corporativos com menor liquidez. Ainda assim, o comportamento dos investidores permaneceu construtivo, sustentado por um ambiente técnico favorável e pela continuidade da elevada demanda por ativos de crédito.', 'Já no mercado primário, as emissões bancárias seguiram registrando forte demanda por parte dos investidores. As ofertas de Letras Financeiras Seniores distribuídas ao longo do mês apresentaram níveis elevados de subscrição, com demanda que, em diversos casos, superou três vezes o volume ofertado. Esse forte apetite permitiu que as operações fossem precificadas com taxas inferiores aos limites inicialmente indicados pelos emissores, evidenciando a elevada disponibilidade de recursos para alocação na indústria de crédito. Por outro lado, o pipeline de emissões corporativas permaneceu limitado, restringindo a oferta de novos ativos em um momento de demanda ainda aquecida.', 'Em relação aos fluxos, os fundos com alocação mínima de 15% em crédito e ao menos 1% em debêntures apresentaram captação líquida próxima de R$ 8 bilhões em agosto, resultado significativamente superior ao observado no mês anterior. O volume reforça a percepção de que os investidores seguem direcionando recursos para estratégias de crédito, impulsionados pelo elevado nível de carrego proporcionado pelos ativos indexados ao CDI e pela busca por alternativas de investimento com perfil de risco-retorno atrativo.', 'Nesse contexto, a combinação entre fluxos positivos para a indústria, vencimentos e amortizações recorrentes das carteiras, além da limitada oferta de novos ativos corporativos, continuou sustentando a demanda por crédito privado. Ainda que agosto tenha apresentado uma leve reabertura dos spreads médios de mercado, a dinâmica técnica permanece favorável e os prêmios seguem negociando em patamares historicamente reduzidos.', 'Por fim, sob a ótica da gestão, seguimos acompanhando de forma criteriosa a evolução dos fundamentos dos emissores presentes nas carteiras, com atenção especial aos indicadores operacionais, à geração de caixa e à manutenção de estruturas de capital adequadas. Em um ambiente em que os spreads permanecem comprimidos em termos históricos, mantemos disciplina na alocação dos recursos, priorizando operações que apresentem adequada relação entre risco e retorno e preservando flexibilidade para captura de oportunidades que possam surgir em eventuais períodos de maior volatilidade do mercado.', 'Nesse cenário, o Tivio Institucional 15 apresentou rentabilidade de 1,11% no mês (102% do CDI), acumulando 9,53% (102% do CDI) no ano. Na parcela de corporativos, os maiores atribuidores de resultado foram para Tupy e Randon, enquanto Hapvida foi o maior detrator.']</t>
         </is>
       </c>
     </row>
@@ -5496,17 +5496,17 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>perfrows</t>
+          <t>adm</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>{'pct': ['113%', '101%', '101%']}</t>
+          <t>0,63% a.a.</t>
         </is>
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>{'fundo': ['1,12%', '9,45%', '14,68%', '−', '−', '25,93%'], 'bench': ['1,09%', '9,33%', '14,57%', '−', '−', '25,71%'], 'pct': ['102%', '101%', '101%', '−', '−', '101%']}</t>
+          <t>0,625% a.a.</t>
         </is>
       </c>
     </row>
@@ -5523,17 +5523,17 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>emissores</t>
+          <t>perf</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>[['AEGEA', '2,88%', 100], ['EQUATORIAL', '2,55%', 89], ['TUPY', '2,22%', 77], ['SABESP', '1,94%', 67], ['ENGIE', '1,67%', 58]]</t>
+          <t>20% do que exceder o CDI</t>
         </is>
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>[['C6', '6,00%', 100], ['ABC', '3,78%', 63], ['XP', '3,62%', 60], ['BTG', '3,62%', 60], ['BRADESCO', '1,94%', 32]]</t>
+          <t>20% do que exceder 100% do CDI</t>
         </is>
       </c>
     </row>
@@ -5550,17 +5550,17 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>setores</t>
+          <t>pl</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>[['Financeiro', '33%'], ['FIDC', '15%'], ['Energia Elétrica', '8%'], ['Saneamento', '6%'], ['Transporte e Logística', '5%'], ['Caixa', '16%']]</t>
+          <t>R$ 143.232.764,20</t>
         </is>
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>[['Financeiro', '30,8%'], ['FIDC', '14,4%'], ['Energia Elétrica', '7,8%'], ['Locação de veículos', '4,2%'], ['Saneamento', '3,8%'], ['Caixa', '19,7%']]</t>
+          <t>R$ 126.168.780,56</t>
         </is>
       </c>
     </row>
@@ -5577,17 +5577,17 @@
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>rating</t>
+          <t>plm</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>[['AAA', '46,2%', 100], ['AA+', '24,8%', 54], ['AA', '14,1%', 31], ['AA-', '9,4%', 20], ['A+', '3,9%', 8], ['A', '1,6%', 3]]</t>
+          <t>R$ 155.004.649,74</t>
         </is>
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>[['AAA', '36,0%', 100], ['AA+', '8,6%', 24], ['AA', '4,5%', 13], ['AA-', '6,2%', 17], ['A+', '4,7%', 13], ['A', '6,8%', 19]]</t>
+          <t>R$ 158.893.390,74</t>
         </is>
       </c>
     </row>
@@ -5604,17 +5604,17 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>val</t>
+          <t>perfrows</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>{'pct': ['113%', '101%', '101%']}</t>
         </is>
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>{'fundo': ['1,12%', '9,45%', '14,68%', '−', '−', '25,93%'], 'bench': ['1,09%', '9,33%', '14,57%', '−', '−', '25,71%'], 'pct': ['102%', '101%', '101%', '−', '−', '101%']}</t>
         </is>
       </c>
     </row>
@@ -5631,17 +5631,17 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>val</t>
+          <t>emissores</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>[['AEGEA', '2,88%', 100], ['EQUATORIAL', '2,55%', 89], ['TUPY', '2,22%', 77], ['SABESP', '1,94%', 67], ['ENGIE', '1,67%', 58]]</t>
         </is>
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>1,86</t>
+          <t>[['C6', '6,00%', 100], ['ABC', '3,78%', 63], ['XP', '3,62%', 60], ['BTG', '3,62%', 60], ['BRADESCO', '1,94%', 32]]</t>
         </is>
       </c>
     </row>
@@ -5658,17 +5658,17 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>unit</t>
+          <t>setores</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>anos</t>
+          <t>[['Financeiro', '33%'], ['FIDC', '15%'], ['Energia Elétrica', '8%'], ['Saneamento', '6%'], ['Transporte e Logística', '5%'], ['Caixa', '16%']]</t>
         </is>
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>ano</t>
+          <t>[['Financeiro', '30,8%'], ['FIDC', '14,4%'], ['Energia Elétrica', '7,8%'], ['Locação de veículos', '4,2%'], ['Saneamento', '3,8%'], ['Caixa', '19,7%']]</t>
         </is>
       </c>
     </row>
@@ -5685,17 +5685,17 @@
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>hist12</t>
+          <t>rating</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>[['AAA', '46,2%', 100], ['AA+', '24,8%', 54], ['AA', '14,1%', 31], ['AA-', '9,4%', 20], ['A+', '3,9%', 8], ['A', '1,6%', 3]]</t>
         </is>
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>{'b': 'CDI', 'l': ['2025-08', '2025-09', '2025-10', '2025-11', '2025-12', '2026-01', '2026-02', '2026-03', '2026-04', '2026-05', '2026-06', '2026-07', '2026-08'], 'f': [0.0, 1.3, 2.52, 3.56, 4.85, 6.13, 7.14, 8.01, 9.16, 10.62, 11.95, 13.48, 14.75], 'c': [0.0, 1.22, 2.51, 3.59, 4.85, 6.07, 7.13, 8.43, 9.61, 10.79, 12.03, 13.39, 14.63]}</t>
+          <t>[['AAA', '36,0%', 100], ['AA+', '8,6%', 24], ['AA', '4,5%', 13], ['AA-', '6,2%', 17], ['A+', '4,7%', 13], ['A', '6,8%', 19]]</t>
         </is>
       </c>
     </row>
@@ -5712,17 +5712,17 @@
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>histEnd</t>
+          <t>val</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>[12.12, 12.0, 'CDI']</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>[14.75, 14.63, 'CDI']</t>
+          <t>1,04%</t>
         </is>
       </c>
     </row>
@@ -5739,17 +5739,17 @@
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>comentario</t>
+          <t>val</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>['No mês, o mercado de crédito privado high grade manteve o movimento de fechamento gradual de spreads, com fluxo comprador consistente no secundário e oferta primária ainda concentrada em emissores de primeira linha.', 'A liquidez permaneceu saudável ao longo da curva, com boa demanda por papéis bancários e por debêntures de empresas de energia, saneamento e infraestrutura, setores de maior peso na carteira.', 'Do ponto de vista da gestão, seguimos priorizando emissores de baixo risco de crédito e o controle da duration, mantendo carrego atrativo sobre o CDI sem elevar de forma relevante a volatilidade da cota.', 'O INSTITUCIONAL 30 apresentou rentabilidade de &lt;b&gt;1,36%&lt;/b&gt; no mês (&lt;b&gt;113% do CDI&lt;/b&gt;), acumulando &lt;b&gt;8,08%&lt;/b&gt; no ano. Os principais atribuidores de resultado foram as debêntures corporativas e a parcela bancária da carteira.']</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>['Em agosto, o mercado de crédito foi marcado por um ambiente de menor liquidez nas negociações do mercado secundário e por uma leve reabertura dos spreads de crédito. Após meses consecutivos de compressão dos prêmios de risco, observou-se um movimento mais cauteloso por parte dos investidores, com os spreads médios dos títulos corporativos indexados ao CDI avançando aproximadamente 0,03%, passando de CDI + 1,19% para CDI + 1,22% ao ano. Apesar desse ajuste, os níveis de prêmio permaneceram próximos das mínimas históricas observadas ao longo do ciclo recente.', 'No mercado secundário, a redução do volume negociado contribuiu para uma formação de preços mais seletiva, especialmente em ativos corporativos com menor liquidez. Ainda assim, o comportamento dos investidores permaneceu construtivo, sustentado por um ambiente técnico favorável e pela continuidade da elevada demanda por ativos de crédito.', 'Já no mercado primário, as emissões bancárias seguiram registrando forte demanda por parte dos investidores. As ofertas de Letras Financeiras Seniores distribuídas ao longo do mês apresentaram níveis elevados de subscrição, com demanda que, em diversos casos, superou três vezes o volume ofertado. Esse forte apetite permitiu que as operações fossem precificadas com taxas inferiores aos limites inicialmente indicados pelos emissores, evidenciando a elevada disponibilidade de recursos para alocação na indústria de crédito. Por outro lado, o pipeline de emissões corporativas permaneceu limitado, restringindo a oferta de novos ativos em um momento de demanda ainda aquecida.', 'Em relação aos fluxos, os fundos com alocação mínima de 15% em crédito e ao menos 1% em debêntures apresentaram captação líquida próxima de R$ 8 bilhões em agosto, resultado significativamente superior ao observado no mês anterior. O volume reforça a percepção de que os investidores seguem direcionando recursos para estratégias de crédito, impulsionados pelo elevado nível de carrego proporcionado pelos ativos indexados ao CDI e pela busca por alternativas de investimento com perfil de risco-retorno atrativo.', 'Nesse contexto, a combinação entre fluxos positivos para a indústria, vencimentos e amortizações recorrentes das carteiras, além da limitada oferta de novos ativos corporativos, continuou sustentando a demanda por crédito privado. Ainda que agosto tenha apresentado uma leve reabertura dos spreads médios de mercado, a dinâmica técnica permanece favorável e os prêmios seguem negociando em patamares historicamente reduzidos.', 'Por fim, sob a ótica da gestão, seguimos acompanhando de forma criteriosa a evolução dos fundamentos dos emissores presentes nas carteiras, com atenção especial aos indicadores operacionais, à geração de caixa e à manutenção de estruturas de capital adequadas. Em um ambiente em que os spreads permanecem comprimidos em termos históricos, mantemos disciplina na alocação dos recursos, priorizando operações que apresentem adequada relação entre risco e retorno e preservando flexibilidade para captura de oportunidades que possam surgir em eventuais períodos de maior volatilidade do mercado.', 'Nesse cenário, o Tivio Institucional 30 apresentou rentabilidade de 1,12% no mês (102% do CDI), acumulando 9,45% (101% do CDI) no ano. Na parcela de corporativos, os maiores atribuidores de resultado foram para Tupy e Randon, enquanto Hapvida foi o maior detrator.']</t>
+          <t>1,86</t>
         </is>
       </c>
     </row>
@@ -5761,22 +5761,22 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>infraplus</t>
+          <t>inst30</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>pl</t>
+          <t>unit</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>R$ 42.983.282,75</t>
+          <t>anos</t>
         </is>
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>R$ 42.694.019,75</t>
+          <t>ano</t>
         </is>
       </c>
     </row>
@@ -5788,22 +5788,22 @@
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>infraplus</t>
+          <t>inst30</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>plm</t>
+          <t>hist12</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>R$ 52.049.593,91</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>R$ 49.421.174,50</t>
+          <t>{'b': 'CDI', 'l': ['2025-08', '2025-09', '2025-10', '2025-11', '2025-12', '2026-01', '2026-02', '2026-03', '2026-04', '2026-05', '2026-06', '2026-07', '2026-08'], 'f': [0.0, 1.3, 2.52, 3.56, 4.85, 6.13, 7.14, 8.01, 9.16, 10.62, 11.95, 13.48, 14.75], 'c': [0.0, 1.22, 2.51, 3.59, 4.85, 6.07, 7.13, 8.43, 9.61, 10.79, 12.03, 13.39, 14.63]}</t>
         </is>
       </c>
     </row>
@@ -5815,22 +5815,22 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>infraplus</t>
+          <t>inst30</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>perfrows</t>
+          <t>histEnd</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>{'abs': ['1,24%', '7,80%', '12,94%'], 'alfa': ['−0,14%', '−3,14%', '−2,75%']}</t>
+          <t>[12.12, 12.0, 'CDI']</t>
         </is>
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>{'fundo': ['1,26%', '5,98%', '9,91%', '19,03%', '29,49%', '77,41%'], 'bench': ['1,28%', '9,18%', '13,34%', '23,32%', '33,11%', '87,91%'], 'abs': ['1,26%', '5,98%', '9,91%', '19,03%', '29,49%', '77,41%'], 'alfa': ['−0,01%', '−3,20%', '−3,44%', '−4,28%', '−3,62%', '−10,50%']}</t>
+          <t>[14.75, 14.63, 'CDI']</t>
         </is>
       </c>
     </row>
@@ -5842,22 +5842,22 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>infraplus</t>
+          <t>inst30</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>emissores</t>
+          <t>comentario</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>[['EQUATORIAL', '3,87%', 100], ['CEMIG', '3,42%', 88], ['COPEL', '3,14%', 81], ['SABESP', '3,03%', 78], ['ELETROBRAS', '2,92%', 75]]</t>
+          <t>['No mês, o mercado de crédito privado high grade manteve o movimento de fechamento gradual de spreads, com fluxo comprador consistente no secundário e oferta primária ainda concentrada em emissores de primeira linha.', 'A liquidez permaneceu saudável ao longo da curva, com boa demanda por papéis bancários e por debêntures de empresas de energia, saneamento e infraestrutura, setores de maior peso na carteira.', 'Do ponto de vista da gestão, seguimos priorizando emissores de baixo risco de crédito e o controle da duration, mantendo carrego atrativo sobre o CDI sem elevar de forma relevante a volatilidade da cota.', 'O INSTITUCIONAL 30 apresentou rentabilidade de &lt;b&gt;1,36%&lt;/b&gt; no mês (&lt;b&gt;113% do CDI&lt;/b&gt;), acumulando &lt;b&gt;8,08%&lt;/b&gt; no ano. Os principais atribuidores de resultado foram as debêntures corporativas e a parcela bancária da carteira.']</t>
         </is>
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>[['AUREN', '7,68%', 100], ['EQUATORIAL', '7,24%', 94], ['EDF', '5,54%', 72], ['SINOP', '3,99%', 52], ['ELETROBRAS', '3,65%', 48]]</t>
+          <t>['Em agosto, o mercado de crédito foi marcado por um ambiente de menor liquidez nas negociações do mercado secundário e por uma leve reabertura dos spreads de crédito. Após meses consecutivos de compressão dos prêmios de risco, observou-se um movimento mais cauteloso por parte dos investidores, com os spreads médios dos títulos corporativos indexados ao CDI avançando aproximadamente 0,03%, passando de CDI + 1,19% para CDI + 1,22% ao ano. Apesar desse ajuste, os níveis de prêmio permaneceram próximos das mínimas históricas observadas ao longo do ciclo recente.', 'No mercado secundário, a redução do volume negociado contribuiu para uma formação de preços mais seletiva, especialmente em ativos corporativos com menor liquidez. Ainda assim, o comportamento dos investidores permaneceu construtivo, sustentado por um ambiente técnico favorável e pela continuidade da elevada demanda por ativos de crédito.', 'Já no mercado primário, as emissões bancárias seguiram registrando forte demanda por parte dos investidores. As ofertas de Letras Financeiras Seniores distribuídas ao longo do mês apresentaram níveis elevados de subscrição, com demanda que, em diversos casos, superou três vezes o volume ofertado. Esse forte apetite permitiu que as operações fossem precificadas com taxas inferiores aos limites inicialmente indicados pelos emissores, evidenciando a elevada disponibilidade de recursos para alocação na indústria de crédito. Por outro lado, o pipeline de emissões corporativas permaneceu limitado, restringindo a oferta de novos ativos em um momento de demanda ainda aquecida.', 'Em relação aos fluxos, os fundos com alocação mínima de 15% em crédito e ao menos 1% em debêntures apresentaram captação líquida próxima de R$ 8 bilhões em agosto, resultado significativamente superior ao observado no mês anterior. O volume reforça a percepção de que os investidores seguem direcionando recursos para estratégias de crédito, impulsionados pelo elevado nível de carrego proporcionado pelos ativos indexados ao CDI e pela busca por alternativas de investimento com perfil de risco-retorno atrativo.', 'Nesse contexto, a combinação entre fluxos positivos para a indústria, vencimentos e amortizações recorrentes das carteiras, além da limitada oferta de novos ativos corporativos, continuou sustentando a demanda por crédito privado. Ainda que agosto tenha apresentado uma leve reabertura dos spreads médios de mercado, a dinâmica técnica permanece favorável e os prêmios seguem negociando em patamares historicamente reduzidos.', 'Por fim, sob a ótica da gestão, seguimos acompanhando de forma criteriosa a evolução dos fundamentos dos emissores presentes nas carteiras, com atenção especial aos indicadores operacionais, à geração de caixa e à manutenção de estruturas de capital adequadas. Em um ambiente em que os spreads permanecem comprimidos em termos históricos, mantemos disciplina na alocação dos recursos, priorizando operações que apresentem adequada relação entre risco e retorno e preservando flexibilidade para captura de oportunidades que possam surgir em eventuais períodos de maior volatilidade do mercado.', 'Nesse cenário, o Tivio Institucional 30 apresentou rentabilidade de 1,12% no mês (102% do CDI), acumulando 9,45% (101% do CDI) no ano. Na parcela de corporativos, os maiores atribuidores de resultado foram para Tupy e Randon, enquanto Hapvida foi o maior detrator.']</t>
         </is>
       </c>
     </row>
@@ -5874,17 +5874,17 @@
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>setores</t>
+          <t>pl</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>[['Energia Elétrica', '55%'], ['Transporte e Logística', '15%'], ['Saneamento', '7%'], ['Petróleo e Gás', '5%'], ['TI e Telecomunicações', '4%'], ['Caixa', '5%']]</t>
+          <t>R$ 42.983.282,75</t>
         </is>
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>[['Energia Elétrica', '55,9%'], ['Transporte e Logística', '15,3%'], ['Saneamento', '7,3%'], ['TI e Telecomunicações', '5,4%'], ['Petróleo e Gás', '4,8%'], ['Caixa', '4,8%']]</t>
+          <t>R$ 42.694.019,75</t>
         </is>
       </c>
     </row>
@@ -5901,17 +5901,17 @@
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>rating</t>
+          <t>plm</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>[['AAA', '32,35%', 100], ['AA+', '17,91%', 55], ['AA', '11,27%', 35], ['AA-', '15,61%', 48], ['A+', '7,15%', 22], ['A', '1,85%', 6]]</t>
+          <t>R$ 52.049.593,91</t>
         </is>
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>[['AAA', '35,4%', 100], ['AA+', '26,0%', 74], ['AA', '11,1%', 31], ['AA-', '8,8%', 25], ['A+', '5,1%', 14], ['A', '2,4%', 7]]</t>
+          <t>R$ 49.421.174,50</t>
         </is>
       </c>
     </row>
@@ -5928,17 +5928,17 @@
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>val</t>
+          <t>perfrows</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>8,63%</t>
+          <t>{'abs': ['1,24%', '7,80%', '12,94%'], 'alfa': ['−0,14%', '−3,14%', '−2,75%']}</t>
         </is>
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>8,23%</t>
+          <t>{'fundo': ['1,26%', '5,98%', '9,91%', '19,03%', '29,49%', '77,41%'], 'bench': ['1,28%', '9,18%', '13,34%', '23,32%', '33,11%', '87,91%'], 'abs': ['1,26%', '5,98%', '9,91%', '19,03%', '29,49%', '77,41%'], 'alfa': ['−0,01%', '−3,20%', '−3,44%', '−4,28%', '−3,62%', '−10,50%']}</t>
         </is>
       </c>
     </row>
@@ -5955,17 +5955,17 @@
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>val</t>
+          <t>emissores</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>4,00</t>
+          <t>[['EQUATORIAL', '3,87%', 100], ['CEMIG', '3,42%', 88], ['COPEL', '3,14%', 81], ['SABESP', '3,03%', 78], ['ELETROBRAS', '2,92%', 75]]</t>
         </is>
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>3,98</t>
+          <t>[['AUREN', '7,68%', 100], ['EQUATORIAL', '7,24%', 94], ['EDF', '5,54%', 72], ['SINOP', '3,99%', 52], ['ELETROBRAS', '3,65%', 48]]</t>
         </is>
       </c>
     </row>
@@ -5982,17 +5982,17 @@
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>hist12</t>
+          <t>setores</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>[['Energia Elétrica', '55%'], ['Transporte e Logística', '15%'], ['Saneamento', '7%'], ['Petróleo e Gás', '5%'], ['TI e Telecomunicações', '4%'], ['Caixa', '5%']]</t>
         </is>
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>{'b': 'IMA-B 5', 'l': ['2025-08', '2025-09', '2025-10', '2025-11', '2025-12', '2026-01', '2026-02', '2026-03', '2026-04', '2026-05', '2026-06', '2026-07', '2026-08'], 'f': [0.0, 1.64, 1.66, 3.1, 3.59, 5.89, 6.95, 6.67, 6.97, 7.26, 7.24, 8.41, 9.78], 'c': [0.0, 0.66, 1.69, 2.78, 3.76, 5.01, 6.29, 7.77, 9.19, 10.24, 10.48, 11.85, 13.28]}</t>
+          <t>[['Energia Elétrica', '55,9%'], ['Transporte e Logística', '15,3%'], ['Saneamento', '7,3%'], ['TI e Telecomunicações', '5,4%'], ['Petróleo e Gás', '4,8%'], ['Caixa', '4,8%']]</t>
         </is>
       </c>
     </row>
@@ -6009,17 +6009,17 @@
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>histEnd</t>
+          <t>rating</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>[12.94, 15.69, 'IMA-B 5']</t>
+          <t>[['AAA', '32,35%', 100], ['AA+', '17,91%', 55], ['AA', '11,27%', 35], ['AA-', '15,61%', 48], ['A+', '7,15%', 22], ['A', '1,85%', 6]]</t>
         </is>
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>[9.78, 13.28, 'IMA-B 5']</t>
+          <t>[['AAA', '35,4%', 100], ['AA+', '26,0%', 74], ['AA', '11,1%', 31], ['AA-', '8,8%', 25], ['A+', '5,1%', 14], ['A', '2,4%', 7]]</t>
         </is>
       </c>
     </row>
@@ -6036,17 +6036,17 @@
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>comentario</t>
+          <t>val</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>['Em julho, os títulos de crédito indexados ao IPCA precificados pela ANBIMA apresentaram desempenho negativo, refletindo a elevação da curva real de juros ao longo do período. Embora os spreads de crédito tenham fechado cerca de 16 bps em relação ao mês anterior, o avanço da curva de juros reais prevaleceu sobre esse efeito.', 'No mercado primário, manteve-se o cenário de oferta restrita, com parcela relevante das emissões sendo absorvida pelos balanços dos bancos distribuidores. No secundário, houve retomada da demanda por papéis incentivados, inclusive nos vencimentos mais longos.', 'Do ponto de vista da gestão, mantivemos postura cautelosa, priorizando o encurtamento da duration da carteira como forma de mitigar volatilidade e reduzir a sensibilidade a movimentos adversos nos spreads.', 'O Infra Plus apresentou rentabilidade, isenta de imposto de renda, de &lt;b&gt;1,24%&lt;/b&gt; no mês, acumulando &lt;b&gt;7,80%&lt;/b&gt; no ano. Destacam-se as debêntures de RUMO e NTS, enquanto Alloha Fibra foi a maior detratora.']</t>
+          <t>8,63%</t>
         </is>
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>['Em agosto, os títulos de crédito indexados ao IPCA precificados pela ANBIMA apresentaram desempenho positivo, refletindo principalmente o movimento de fechamento da curva real de juros observado ao longo do período. Embora os spreads de crédito tenham registrado abertura média de aproximadamente 5 bps em relação a julho, a redução das taxas reais ao longo da estrutura a termo mais do que compensou esse movimento. Como resultado, as taxas médias dos títulos incentivados precificados pela ANBIMA encerraram o mês com fechamento próximo de 16 bps, proporcionando valorização dos ativos no mercado secundário.', 'No mercado primário, manteve-se o cenário de oferta restrita de ativos, com parcela relevante das emissões sendo absorvida diretamente pelos balanços dos bancos distribuidores. Já no mercado secundário, observou-se um nível de liquidez inferior à média observada ao longo de 2025, contribuindo para um ambiente de maior equilíbrio entre oferta e demanda dos ativos negociados.', 'Sob a ótica da gestão, mantivemos uma postura cautelosa ao longo do período, priorizando o encurtamento da duration da carteira como forma de mitigar a volatilidade e reduzir a sensibilidade do portfólio a eventuais movimentos adversos nos spreads de crédito. Apesar da melhora observada no desempenho dos ativos incentivados no mês, seguimos avaliando que os níveis atuais de prêmio ainda oferecem pouca margem de segurança frente aos riscos inerentes à classe. Dessa forma, permanecemos atentos à evolução das condições de mercado e à dinâmica de precificação dos ativos, buscando identificar oportunidades mais atrativas para aumentar a exposição ao risco de crédito de forma gradual e criteriosa, quando a relação risco-retorno se mostrar mais favorável.', 'Nesse cenário, o Tivio Infra Plus apresentou rentabilidade, isenta de imposto de renda de 1,26% no mês, acumulando 5,98% no ano. Na atribuição de performance, pode-se destacar as debêntures de NTS e São Simão, enquanto as de Jalles Machado foram as maiores detratoras.']</t>
+          <t>8,23%</t>
         </is>
       </c>
     </row>
@@ -6058,22 +6058,22 @@
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>infraplus</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>val</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>31/07/2026</t>
+          <t>4,00</t>
         </is>
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>31/08/2026</t>
+          <t>3,98</t>
         </is>
       </c>
     </row>
@@ -6085,22 +6085,22 @@
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>infraplus</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>hist12</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>Julho de 2026</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>Agosto de 2026</t>
+          <t>{'b': 'IMA-B 5', 'l': ['2025-08', '2025-09', '2025-10', '2025-11', '2025-12', '2026-01', '2026-02', '2026-03', '2026-04', '2026-05', '2026-06', '2026-07', '2026-08'], 'f': [0.0, 1.64, 1.66, 3.1, 3.59, 5.89, 6.95, 6.67, 6.97, 7.26, 7.24, 8.41, 9.78], 'c': [0.0, 0.66, 1.69, 2.78, 3.76, 5.01, 6.29, 7.77, 9.19, 10.24, 10.48, 11.85, 13.28]}</t>
         </is>
       </c>
     </row>
@@ -6112,22 +6112,22 @@
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>infraplus</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>histEnd</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>julho de 2026</t>
+          <t>[12.94, 15.69, 'IMA-B 5']</t>
         </is>
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>agosto de 2026</t>
+          <t>[9.78, 13.28, 'IMA-B 5']</t>
         </is>
       </c>
     </row>
@@ -6139,22 +6139,22 @@
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>infraplus</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>comentario</t>
         </is>
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>Julho 2026</t>
+          <t>['Em julho, os títulos de crédito indexados ao IPCA precificados pela ANBIMA apresentaram desempenho negativo, refletindo a elevação da curva real de juros ao longo do período. Embora os spreads de crédito tenham fechado cerca de 16 bps em relação ao mês anterior, o avanço da curva de juros reais prevaleceu sobre esse efeito.', 'No mercado primário, manteve-se o cenário de oferta restrita, com parcela relevante das emissões sendo absorvida pelos balanços dos bancos distribuidores. No secundário, houve retomada da demanda por papéis incentivados, inclusive nos vencimentos mais longos.', 'Do ponto de vista da gestão, mantivemos postura cautelosa, priorizando o encurtamento da duration da carteira como forma de mitigar volatilidade e reduzir a sensibilidade a movimentos adversos nos spreads.', 'O Infra Plus apresentou rentabilidade, isenta de imposto de renda, de &lt;b&gt;1,24%&lt;/b&gt; no mês, acumulando &lt;b&gt;7,80%&lt;/b&gt; no ano. Destacam-se as debêntures de RUMO e NTS, enquanto Alloha Fibra foi a maior detratora.']</t>
         </is>
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>Agosto 2026</t>
+          <t>['Em agosto, os títulos de crédito indexados ao IPCA precificados pela ANBIMA apresentaram desempenho positivo, refletindo principalmente o movimento de fechamento da curva real de juros observado ao longo do período. Embora os spreads de crédito tenham registrado abertura média de aproximadamente 5 bps em relação a julho, a redução das taxas reais ao longo da estrutura a termo mais do que compensou esse movimento. Como resultado, as taxas médias dos títulos incentivados precificados pela ANBIMA encerraram o mês com fechamento próximo de 16 bps, proporcionando valorização dos ativos no mercado secundário.', 'No mercado primário, manteve-se o cenário de oferta restrita de ativos, com parcela relevante das emissões sendo absorvida diretamente pelos balanços dos bancos distribuidores. Já no mercado secundário, observou-se um nível de liquidez inferior à média observada ao longo de 2025, contribuindo para um ambiente de maior equilíbrio entre oferta e demanda dos ativos negociados.', 'Sob a ótica da gestão, mantivemos uma postura cautelosa ao longo do período, priorizando o encurtamento da duration da carteira como forma de mitigar a volatilidade e reduzir a sensibilidade do portfólio a eventuais movimentos adversos nos spreads de crédito. Apesar da melhora observada no desempenho dos ativos incentivados no mês, seguimos avaliando que os níveis atuais de prêmio ainda oferecem pouca margem de segurança frente aos riscos inerentes à classe. Dessa forma, permanecemos atentos à evolução das condições de mercado e à dinâmica de precificação dos ativos, buscando identificar oportunidades mais atrativas para aumentar a exposição ao risco de crédito de forma gradual e criteriosa, quando a relação risco-retorno se mostrar mais favorável.', 'Nesse cenário, o Tivio Infra Plus apresentou rentabilidade, isenta de imposto de renda de 1,26% no mês, acumulando 5,98% no ano. Na atribuição de performance, pode-se destacar as debêntures de NTS e São Simão, enquanto as de Jalles Machado foram as maiores detratoras.']</t>
         </is>
       </c>
     </row>
@@ -6176,12 +6176,12 @@
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>-jul26</t>
+          <t>31/07/2026</t>
         </is>
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>-ago26</t>
+          <t>31/08/2026</t>
         </is>
       </c>
     </row>
@@ -6203,12 +6203,12 @@
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>julho/2026</t>
+          <t>Julho de 2026</t>
         </is>
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>agosto/2026</t>
+          <t>Agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -6230,12 +6230,12 @@
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>const A=6;const track</t>
+          <t>julho de 2026</t>
         </is>
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>const A=7;const track</t>
+          <t>agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -6252,125 +6252,125 @@
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>libs de exportação</t>
+          <t>data</t>
         </is>
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>CDN</t>
+          <t>Julho 2026</t>
         </is>
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>4 referências → vendor/ local (CDN como reserva)</t>
+          <t>Agosto 2026</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>tivio-central.html</t>
+          <t>tivio-relatorio-gestao-credito-privado.html</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>s1</t>
+          <t>—</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>data</t>
         </is>
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>Julho 2026</t>
+          <t>-jul26</t>
         </is>
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>Agosto 2026</t>
+          <t>-ago26</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>tivio-central.html</t>
+          <t>tivio-relatorio-gestao-credito-privado.html</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>s2</t>
+          <t>—</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>data</t>
         </is>
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>Julho 2026</t>
+          <t>julho/2026</t>
         </is>
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>Agosto 2026</t>
+          <t>agosto/2026</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>tivio-central.html</t>
+          <t>tivio-relatorio-gestao-credito-privado.html</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>s8</t>
+          <t>—</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>data</t>
         </is>
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>Julho 2026</t>
+          <t>const A=6;const track</t>
         </is>
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>Agosto 2026</t>
+          <t>const A=7;const track</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>tivio-central.html</t>
+          <t>tivio-relatorio-gestao-credito-privado.html</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>r1</t>
+          <t>—</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>libs de exportação</t>
         </is>
       </c>
       <c r="D220" t="inlineStr">
         <is>
-          <t>Julho 2026</t>
+          <t>CDN</t>
         </is>
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>Agosto 2026</t>
+          <t>4 referências → vendor/ local (CDN como reserva)</t>
         </is>
       </c>
     </row>
@@ -6382,7 +6382,7 @@
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>e1</t>
+          <t>s1</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
@@ -6409,22 +6409,22 @@
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>s2</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>Central</t>
+          <t>date</t>
         </is>
       </c>
       <c r="D222" t="inlineStr">
         <is>
-          <t>cards de relatório</t>
+          <t>Julho 2026</t>
         </is>
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>13 registrados para Agosto 2026</t>
+          <t>Agosto 2026</t>
         </is>
       </c>
     </row>
@@ -6436,16 +6436,232 @@
       </c>
       <c r="B223" t="inlineStr">
         <is>
+          <t>s8</t>
+        </is>
+      </c>
+      <c r="C223" t="inlineStr">
+        <is>
+          <t>date</t>
+        </is>
+      </c>
+      <c r="D223" t="inlineStr">
+        <is>
+          <t>Julho 2026</t>
+        </is>
+      </c>
+      <c r="E223" t="inlineStr">
+        <is>
+          <t>Agosto 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>tivio-central.html</t>
+        </is>
+      </c>
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>r1</t>
+        </is>
+      </c>
+      <c r="C224" t="inlineStr">
+        <is>
+          <t>date</t>
+        </is>
+      </c>
+      <c r="D224" t="inlineStr">
+        <is>
+          <t>Julho 2026</t>
+        </is>
+      </c>
+      <c r="E224" t="inlineStr">
+        <is>
+          <t>Agosto 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>tivio-central.html</t>
+        </is>
+      </c>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>e1</t>
+        </is>
+      </c>
+      <c r="C225" t="inlineStr">
+        <is>
+          <t>date</t>
+        </is>
+      </c>
+      <c r="D225" t="inlineStr">
+        <is>
+          <t>Julho 2026</t>
+        </is>
+      </c>
+      <c r="E225" t="inlineStr">
+        <is>
+          <t>Agosto 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>tivio-central.html</t>
+        </is>
+      </c>
+      <c r="B226" t="inlineStr">
+        <is>
+          <t>r1</t>
+        </is>
+      </c>
+      <c r="C226" t="inlineStr">
+        <is>
+          <t>title</t>
+        </is>
+      </c>
+      <c r="D226" t="inlineStr">
+        <is>
+          <t>Relatórios de Gestão · Crédito Privado</t>
+        </is>
+      </c>
+      <c r="E226" t="inlineStr">
+        <is>
+          <t>Gerador de Relatório de Gestão · Crédito Privado</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>tivio-central.html</t>
+        </is>
+      </c>
+      <c r="B227" t="inlineStr">
+        <is>
+          <t>r1</t>
+        </is>
+      </c>
+      <c r="C227" t="inlineStr">
+        <is>
+          <t>desc</t>
+        </is>
+      </c>
+      <c r="D227" t="inlineStr">
+        <is>
+          <t>Relatório completo de 4 páginas (A4) por fundo, Banks, Institucional, Institucional 15, Institucional 30 e Infra Plus: objetivo, rentabilidade, emissores, alocação e rating; histórico e comentário do gestor; mercado de crédito; e características + disclaimer. Exportação em JPG e PDF.</t>
+        </is>
+      </c>
+      <c r="E227" t="inlineStr">
+        <is>
+          <t>Construtor interativo, folha a folha. Os relatórios prontos do mês estão no card acima. Relatório completo de 4 páginas (A4) por fundo, Banks, Institucional, Institucional 15, Institucional 30 e Infra Plus: objetivo, rentabilidade, emissores, alocação e rating; histórico e comentário do gestor; mercado de crédito; e características + disclaimer. Exportação em JPG e PDF.</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>tivio-central.html</t>
+        </is>
+      </c>
+      <c r="B228" t="inlineStr">
+        <is>
+          <t>r2</t>
+        </is>
+      </c>
+      <c r="C228" t="inlineStr">
+        <is>
+          <t>title</t>
+        </is>
+      </c>
+      <c r="D228" t="inlineStr">
+        <is>
+          <t>Relatório de Gestão · Incentivado CDI 30</t>
+        </is>
+      </c>
+      <c r="E228" t="inlineStr">
+        <is>
+          <t>Gerador de Relatório de Gestão · Incentivado CDI 30</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>tivio-central.html</t>
+        </is>
+      </c>
+      <c r="B229" t="inlineStr">
+        <is>
+          <t>r2</t>
+        </is>
+      </c>
+      <c r="C229" t="inlineStr">
+        <is>
+          <t>desc</t>
+        </is>
+      </c>
+      <c r="D229" t="inlineStr">
+        <is>
+          <t>Relatório de gestão mensal do Tivio Institucional Inc CDI 30 FIF (debêntures incentivadas · CDI).</t>
+        </is>
+      </c>
+      <c r="E229" t="inlineStr">
+        <is>
+          <t>Construtor interativo, folha a folha. Os relatórios prontos do mês estão no card acima. Relatório de gestão mensal do Tivio Institucional Inc CDI 30 FIF (debêntures incentivadas · CDI).</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>tivio-central.html</t>
+        </is>
+      </c>
+      <c r="B230" t="inlineStr">
+        <is>
           <t>—</t>
         </is>
       </c>
-      <c r="C223" t="inlineStr">
+      <c r="C230" t="inlineStr">
+        <is>
+          <t>Central</t>
+        </is>
+      </c>
+      <c r="D230" t="inlineStr">
+        <is>
+          <t>cards de relatório</t>
+        </is>
+      </c>
+      <c r="E230" t="inlineStr">
+        <is>
+          <t>2 registrados para Agosto 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>tivio-central.html</t>
+        </is>
+      </c>
+      <c r="B231" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C231" t="inlineStr">
         <is>
           <t>data automática</t>
         </is>
       </c>
-      <c r="D223" t="inlineStr"/>
-      <c r="E223" t="inlineStr">
+      <c r="D231" t="inlineStr"/>
+      <c r="E231" t="inlineStr">
         <is>
           <t>DATA_BASE=2026-08-31</t>
         </is>
@@ -12932,7 +13148,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C23"/>
+  <dimension ref="A1:C24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
@@ -13283,51 +13499,68 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>tivio-email-fundos-credito.html</t>
+          <t>relatorio/credito_privado</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>alt180</t>
+          <t>bvp</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>o texto se refere a "julho" como o mês corrente — a data base é agosto</t>
+          <t>logo não encontrado em assets/logos (procurei "tivio_bvp")</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>tivio-post-investment-solutions.html</t>
+          <t>tivio-email-fundos-credito.html</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>topgestormacro</t>
+          <t>alt180</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>sem dados — rentabilidade e PL mantidos</t>
+          <t>o texto se refere a "julho" como o mês corrente — a data base é agosto</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
+          <t>tivio-post-investment-solutions.html</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>topgestormacro</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>sem dados — rentabilidade e PL mantidos</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
           <t>tivio-central.html</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
+      <c r="B24" t="inlineStr">
         <is>
           <t>tivio-central.html</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>card "Relatório de Gestão · Incentivado CDI 30" removido: aponta para "Tivio Incentivado CDI 30 - Relatório de Gestão Mensal.html", que não existe nesta edição</t>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>card "Gerador de Relatório de Gestão · Incentivado CDI 30" removido: aponta para "Tivio Incentivado CDI 30 - Relatório de Gestão Mensal.html", que não existe nesta edição</t>
         </is>
       </c>
     </row>
@@ -13342,7 +13575,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C48"/>
+  <dimension ref="A1:C37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="58" customWidth="1" min="1" max="1"/>
@@ -13370,706 +13603,541 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Tivio Banks - Relatório de Gestão - Agosto 2026.html</t>
+          <t>Tivio Banks - Relatório de Gestão - Agosto 2026.pdf</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>html</t>
+          <t>pdf</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>337714</v>
+        <v>362956</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Tivio Institucional - Relatório de Gestão - Agosto 2026.html</t>
+          <t>Tivio Banks - Relatório de Gestão - Agosto 2026.pptx</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>html</t>
+          <t>pptx</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>345960</v>
+        <v>47619</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Tivio Institucional 15 - Relatório de Gestão - Agosto 2026.html</t>
+          <t>Tivio Institucional - Relatório de Gestão - Agosto 2026.pdf</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>html</t>
+          <t>pdf</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>348537</v>
+        <v>372505</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Tivio Institucional 30 - Relatório de Gestão - Agosto 2026.html</t>
+          <t>Tivio Institucional - Relatório de Gestão - Agosto 2026.pptx</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>html</t>
+          <t>pptx</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>350499</v>
+        <v>47823</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Tivio Infra Plus - Relatório de Gestão - Agosto 2026.html</t>
+          <t>Tivio Institucional 15 - Relatório de Gestão - Agosto 2026.pdf</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>html</t>
+          <t>pdf</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>341721</v>
+        <v>375141</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Tivio BVP - Relatório de Gestão - Agosto 2026.html</t>
+          <t>Tivio Institucional 15 - Relatório de Gestão - Agosto 2026.pptx</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>html</t>
+          <t>pptx</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>325134</v>
+        <v>47845</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Tivio RF CP - Relatório de Gestão - Agosto 2026.html</t>
+          <t>Tivio Institucional 30 - Relatório de Gestão - Agosto 2026.pdf</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>html</t>
+          <t>pdf</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>338290</v>
+        <v>372749</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Tivio ALT 180 - Relatório de Gestão - Agosto 2026.html</t>
+          <t>Tivio Institucional 30 - Relatório de Gestão - Agosto 2026.pptx</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>html</t>
+          <t>pptx</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>328509</v>
+        <v>47694</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Tivio ALT 90 - Relatório de Gestão - Agosto 2026.html</t>
+          <t>Tivio Infra Plus - Relatório de Gestão - Agosto 2026.pdf</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>html</t>
+          <t>pdf</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>327610</v>
+        <v>359845</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Tivio ALT Light - Relatório de Gestão - Agosto 2026.html</t>
+          <t>Tivio Infra Plus - Relatório de Gestão - Agosto 2026.pptx</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>html</t>
+          <t>pptx</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>327741</v>
+        <v>46722</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Tivio Infra Plus CDI - Relatório de Gestão - Agosto 2026.html</t>
+          <t>Tivio BVP - Relatório de Gestão - Agosto 2026.pdf</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>html</t>
+          <t>pdf</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>348878</v>
+        <v>362036</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Tivio Esplanada - Relatório de Gestão - Agosto 2026.html</t>
+          <t>Tivio BVP - Relatório de Gestão - Agosto 2026.pptx</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>html</t>
+          <t>pptx</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>331377</v>
+        <v>47649</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Tivio Legacy Prev - Relatório de Gestão - Agosto 2026.html</t>
+          <t>Tivio RF CP - Relatório de Gestão - Agosto 2026.pdf</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>html</t>
+          <t>pdf</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>333666</v>
+        <v>362558</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Tivio Banks - Relatório de Gestão - Agosto 2026.pdf</t>
+          <t>Tivio RF CP - Relatório de Gestão - Agosto 2026.pptx</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>pdf</t>
+          <t>pptx</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>349660</v>
+        <v>47696</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Tivio Banks - Relatório de Gestão - Agosto 2026.pptx</t>
+          <t>Tivio ALT 180 - Relatório de Gestão - Agosto 2026.pdf</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>pptx</t>
+          <t>pdf</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>47618</v>
+        <v>331968</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Tivio Institucional - Relatório de Gestão - Agosto 2026.pdf</t>
+          <t>Tivio ALT 180 - Relatório de Gestão - Agosto 2026.pptx</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>pdf</t>
+          <t>pptx</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>356572</v>
+        <v>43234</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Tivio Institucional - Relatório de Gestão - Agosto 2026.pptx</t>
+          <t>Tivio ALT 90 - Relatório de Gestão - Agosto 2026.pdf</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>pptx</t>
+          <t>pdf</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>47822</v>
+        <v>331174</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Tivio Institucional 15 - Relatório de Gestão - Agosto 2026.pdf</t>
+          <t>Tivio ALT 90 - Relatório de Gestão - Agosto 2026.pptx</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>pdf</t>
+          <t>pptx</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>359553</v>
+        <v>43205</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Tivio Institucional 15 - Relatório de Gestão - Agosto 2026.pptx</t>
+          <t>Tivio ALT Light - Relatório de Gestão - Agosto 2026.pdf</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>pptx</t>
+          <t>pdf</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>47845</v>
+        <v>346891</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Tivio Institucional 30 - Relatório de Gestão - Agosto 2026.pdf</t>
+          <t>Tivio ALT Light - Relatório de Gestão - Agosto 2026.pptx</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>pdf</t>
+          <t>pptx</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>357406</v>
+        <v>42082</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Tivio Institucional 30 - Relatório de Gestão - Agosto 2026.pptx</t>
+          <t>Tivio Infra Plus CDI - Relatório de Gestão - Agosto 2026.pdf</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>pptx</t>
+          <t>pdf</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>47695</v>
+        <v>365878</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Tivio Infra Plus - Relatório de Gestão - Agosto 2026.pdf</t>
+          <t>Tivio Infra Plus CDI - Relatório de Gestão - Agosto 2026.pptx</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>pdf</t>
+          <t>pptx</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>349868</v>
+        <v>47115</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Tivio Infra Plus - Relatório de Gestão - Agosto 2026.pptx</t>
+          <t>Tivio Esplanada - Relatório de Gestão - Agosto 2026.pdf</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>pptx</t>
+          <t>pdf</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>46723</v>
+        <v>359091</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Tivio BVP - Relatório de Gestão - Agosto 2026.pdf</t>
+          <t>Tivio Esplanada - Relatório de Gestão - Agosto 2026.pptx</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>pdf</t>
+          <t>pptx</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>346073</v>
+        <v>46717</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Tivio BVP - Relatório de Gestão - Agosto 2026.pptx</t>
+          <t>Tivio Legacy Prev - Relatório de Gestão - Agosto 2026.pdf</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>pptx</t>
+          <t>pdf</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>47654</v>
+        <v>362344</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Tivio RF CP - Relatório de Gestão - Agosto 2026.pdf</t>
+          <t>Tivio Legacy Prev - Relatório de Gestão - Agosto 2026.pptx</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>pdf</t>
+          <t>pptx</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>346414</v>
+        <v>47667</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Tivio RF CP - Relatório de Gestão - Agosto 2026.pptx</t>
+          <t>Relatório de Gestão - Crédito Privado - Agosto 2026.html</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>pptx</t>
+          <t>html</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>47691</v>
+        <v>3061451</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Tivio ALT 180 - Relatório de Gestão - Agosto 2026.pdf</t>
+          <t>Relatório de Gestão - Crédito Estruturado - Agosto 2026.html</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>pdf</t>
+          <t>html</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>323363</v>
+        <v>916067</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Tivio ALT 180 - Relatório de Gestão - Agosto 2026.pptx</t>
+          <t>tivio-construtor-one-pager.html</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>pptx</t>
+          <t>html</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>43224</v>
+        <v>87214</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Tivio ALT 90 - Relatório de Gestão - Agosto 2026.pdf</t>
+          <t>tivio-email-fundos-credito.html</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>pdf</t>
+          <t>html</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>323905</v>
+        <v>130889</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Tivio ALT 90 - Relatório de Gestão - Agosto 2026.pptx</t>
+          <t>tivio-email-nordea-studio.html</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>pptx</t>
+          <t>html</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>43195</v>
+        <v>49750</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Tivio ALT Light - Relatório de Gestão - Agosto 2026.pdf</t>
+          <t>tivio-post-credito-estruturado.html</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>pdf</t>
+          <t>html</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>340010</v>
+        <v>113302</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Tivio ALT Light - Relatório de Gestão - Agosto 2026.pptx</t>
+          <t>tivio-post-credito-privado.html</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>pptx</t>
+          <t>html</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>42078</v>
+        <v>126107</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Tivio Infra Plus CDI - Relatório de Gestão - Agosto 2026.pdf</t>
+          <t>tivio-post-investment-solutions.html</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>pdf</t>
+          <t>html</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>351728</v>
+        <v>103643</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Tivio Infra Plus CDI - Relatório de Gestão - Agosto 2026.pptx</t>
+          <t>tivio-relatorio-gestao-credito-privado.html</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>pptx</t>
+          <t>html</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>47122</v>
+        <v>121698</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Tivio Esplanada - Relatório de Gestão - Agosto 2026.pdf</t>
+          <t>tivio-central.html</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>pdf</t>
+          <t>html</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>348578</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>Tivio Esplanada - Relatório de Gestão - Agosto 2026.pptx</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>pptx</t>
-        </is>
-      </c>
-      <c r="C38" t="n">
-        <v>46718</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>Tivio Legacy Prev - Relatório de Gestão - Agosto 2026.pdf</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>pdf</t>
-        </is>
-      </c>
-      <c r="C39" t="n">
-        <v>347005</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>Tivio Legacy Prev - Relatório de Gestão - Agosto 2026.pptx</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>pptx</t>
-        </is>
-      </c>
-      <c r="C40" t="n">
-        <v>47671</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>tivio-construtor-one-pager.html</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>html</t>
-        </is>
-      </c>
-      <c r="C41" t="n">
-        <v>87214</v>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>tivio-email-fundos-credito.html</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>html</t>
-        </is>
-      </c>
-      <c r="C42" t="n">
-        <v>130847</v>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>tivio-email-nordea-studio.html</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>html</t>
-        </is>
-      </c>
-      <c r="C43" t="n">
-        <v>49750</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>tivio-post-credito-estruturado.html</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>html</t>
-        </is>
-      </c>
-      <c r="C44" t="n">
-        <v>113275</v>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>tivio-post-credito-privado.html</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>html</t>
-        </is>
-      </c>
-      <c r="C45" t="n">
-        <v>126107</v>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>tivio-post-investment-solutions.html</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>html</t>
-        </is>
-      </c>
-      <c r="C46" t="n">
-        <v>103643</v>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>tivio-relatorio-gestao-credito-privado.html</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>html</t>
-        </is>
-      </c>
-      <c r="C47" t="n">
-        <v>121698</v>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>tivio-central.html</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>html</t>
-        </is>
-      </c>
-      <c r="C48" t="n">
-        <v>71673</v>
+        <v>66082</v>
       </c>
     </row>
   </sheetData>
